--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -119,9 +119,6 @@
     <t xml:space="preserve">2.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.1.1.1.2.1</t>
   </si>
   <si>
@@ -134,37 +131,25 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
@@ -173,13 +158,34 @@
     <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
     <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
 </sst>
 </file>
@@ -1388,7 +1394,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -1441,7 +1447,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1494,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L19" t="n">
         <v>3</v>
@@ -1538,7 +1544,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1591,7 +1597,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1644,7 +1650,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1697,7 +1703,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1706,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1750,7 +1756,7 @@
         <v>2</v>
       </c>
       <c r="H24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1759,7 +1765,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -1803,7 +1809,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1812,7 +1818,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="L25" t="n">
         <v>3</v>
@@ -1865,7 +1871,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1918,7 +1924,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -1971,7 +1977,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2024,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2077,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2130,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -2183,7 +2189,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2236,7 +2242,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2289,7 +2295,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2342,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2395,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2448,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -2501,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2554,7 +2560,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2607,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2660,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2713,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2766,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -2810,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="H44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I44" t="n">
         <v>2</v>
@@ -2819,7 +2825,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2863,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="H45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
@@ -2872,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -2916,7 +2922,7 @@
         <v>2</v>
       </c>
       <c r="H46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I46" t="n">
         <v>2</v>
@@ -2925,7 +2931,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -2969,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="H47" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I47" t="n">
         <v>2</v>
@@ -2978,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -3022,7 +3028,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I48" t="n">
         <v>2</v>
@@ -3031,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3075,7 +3081,7 @@
         <v>2</v>
       </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
@@ -3084,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -3137,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3190,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3243,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3296,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3349,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3402,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3455,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3508,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3561,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3614,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3667,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3720,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3773,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3826,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3879,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3932,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3985,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -4038,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4082,7 +4088,7 @@
         <v>2</v>
       </c>
       <c r="H68" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I68" t="n">
         <v>3</v>
@@ -4091,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4135,7 +4141,7 @@
         <v>2</v>
       </c>
       <c r="H69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I69" t="n">
         <v>3</v>
@@ -4144,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4188,7 +4194,7 @@
         <v>2</v>
       </c>
       <c r="H70" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I70" t="n">
         <v>3</v>
@@ -4197,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4241,7 +4247,7 @@
         <v>2</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I71" t="n">
         <v>3</v>
@@ -4250,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4294,7 +4300,7 @@
         <v>2</v>
       </c>
       <c r="H72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I72" t="n">
         <v>3</v>
@@ -4303,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4347,7 +4353,7 @@
         <v>2</v>
       </c>
       <c r="H73" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I73" t="n">
         <v>3</v>
@@ -4356,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4409,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4462,7 +4468,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4515,7 +4521,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4568,13 +4574,13 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
@@ -4621,13 +4627,13 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
@@ -4674,13 +4680,13 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
@@ -4727,7 +4733,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4780,7 +4786,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4833,7 +4839,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4886,7 +4892,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -4939,7 +4945,7 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
@@ -4992,7 +4998,7 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -5045,7 +5051,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5098,7 +5104,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5151,7 +5157,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5204,13 +5210,13 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
@@ -5257,13 +5263,13 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
@@ -5310,13 +5316,13 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
@@ -5354,7 +5360,7 @@
         <v>2</v>
       </c>
       <c r="H92" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I92" t="n">
         <v>4</v>
@@ -5363,7 +5369,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5407,7 +5413,7 @@
         <v>2</v>
       </c>
       <c r="H93" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I93" t="n">
         <v>4</v>
@@ -5416,7 +5422,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5460,7 +5466,7 @@
         <v>2</v>
       </c>
       <c r="H94" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I94" t="n">
         <v>4</v>
@@ -5469,7 +5475,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5513,7 +5519,7 @@
         <v>2</v>
       </c>
       <c r="H95" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I95" t="n">
         <v>4</v>
@@ -5522,7 +5528,7 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -5566,7 +5572,7 @@
         <v>2</v>
       </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I96" t="n">
         <v>4</v>
@@ -5575,7 +5581,7 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
@@ -5619,7 +5625,7 @@
         <v>2</v>
       </c>
       <c r="H97" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I97" t="n">
         <v>4</v>
@@ -5628,7 +5634,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
@@ -5681,7 +5687,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -5734,7 +5740,7 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
@@ -5787,7 +5793,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
@@ -5840,7 +5846,7 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -5893,7 +5899,7 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
@@ -5946,7 +5952,7 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -5999,7 +6005,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6052,7 +6058,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6105,7 +6111,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6158,7 +6164,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
@@ -6211,7 +6217,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
@@ -6264,7 +6270,7 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
@@ -6317,7 +6323,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -6370,7 +6376,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
@@ -6423,7 +6429,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
@@ -6476,7 +6482,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -6529,7 +6535,7 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
@@ -6582,7 +6588,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
@@ -6626,7 +6632,7 @@
         <v>2</v>
       </c>
       <c r="H116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I116" t="n">
         <v>5</v>
@@ -6635,7 +6641,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6679,7 +6685,7 @@
         <v>2</v>
       </c>
       <c r="H117" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I117" t="n">
         <v>5</v>
@@ -6688,7 +6694,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6732,7 +6738,7 @@
         <v>2</v>
       </c>
       <c r="H118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I118" t="n">
         <v>5</v>
@@ -6741,7 +6747,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6785,7 +6791,7 @@
         <v>2</v>
       </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I119" t="n">
         <v>5</v>
@@ -6794,7 +6800,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
@@ -6838,7 +6844,7 @@
         <v>2</v>
       </c>
       <c r="H120" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I120" t="n">
         <v>5</v>
@@ -6847,7 +6853,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
@@ -6891,7 +6897,7 @@
         <v>2</v>
       </c>
       <c r="H121" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I121" t="n">
         <v>5</v>
@@ -6900,7 +6906,7 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
@@ -6953,13 +6959,13 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
@@ -7006,13 +7012,13 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
@@ -7059,13 +7065,13 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
@@ -7112,7 +7118,7 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
@@ -7165,7 +7171,7 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
@@ -7218,7 +7224,7 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7271,13 +7277,13 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
@@ -7324,13 +7330,13 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
@@ -7377,13 +7383,13 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
@@ -7430,7 +7436,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -7483,7 +7489,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
@@ -7536,7 +7542,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7589,13 +7595,13 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
@@ -7642,13 +7648,13 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
@@ -7695,13 +7701,13 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
@@ -7748,7 +7754,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
@@ -7801,7 +7807,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
@@ -7854,7 +7860,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
@@ -7898,7 +7904,7 @@
         <v>2</v>
       </c>
       <c r="H140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I140" t="n">
         <v>6</v>
@@ -7907,13 +7913,13 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
@@ -7951,7 +7957,7 @@
         <v>2</v>
       </c>
       <c r="H141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I141" t="n">
         <v>6</v>
@@ -7960,13 +7966,13 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
@@ -8004,7 +8010,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I142" t="n">
         <v>6</v>
@@ -8013,13 +8019,13 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
@@ -8057,7 +8063,7 @@
         <v>2</v>
       </c>
       <c r="H143" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I143" t="n">
         <v>6</v>
@@ -8066,7 +8072,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
@@ -8110,7 +8116,7 @@
         <v>2</v>
       </c>
       <c r="H144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I144" t="n">
         <v>6</v>
@@ -8119,7 +8125,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
@@ -8163,7 +8169,7 @@
         <v>2</v>
       </c>
       <c r="H145" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I145" t="n">
         <v>6</v>
@@ -8172,7 +8178,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -8191,6 +8197,3822 @@
       </c>
       <c r="Q145" t="n">
         <v>633</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>289</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="s">
+        <v>50</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="s">
+        <v>51</v>
+      </c>
+      <c r="N146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O146" t="n">
+        <v>7</v>
+      </c>
+      <c r="P146" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>290</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>50</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>51</v>
+      </c>
+      <c r="N147" t="s">
+        <v>22</v>
+      </c>
+      <c r="O147" t="n">
+        <v>7</v>
+      </c>
+      <c r="P147" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>291</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>50</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="s">
+        <v>51</v>
+      </c>
+      <c r="N148" t="s">
+        <v>22</v>
+      </c>
+      <c r="O148" t="n">
+        <v>7</v>
+      </c>
+      <c r="P148" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>295</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>52</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>53</v>
+      </c>
+      <c r="N149" t="s">
+        <v>26</v>
+      </c>
+      <c r="O149" t="n">
+        <v>5</v>
+      </c>
+      <c r="P149" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>296</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>52</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="s">
+        <v>53</v>
+      </c>
+      <c r="N150" t="s">
+        <v>26</v>
+      </c>
+      <c r="O150" t="n">
+        <v>5</v>
+      </c>
+      <c r="P150" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>297</v>
+      </c>
+      <c r="B151" t="b">
+        <v>0</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>52</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="s">
+        <v>53</v>
+      </c>
+      <c r="N151" t="s">
+        <v>26</v>
+      </c>
+      <c r="O151" t="n">
+        <v>5</v>
+      </c>
+      <c r="P151" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>301</v>
+      </c>
+      <c r="B152" t="b">
+        <v>0</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" t="n">
+        <v>7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>50</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="s">
+        <v>28</v>
+      </c>
+      <c r="N152" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152" t="n">
+        <v>4</v>
+      </c>
+      <c r="P152" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>302</v>
+      </c>
+      <c r="B153" t="b">
+        <v>0</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I153" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>50</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" t="s">
+        <v>29</v>
+      </c>
+      <c r="O153" t="n">
+        <v>4</v>
+      </c>
+      <c r="P153" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>303</v>
+      </c>
+      <c r="B154" t="b">
+        <v>0</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>50</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O154" t="n">
+        <v>4</v>
+      </c>
+      <c r="P154" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>307</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>30</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>52</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="s">
+        <v>54</v>
+      </c>
+      <c r="N155" t="s">
+        <v>32</v>
+      </c>
+      <c r="O155" t="n">
+        <v>5</v>
+      </c>
+      <c r="P155" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>308</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>30</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>52</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="s">
+        <v>54</v>
+      </c>
+      <c r="N156" t="s">
+        <v>32</v>
+      </c>
+      <c r="O156" t="n">
+        <v>5</v>
+      </c>
+      <c r="P156" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>309</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>30</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>52</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" t="s">
+        <v>54</v>
+      </c>
+      <c r="N157" t="s">
+        <v>32</v>
+      </c>
+      <c r="O157" t="n">
+        <v>5</v>
+      </c>
+      <c r="P157" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>313</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="s">
+        <v>33</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="s">
+        <v>50</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>51</v>
+      </c>
+      <c r="N158" t="s">
+        <v>22</v>
+      </c>
+      <c r="O158" t="n">
+        <v>7</v>
+      </c>
+      <c r="P158" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>314</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="s">
+        <v>33</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>50</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="s">
+        <v>51</v>
+      </c>
+      <c r="N159" t="s">
+        <v>22</v>
+      </c>
+      <c r="O159" t="n">
+        <v>7</v>
+      </c>
+      <c r="P159" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>315</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>33</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>50</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="s">
+        <v>51</v>
+      </c>
+      <c r="N160" t="s">
+        <v>22</v>
+      </c>
+      <c r="O160" t="n">
+        <v>7</v>
+      </c>
+      <c r="P160" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>319</v>
+      </c>
+      <c r="B161" t="b">
+        <v>0</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>52</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="s">
+        <v>53</v>
+      </c>
+      <c r="N161" t="s">
+        <v>26</v>
+      </c>
+      <c r="O161" t="n">
+        <v>5</v>
+      </c>
+      <c r="P161" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>320</v>
+      </c>
+      <c r="B162" t="b">
+        <v>0</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>34</v>
+      </c>
+      <c r="I162" t="n">
+        <v>7</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>52</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="s">
+        <v>53</v>
+      </c>
+      <c r="N162" t="s">
+        <v>26</v>
+      </c>
+      <c r="O162" t="n">
+        <v>5</v>
+      </c>
+      <c r="P162" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>321</v>
+      </c>
+      <c r="B163" t="b">
+        <v>0</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="s">
+        <v>34</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>52</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="s">
+        <v>53</v>
+      </c>
+      <c r="N163" t="s">
+        <v>26</v>
+      </c>
+      <c r="O163" t="n">
+        <v>5</v>
+      </c>
+      <c r="P163" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>325</v>
+      </c>
+      <c r="B164" t="b">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="s">
+        <v>35</v>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="s">
+        <v>50</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" t="s">
+        <v>29</v>
+      </c>
+      <c r="O164" t="n">
+        <v>4</v>
+      </c>
+      <c r="P164" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>326</v>
+      </c>
+      <c r="B165" t="b">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="s">
+        <v>35</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="s">
+        <v>50</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" t="s">
+        <v>29</v>
+      </c>
+      <c r="O165" t="n">
+        <v>4</v>
+      </c>
+      <c r="P165" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>327</v>
+      </c>
+      <c r="B166" t="b">
+        <v>0</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="s">
+        <v>35</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
+        <v>50</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" t="s">
+        <v>28</v>
+      </c>
+      <c r="N166" t="s">
+        <v>29</v>
+      </c>
+      <c r="O166" t="n">
+        <v>4</v>
+      </c>
+      <c r="P166" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>331</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="s">
+        <v>36</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="s">
+        <v>52</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="s">
+        <v>54</v>
+      </c>
+      <c r="N167" t="s">
+        <v>32</v>
+      </c>
+      <c r="O167" t="n">
+        <v>5</v>
+      </c>
+      <c r="P167" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>332</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
+        <v>36</v>
+      </c>
+      <c r="I168" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="s">
+        <v>52</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="s">
+        <v>54</v>
+      </c>
+      <c r="N168" t="s">
+        <v>32</v>
+      </c>
+      <c r="O168" t="n">
+        <v>5</v>
+      </c>
+      <c r="P168" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>333</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="s">
+        <v>36</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="s">
+        <v>52</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="s">
+        <v>54</v>
+      </c>
+      <c r="N169" t="s">
+        <v>32</v>
+      </c>
+      <c r="O169" t="n">
+        <v>5</v>
+      </c>
+      <c r="P169" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>337</v>
+      </c>
+      <c r="B170" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>19</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="s">
+        <v>55</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="s">
+        <v>51</v>
+      </c>
+      <c r="N170" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" t="n">
+        <v>7</v>
+      </c>
+      <c r="P170" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>338</v>
+      </c>
+      <c r="B171" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>55</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="s">
+        <v>51</v>
+      </c>
+      <c r="N171" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" t="n">
+        <v>7</v>
+      </c>
+      <c r="P171" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>339</v>
+      </c>
+      <c r="B172" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="s">
+        <v>55</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="s">
+        <v>51</v>
+      </c>
+      <c r="N172" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" t="n">
+        <v>7</v>
+      </c>
+      <c r="P172" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>343</v>
+      </c>
+      <c r="B173" t="b">
+        <v>0</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="s">
+        <v>52</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="s">
+        <v>53</v>
+      </c>
+      <c r="N173" t="s">
+        <v>26</v>
+      </c>
+      <c r="O173" t="n">
+        <v>5</v>
+      </c>
+      <c r="P173" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>344</v>
+      </c>
+      <c r="B174" t="b">
+        <v>0</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="s">
+        <v>52</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="s">
+        <v>53</v>
+      </c>
+      <c r="N174" t="s">
+        <v>26</v>
+      </c>
+      <c r="O174" t="n">
+        <v>5</v>
+      </c>
+      <c r="P174" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>345</v>
+      </c>
+      <c r="B175" t="b">
+        <v>0</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>18</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>52</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="s">
+        <v>53</v>
+      </c>
+      <c r="N175" t="s">
+        <v>26</v>
+      </c>
+      <c r="O175" t="n">
+        <v>5</v>
+      </c>
+      <c r="P175" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>349</v>
+      </c>
+      <c r="B176" t="b">
+        <v>0</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>27</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>55</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O176" t="n">
+        <v>4</v>
+      </c>
+      <c r="P176" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>350</v>
+      </c>
+      <c r="B177" t="b">
+        <v>0</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>18</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="s">
+        <v>27</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>55</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177" t="n">
+        <v>4</v>
+      </c>
+      <c r="P177" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>351</v>
+      </c>
+      <c r="B178" t="b">
+        <v>0</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>27</v>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="s">
+        <v>55</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="s">
+        <v>28</v>
+      </c>
+      <c r="N178" t="s">
+        <v>29</v>
+      </c>
+      <c r="O178" t="n">
+        <v>4</v>
+      </c>
+      <c r="P178" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>355</v>
+      </c>
+      <c r="B179" t="b">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>30</v>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="s">
+        <v>52</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="s">
+        <v>54</v>
+      </c>
+      <c r="N179" t="s">
+        <v>32</v>
+      </c>
+      <c r="O179" t="n">
+        <v>5</v>
+      </c>
+      <c r="P179" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>356</v>
+      </c>
+      <c r="B180" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>18</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>30</v>
+      </c>
+      <c r="I180" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="s">
+        <v>52</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="s">
+        <v>54</v>
+      </c>
+      <c r="N180" t="s">
+        <v>32</v>
+      </c>
+      <c r="O180" t="n">
+        <v>5</v>
+      </c>
+      <c r="P180" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>357</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>18</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>30</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="s">
+        <v>52</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="s">
+        <v>54</v>
+      </c>
+      <c r="N181" t="s">
+        <v>32</v>
+      </c>
+      <c r="O181" t="n">
+        <v>5</v>
+      </c>
+      <c r="P181" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>361</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>33</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="s">
+        <v>55</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
+        <v>51</v>
+      </c>
+      <c r="N182" t="s">
+        <v>22</v>
+      </c>
+      <c r="O182" t="n">
+        <v>7</v>
+      </c>
+      <c r="P182" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>362</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>33</v>
+      </c>
+      <c r="I183" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="s">
+        <v>55</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>51</v>
+      </c>
+      <c r="N183" t="s">
+        <v>22</v>
+      </c>
+      <c r="O183" t="n">
+        <v>7</v>
+      </c>
+      <c r="P183" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>363</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>33</v>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="s">
+        <v>55</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>51</v>
+      </c>
+      <c r="N184" t="s">
+        <v>22</v>
+      </c>
+      <c r="O184" t="n">
+        <v>7</v>
+      </c>
+      <c r="P184" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>367</v>
+      </c>
+      <c r="B185" t="b">
+        <v>0</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>34</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="s">
+        <v>52</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="s">
+        <v>53</v>
+      </c>
+      <c r="N185" t="s">
+        <v>26</v>
+      </c>
+      <c r="O185" t="n">
+        <v>5</v>
+      </c>
+      <c r="P185" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>368</v>
+      </c>
+      <c r="B186" t="b">
+        <v>0</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="s">
+        <v>34</v>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>52</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="s">
+        <v>53</v>
+      </c>
+      <c r="N186" t="s">
+        <v>26</v>
+      </c>
+      <c r="O186" t="n">
+        <v>5</v>
+      </c>
+      <c r="P186" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>369</v>
+      </c>
+      <c r="B187" t="b">
+        <v>0</v>
+      </c>
+      <c r="C187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="s">
+        <v>34</v>
+      </c>
+      <c r="I187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>52</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="s">
+        <v>53</v>
+      </c>
+      <c r="N187" t="s">
+        <v>26</v>
+      </c>
+      <c r="O187" t="n">
+        <v>5</v>
+      </c>
+      <c r="P187" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>373</v>
+      </c>
+      <c r="B188" t="b">
+        <v>0</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="s">
+        <v>35</v>
+      </c>
+      <c r="I188" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="s">
+        <v>55</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188" t="s">
+        <v>29</v>
+      </c>
+      <c r="O188" t="n">
+        <v>4</v>
+      </c>
+      <c r="P188" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>374</v>
+      </c>
+      <c r="B189" t="b">
+        <v>0</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="s">
+        <v>35</v>
+      </c>
+      <c r="I189" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="s">
+        <v>55</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
+        <v>29</v>
+      </c>
+      <c r="O189" t="n">
+        <v>4</v>
+      </c>
+      <c r="P189" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>375</v>
+      </c>
+      <c r="B190" t="b">
+        <v>0</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="s">
+        <v>35</v>
+      </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="s">
+        <v>55</v>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="s">
+        <v>28</v>
+      </c>
+      <c r="N190" t="s">
+        <v>29</v>
+      </c>
+      <c r="O190" t="n">
+        <v>4</v>
+      </c>
+      <c r="P190" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>379</v>
+      </c>
+      <c r="B191" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="s">
+        <v>36</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="s">
+        <v>52</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="s">
+        <v>54</v>
+      </c>
+      <c r="N191" t="s">
+        <v>32</v>
+      </c>
+      <c r="O191" t="n">
+        <v>5</v>
+      </c>
+      <c r="P191" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>380</v>
+      </c>
+      <c r="B192" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="s">
+        <v>36</v>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="s">
+        <v>52</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="s">
+        <v>54</v>
+      </c>
+      <c r="N192" t="s">
+        <v>32</v>
+      </c>
+      <c r="O192" t="n">
+        <v>5</v>
+      </c>
+      <c r="P192" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>381</v>
+      </c>
+      <c r="B193" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="s">
+        <v>36</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>52</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>54</v>
+      </c>
+      <c r="N193" t="s">
+        <v>32</v>
+      </c>
+      <c r="O193" t="n">
+        <v>5</v>
+      </c>
+      <c r="P193" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>385</v>
+      </c>
+      <c r="B194" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" t="n">
+        <v>9</v>
+      </c>
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>56</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>57</v>
+      </c>
+      <c r="N194" t="s">
+        <v>22</v>
+      </c>
+      <c r="O194" t="n">
+        <v>5</v>
+      </c>
+      <c r="P194" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>386</v>
+      </c>
+      <c r="B195" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>56</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="s">
+        <v>57</v>
+      </c>
+      <c r="N195" t="s">
+        <v>22</v>
+      </c>
+      <c r="O195" t="n">
+        <v>5</v>
+      </c>
+      <c r="P195" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>387</v>
+      </c>
+      <c r="B196" t="b">
+        <v>0</v>
+      </c>
+      <c r="C196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="s">
+        <v>56</v>
+      </c>
+      <c r="L196" t="n">
+        <v>3</v>
+      </c>
+      <c r="M196" t="s">
+        <v>57</v>
+      </c>
+      <c r="N196" t="s">
+        <v>22</v>
+      </c>
+      <c r="O196" t="n">
+        <v>5</v>
+      </c>
+      <c r="P196" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>391</v>
+      </c>
+      <c r="B197" t="b">
+        <v>0</v>
+      </c>
+      <c r="C197" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="s">
+        <v>52</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="s">
+        <v>53</v>
+      </c>
+      <c r="N197" t="s">
+        <v>26</v>
+      </c>
+      <c r="O197" t="n">
+        <v>5</v>
+      </c>
+      <c r="P197" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>392</v>
+      </c>
+      <c r="B198" t="b">
+        <v>0</v>
+      </c>
+      <c r="C198" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="s">
+        <v>52</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="s">
+        <v>53</v>
+      </c>
+      <c r="N198" t="s">
+        <v>26</v>
+      </c>
+      <c r="O198" t="n">
+        <v>5</v>
+      </c>
+      <c r="P198" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>393</v>
+      </c>
+      <c r="B199" t="b">
+        <v>0</v>
+      </c>
+      <c r="C199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="s">
+        <v>52</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="s">
+        <v>53</v>
+      </c>
+      <c r="N199" t="s">
+        <v>26</v>
+      </c>
+      <c r="O199" t="n">
+        <v>5</v>
+      </c>
+      <c r="P199" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>397</v>
+      </c>
+      <c r="B200" t="b">
+        <v>0</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="s">
+        <v>27</v>
+      </c>
+      <c r="I200" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="s">
+        <v>56</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="s">
+        <v>49</v>
+      </c>
+      <c r="N200" t="s">
+        <v>29</v>
+      </c>
+      <c r="O200" t="n">
+        <v>3</v>
+      </c>
+      <c r="P200" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>398</v>
+      </c>
+      <c r="B201" t="b">
+        <v>0</v>
+      </c>
+      <c r="C201" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>56</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>49</v>
+      </c>
+      <c r="N201" t="s">
+        <v>29</v>
+      </c>
+      <c r="O201" t="n">
+        <v>3</v>
+      </c>
+      <c r="P201" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>399</v>
+      </c>
+      <c r="B202" t="b">
+        <v>0</v>
+      </c>
+      <c r="C202" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="s">
+        <v>27</v>
+      </c>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>56</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="s">
+        <v>49</v>
+      </c>
+      <c r="N202" t="s">
+        <v>29</v>
+      </c>
+      <c r="O202" t="n">
+        <v>3</v>
+      </c>
+      <c r="P202" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>403</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="s">
+        <v>30</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>52</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>54</v>
+      </c>
+      <c r="N203" t="s">
+        <v>32</v>
+      </c>
+      <c r="O203" t="n">
+        <v>5</v>
+      </c>
+      <c r="P203" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>404</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="s">
+        <v>30</v>
+      </c>
+      <c r="I204" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>52</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="s">
+        <v>54</v>
+      </c>
+      <c r="N204" t="s">
+        <v>32</v>
+      </c>
+      <c r="O204" t="n">
+        <v>5</v>
+      </c>
+      <c r="P204" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>405</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="s">
+        <v>30</v>
+      </c>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="s">
+        <v>52</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="s">
+        <v>54</v>
+      </c>
+      <c r="N205" t="s">
+        <v>32</v>
+      </c>
+      <c r="O205" t="n">
+        <v>5</v>
+      </c>
+      <c r="P205" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>409</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="s">
+        <v>33</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>56</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>57</v>
+      </c>
+      <c r="N206" t="s">
+        <v>22</v>
+      </c>
+      <c r="O206" t="n">
+        <v>5</v>
+      </c>
+      <c r="P206" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>410</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="s">
+        <v>33</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>56</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="s">
+        <v>57</v>
+      </c>
+      <c r="N207" t="s">
+        <v>22</v>
+      </c>
+      <c r="O207" t="n">
+        <v>5</v>
+      </c>
+      <c r="P207" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>411</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="s">
+        <v>33</v>
+      </c>
+      <c r="I208" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>56</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>57</v>
+      </c>
+      <c r="N208" t="s">
+        <v>22</v>
+      </c>
+      <c r="O208" t="n">
+        <v>5</v>
+      </c>
+      <c r="P208" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>415</v>
+      </c>
+      <c r="B209" t="b">
+        <v>0</v>
+      </c>
+      <c r="C209" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="s">
+        <v>34</v>
+      </c>
+      <c r="I209" t="n">
+        <v>9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>52</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>53</v>
+      </c>
+      <c r="N209" t="s">
+        <v>26</v>
+      </c>
+      <c r="O209" t="n">
+        <v>5</v>
+      </c>
+      <c r="P209" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>416</v>
+      </c>
+      <c r="B210" t="b">
+        <v>0</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>18</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="s">
+        <v>34</v>
+      </c>
+      <c r="I210" t="n">
+        <v>9</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="s">
+        <v>52</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="s">
+        <v>53</v>
+      </c>
+      <c r="N210" t="s">
+        <v>26</v>
+      </c>
+      <c r="O210" t="n">
+        <v>5</v>
+      </c>
+      <c r="P210" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>417</v>
+      </c>
+      <c r="B211" t="b">
+        <v>0</v>
+      </c>
+      <c r="C211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="s">
+        <v>34</v>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="s">
+        <v>52</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>53</v>
+      </c>
+      <c r="N211" t="s">
+        <v>26</v>
+      </c>
+      <c r="O211" t="n">
+        <v>5</v>
+      </c>
+      <c r="P211" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>421</v>
+      </c>
+      <c r="B212" t="b">
+        <v>0</v>
+      </c>
+      <c r="C212" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="s">
+        <v>35</v>
+      </c>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="s">
+        <v>56</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="s">
+        <v>49</v>
+      </c>
+      <c r="N212" t="s">
+        <v>29</v>
+      </c>
+      <c r="O212" t="n">
+        <v>3</v>
+      </c>
+      <c r="P212" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>422</v>
+      </c>
+      <c r="B213" t="b">
+        <v>0</v>
+      </c>
+      <c r="C213" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213" t="s">
+        <v>18</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="s">
+        <v>35</v>
+      </c>
+      <c r="I213" t="n">
+        <v>9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>56</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="s">
+        <v>49</v>
+      </c>
+      <c r="N213" t="s">
+        <v>29</v>
+      </c>
+      <c r="O213" t="n">
+        <v>3</v>
+      </c>
+      <c r="P213" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>423</v>
+      </c>
+      <c r="B214" t="b">
+        <v>0</v>
+      </c>
+      <c r="C214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="s">
+        <v>35</v>
+      </c>
+      <c r="I214" t="n">
+        <v>9</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>56</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="s">
+        <v>49</v>
+      </c>
+      <c r="N214" t="s">
+        <v>29</v>
+      </c>
+      <c r="O214" t="n">
+        <v>3</v>
+      </c>
+      <c r="P214" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>427</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="s">
+        <v>36</v>
+      </c>
+      <c r="I215" t="n">
+        <v>9</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>52</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="s">
+        <v>54</v>
+      </c>
+      <c r="N215" t="s">
+        <v>32</v>
+      </c>
+      <c r="O215" t="n">
+        <v>5</v>
+      </c>
+      <c r="P215" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>428</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" t="s">
+        <v>18</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="s">
+        <v>36</v>
+      </c>
+      <c r="I216" t="n">
+        <v>9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="s">
+        <v>52</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="s">
+        <v>54</v>
+      </c>
+      <c r="N216" t="s">
+        <v>32</v>
+      </c>
+      <c r="O216" t="n">
+        <v>5</v>
+      </c>
+      <c r="P216" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>429</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="s">
+        <v>36</v>
+      </c>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="s">
+        <v>52</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="s">
+        <v>54</v>
+      </c>
+      <c r="N217" t="s">
+        <v>32</v>
+      </c>
+      <c r="O217" t="n">
+        <v>5</v>
+      </c>
+      <c r="P217" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+    <t xml:space="preserve">c(74, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2053)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e12", "e15", "e19", "e34", "e369", "e398", "e427", "e460", "e505")</t>
+    <t xml:space="preserve">c("e19", "e34", "e398", "e427", "e460")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 183, 184, 185, 186, 1890, 1891, 1892)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e20", "e31", "e48", "e388", "e428", "e452")</t>
+    <t xml:space="preserve">c("e20", "e31", "e48", "e428")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">c("e407", "e408", "e445", "e476")</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e26", "e27", "e28", "e29", "e364", "e372", "e493", "e514", "e519")</t>
+    <t xml:space="preserve">c("e26", "e27", "e28", "e29", "e364", "e519")</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
@@ -125,12 +125,6 @@
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
@@ -140,52 +134,40 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
+    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 1890, 1891, 1892)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+    <t xml:space="preserve">c(115, 116, 117, 118, 2321, 2322, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
 </sst>
 </file>
@@ -611,13 +593,13 @@
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q2" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3">
@@ -664,13 +646,13 @@
         <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q3" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4">
@@ -717,13 +699,13 @@
         <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q4" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
@@ -770,13 +752,13 @@
         <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q5" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -823,13 +805,13 @@
         <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q6" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -876,13 +858,13 @@
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q7" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -932,10 +914,10 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q8" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -985,10 +967,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q9" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -1038,10 +1020,10 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q10" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -1088,13 +1070,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="12">
@@ -1141,13 +1123,13 @@
         <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13">
@@ -1194,13 +1176,13 @@
         <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q13" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="14">
@@ -1247,13 +1229,13 @@
         <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q14" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15">
@@ -1300,13 +1282,13 @@
         <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q15" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16">
@@ -1353,13 +1335,13 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q16" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17">
@@ -1406,13 +1388,13 @@
         <v>26</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q17" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -1459,13 +1441,13 @@
         <v>26</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -1512,13 +1494,13 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q19" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20">
@@ -1568,10 +1550,10 @@
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21">
@@ -1621,10 +1603,10 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22">
@@ -1674,10 +1656,10 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q22" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
@@ -1724,13 +1706,13 @@
         <v>32</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P23" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q23" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24">
@@ -1777,13 +1759,13 @@
         <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q24" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="25">
@@ -1830,13 +1812,13 @@
         <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q25" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26">
@@ -1871,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1883,13 +1865,13 @@
         <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q26" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27">
@@ -1924,7 +1906,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -1936,13 +1918,13 @@
         <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P27" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q27" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28">
@@ -1977,7 +1959,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -1989,13 +1971,13 @@
         <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P28" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q28" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29">
@@ -2030,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2042,13 +2024,13 @@
         <v>26</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q29" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
@@ -2083,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2095,13 +2077,13 @@
         <v>26</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q30" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31">
@@ -2136,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -2148,13 +2130,13 @@
         <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q31" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
@@ -2189,7 +2171,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2204,10 +2186,10 @@
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33">
@@ -2242,7 +2224,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2257,10 +2239,10 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q33" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
@@ -2295,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2310,10 +2292,10 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q34" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35">
@@ -2348,7 +2330,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2360,13 +2342,13 @@
         <v>32</v>
       </c>
       <c r="O35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q35" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="36">
@@ -2401,7 +2383,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2413,13 +2395,13 @@
         <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q36" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37">
@@ -2454,7 +2436,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -2466,13 +2448,13 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P37" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q37" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38">
@@ -2507,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2519,13 +2501,13 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P38" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q38" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39">
@@ -2560,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2572,13 +2554,13 @@
         <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P39" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q39" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -2613,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2625,13 +2607,13 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P40" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q40" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41">
@@ -2666,7 +2648,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2678,13 +2660,13 @@
         <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q41" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
@@ -2719,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2731,13 +2713,13 @@
         <v>26</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q42" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -2772,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -2784,13 +2766,13 @@
         <v>26</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q43" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
@@ -2825,7 +2807,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2840,10 +2822,10 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q44" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45">
@@ -2878,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -2893,10 +2875,10 @@
         <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q45" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
@@ -2931,7 +2913,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -2946,10 +2928,10 @@
         <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q46" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
@@ -2984,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2996,13 +2978,13 @@
         <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P47" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q47" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="48">
@@ -3037,7 +3019,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3049,13 +3031,13 @@
         <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P48" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q48" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49">
@@ -3090,7 +3072,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -3102,13 +3084,13 @@
         <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P49" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q49" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="50">
@@ -3143,7 +3125,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3155,13 +3137,13 @@
         <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P50" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q50" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51">
@@ -3196,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3208,13 +3190,13 @@
         <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P51" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q51" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52">
@@ -3249,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3261,13 +3243,13 @@
         <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P52" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q52" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53">
@@ -3302,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3314,13 +3296,13 @@
         <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P53" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q53" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
@@ -3355,7 +3337,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3367,13 +3349,13 @@
         <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P54" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q54" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55">
@@ -3408,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3420,13 +3402,13 @@
         <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P55" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q55" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56">
@@ -3461,7 +3443,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3476,10 +3458,10 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q56" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57">
@@ -3514,7 +3496,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3529,10 +3511,10 @@
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q57" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="58">
@@ -3567,7 +3549,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3582,10 +3564,10 @@
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q58" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59">
@@ -3620,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3632,13 +3614,13 @@
         <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q59" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="60">
@@ -3673,7 +3655,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3685,13 +3667,13 @@
         <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P60" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q60" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61">
@@ -3726,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3738,13 +3720,13 @@
         <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P61" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q61" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="62">
@@ -3779,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3791,13 +3773,13 @@
         <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P62" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q62" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63">
@@ -3832,7 +3814,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3844,13 +3826,13 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P63" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q63" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64">
@@ -3885,7 +3867,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3897,13 +3879,13 @@
         <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P64" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q64" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65">
@@ -3938,7 +3920,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3950,13 +3932,13 @@
         <v>26</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P65" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q65" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="66">
@@ -3991,7 +3973,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -4003,13 +3985,13 @@
         <v>26</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q66" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -4044,7 +4026,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4056,13 +4038,13 @@
         <v>26</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P67" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q67" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68">
@@ -4097,7 +4079,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4112,10 +4094,10 @@
         <v>4</v>
       </c>
       <c r="P68" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q68" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
@@ -4150,7 +4132,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4165,10 +4147,10 @@
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q69" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="70">
@@ -4203,7 +4185,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4218,10 +4200,10 @@
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q70" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="71">
@@ -4256,7 +4238,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4268,13 +4250,13 @@
         <v>32</v>
       </c>
       <c r="O71" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P71" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q71" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="72">
@@ -4309,7 +4291,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4321,13 +4303,13 @@
         <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P72" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q72" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="73">
@@ -4362,7 +4344,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4374,13 +4356,13 @@
         <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P73" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q73" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="74">
@@ -4415,7 +4397,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4427,13 +4409,13 @@
         <v>22</v>
       </c>
       <c r="O74" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P74" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q74" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75">
@@ -4468,7 +4450,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4480,13 +4462,13 @@
         <v>22</v>
       </c>
       <c r="O75" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P75" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q75" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76">
@@ -4521,7 +4503,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4533,13 +4515,13 @@
         <v>22</v>
       </c>
       <c r="O76" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P76" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q76" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77">
@@ -4574,25 +4556,25 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P77" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q77" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -4627,25 +4609,25 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P78" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q78" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="79">
@@ -4680,25 +4662,25 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P79" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q79" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -4733,7 +4715,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4748,10 +4730,10 @@
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q80" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -4786,7 +4768,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4801,10 +4783,10 @@
         <v>4</v>
       </c>
       <c r="P81" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q81" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82">
@@ -4839,7 +4821,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4854,10 +4836,10 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q82" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="83">
@@ -4892,7 +4874,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -4904,13 +4886,13 @@
         <v>32</v>
       </c>
       <c r="O83" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P83" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q83" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="84">
@@ -4945,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
@@ -4957,13 +4939,13 @@
         <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P84" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q84" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="85">
@@ -4998,7 +4980,7 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -5010,13 +4992,13 @@
         <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P85" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q85" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="86">
@@ -5051,7 +5033,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5063,13 +5045,13 @@
         <v>22</v>
       </c>
       <c r="O86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P86" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q86" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="87">
@@ -5104,7 +5086,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5116,13 +5098,13 @@
         <v>22</v>
       </c>
       <c r="O87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q87" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88">
@@ -5157,7 +5139,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5169,13 +5151,13 @@
         <v>22</v>
       </c>
       <c r="O88" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P88" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q88" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89">
@@ -5210,25 +5192,25 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P89" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q89" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="90">
@@ -5263,25 +5245,25 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P90" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q90" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="91">
@@ -5316,25 +5298,25 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
       </c>
       <c r="O91" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P91" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q91" t="n">
-        <v>88</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92">
@@ -5369,7 +5351,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5384,10 +5366,10 @@
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q92" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93">
@@ -5422,7 +5404,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5437,10 +5419,10 @@
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q93" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="94">
@@ -5475,7 +5457,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5490,10 +5472,10 @@
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q94" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95">
@@ -5528,7 +5510,7 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -5540,13 +5522,13 @@
         <v>32</v>
       </c>
       <c r="O95" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P95" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q95" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="96">
@@ -5581,7 +5563,7 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
@@ -5593,13 +5575,13 @@
         <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P96" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q96" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="97">
@@ -5634,7 +5616,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
@@ -5646,13 +5628,13 @@
         <v>32</v>
       </c>
       <c r="O97" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P97" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q97" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98">
@@ -5687,7 +5669,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -5699,13 +5681,13 @@
         <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P98" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q98" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99">
@@ -5740,7 +5722,7 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
@@ -5752,13 +5734,13 @@
         <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P99" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q99" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100">
@@ -5793,7 +5775,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
@@ -5805,13 +5787,13 @@
         <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P100" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q100" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101">
@@ -5846,7 +5828,7 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -5858,13 +5840,13 @@
         <v>26</v>
       </c>
       <c r="O101" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P101" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q101" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="102">
@@ -5899,7 +5881,7 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
@@ -5911,13 +5893,13 @@
         <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P102" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q102" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103">
@@ -5952,7 +5934,7 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -5964,13 +5946,13 @@
         <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P103" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q103" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="104">
@@ -6005,7 +5987,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6020,10 +6002,10 @@
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q104" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105">
@@ -6058,7 +6040,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6073,10 +6055,10 @@
         <v>4</v>
       </c>
       <c r="P105" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q105" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="106">
@@ -6111,7 +6093,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6126,10 +6108,10 @@
         <v>4</v>
       </c>
       <c r="P106" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q106" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="107">
@@ -6164,7 +6146,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
@@ -6176,13 +6158,13 @@
         <v>32</v>
       </c>
       <c r="O107" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P107" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q107" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="108">
@@ -6217,7 +6199,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
@@ -6229,13 +6211,13 @@
         <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P108" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q108" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109">
@@ -6270,7 +6252,7 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
@@ -6282,13 +6264,13 @@
         <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P109" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q109" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="110">
@@ -6323,7 +6305,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -6335,13 +6317,13 @@
         <v>22</v>
       </c>
       <c r="O110" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P110" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q110" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111">
@@ -6376,7 +6358,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
@@ -6388,13 +6370,13 @@
         <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P111" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q111" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112">
@@ -6429,7 +6411,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
@@ -6441,13 +6423,13 @@
         <v>22</v>
       </c>
       <c r="O112" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P112" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="Q112" t="n">
-        <v>306</v>
+        <v>237</v>
       </c>
     </row>
     <row r="113">
@@ -6482,7 +6464,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -6494,13 +6476,13 @@
         <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P113" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q113" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="114">
@@ -6535,7 +6517,7 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
@@ -6547,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P114" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q114" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115">
@@ -6588,7 +6570,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
@@ -6600,13 +6582,13 @@
         <v>26</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P115" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q115" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116">
@@ -6641,7 +6623,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6656,10 +6638,10 @@
         <v>4</v>
       </c>
       <c r="P116" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q116" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117">
@@ -6694,7 +6676,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6709,10 +6691,10 @@
         <v>4</v>
       </c>
       <c r="P117" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q117" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="118">
@@ -6747,7 +6729,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6762,10 +6744,10 @@
         <v>4</v>
       </c>
       <c r="P118" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q118" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="119">
@@ -6800,7 +6782,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
@@ -6812,13 +6794,13 @@
         <v>32</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P119" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q119" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="120">
@@ -6853,7 +6835,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
@@ -6865,13 +6847,13 @@
         <v>32</v>
       </c>
       <c r="O120" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P120" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q120" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="121">
@@ -6906,7 +6888,7 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
@@ -6918,13 +6900,13 @@
         <v>32</v>
       </c>
       <c r="O121" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P121" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q121" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="122">
@@ -6959,25 +6941,25 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P122" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q122" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123">
@@ -7012,25 +6994,25 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P123" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q123" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124">
@@ -7065,25 +7047,25 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P124" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q124" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="125">
@@ -7118,7 +7100,7 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
@@ -7130,13 +7112,13 @@
         <v>26</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P125" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q125" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="126">
@@ -7171,7 +7153,7 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
@@ -7183,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="O126" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P126" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q126" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="127">
@@ -7224,7 +7206,7 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7236,13 +7218,13 @@
         <v>26</v>
       </c>
       <c r="O127" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P127" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q127" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="128">
@@ -7277,13 +7259,13 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
+        <v>44</v>
+      </c>
+      <c r="L128" t="n">
+        <v>1</v>
+      </c>
+      <c r="M128" t="s">
         <v>46</v>
-      </c>
-      <c r="L128" t="n">
-        <v>1</v>
-      </c>
-      <c r="M128" t="s">
-        <v>49</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
@@ -7292,10 +7274,10 @@
         <v>3</v>
       </c>
       <c r="P128" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q128" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="129">
@@ -7330,13 +7312,13 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
+        <v>44</v>
+      </c>
+      <c r="L129" t="n">
+        <v>2</v>
+      </c>
+      <c r="M129" t="s">
         <v>46</v>
-      </c>
-      <c r="L129" t="n">
-        <v>2</v>
-      </c>
-      <c r="M129" t="s">
-        <v>49</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
@@ -7345,10 +7327,10 @@
         <v>3</v>
       </c>
       <c r="P129" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q129" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="130">
@@ -7383,13 +7365,13 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
+        <v>44</v>
+      </c>
+      <c r="L130" t="n">
+        <v>3</v>
+      </c>
+      <c r="M130" t="s">
         <v>46</v>
-      </c>
-      <c r="L130" t="n">
-        <v>3</v>
-      </c>
-      <c r="M130" t="s">
-        <v>49</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
@@ -7398,10 +7380,10 @@
         <v>3</v>
       </c>
       <c r="P130" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q130" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="131">
@@ -7436,7 +7418,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -7448,13 +7430,13 @@
         <v>32</v>
       </c>
       <c r="O131" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P131" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q131" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="132">
@@ -7489,7 +7471,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
@@ -7501,13 +7483,13 @@
         <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P132" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q132" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="133">
@@ -7542,7 +7524,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7554,13 +7536,13 @@
         <v>32</v>
       </c>
       <c r="O133" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P133" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q133" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="134">
@@ -7595,25 +7577,25 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P134" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q134" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="135">
@@ -7648,25 +7630,25 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P135" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q135" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136">
@@ -7701,25 +7683,25 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P136" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="Q136" t="n">
-        <v>286</v>
+        <v>237</v>
       </c>
     </row>
     <row r="137">
@@ -7754,7 +7736,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
@@ -7766,13 +7748,13 @@
         <v>26</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P137" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q137" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="138">
@@ -7807,7 +7789,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
@@ -7819,13 +7801,13 @@
         <v>26</v>
       </c>
       <c r="O138" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P138" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q138" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="139">
@@ -7860,7 +7842,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
@@ -7872,13 +7854,13 @@
         <v>26</v>
       </c>
       <c r="O139" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P139" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Q139" t="n">
-        <v>173</v>
+        <v>100</v>
       </c>
     </row>
     <row r="140">
@@ -7886,7 +7868,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -7913,13 +7895,13 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
+        <v>44</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="s">
         <v>46</v>
-      </c>
-      <c r="L140" t="n">
-        <v>1</v>
-      </c>
-      <c r="M140" t="s">
-        <v>49</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
@@ -7928,10 +7910,10 @@
         <v>3</v>
       </c>
       <c r="P140" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q140" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="141">
@@ -7939,7 +7921,7 @@
         <v>278</v>
       </c>
       <c r="B141" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -7966,13 +7948,13 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
+        <v>44</v>
+      </c>
+      <c r="L141" t="n">
+        <v>2</v>
+      </c>
+      <c r="M141" t="s">
         <v>46</v>
-      </c>
-      <c r="L141" t="n">
-        <v>2</v>
-      </c>
-      <c r="M141" t="s">
-        <v>49</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
@@ -7981,10 +7963,10 @@
         <v>3</v>
       </c>
       <c r="P141" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q141" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="142">
@@ -7992,7 +7974,7 @@
         <v>279</v>
       </c>
       <c r="B142" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -8019,13 +8001,13 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
+        <v>44</v>
+      </c>
+      <c r="L142" t="n">
+        <v>3</v>
+      </c>
+      <c r="M142" t="s">
         <v>46</v>
-      </c>
-      <c r="L142" t="n">
-        <v>3</v>
-      </c>
-      <c r="M142" t="s">
-        <v>49</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
@@ -8034,10 +8016,10 @@
         <v>3</v>
       </c>
       <c r="P142" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q142" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="143">
@@ -8072,7 +8054,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
@@ -8084,13 +8066,13 @@
         <v>32</v>
       </c>
       <c r="O143" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P143" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q143" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="144">
@@ -8125,7 +8107,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
@@ -8137,13 +8119,13 @@
         <v>32</v>
       </c>
       <c r="O144" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P144" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q144" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="145">
@@ -8178,7 +8160,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -8190,13 +8172,13 @@
         <v>32</v>
       </c>
       <c r="O145" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P145" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="Q145" t="n">
-        <v>633</v>
+        <v>263</v>
       </c>
     </row>
     <row r="146">
@@ -8204,7 +8186,7 @@
         <v>289</v>
       </c>
       <c r="B146" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -8231,33 +8213,29 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N146" t="s">
         <v>22</v>
       </c>
-      <c r="O146" t="n">
-        <v>7</v>
-      </c>
+      <c r="O146"/>
       <c r="P146" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q146"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>290</v>
       </c>
       <c r="B147" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -8284,33 +8262,29 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N147" t="s">
         <v>22</v>
       </c>
-      <c r="O147" t="n">
-        <v>7</v>
-      </c>
+      <c r="O147"/>
       <c r="P147" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q147"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>291</v>
       </c>
       <c r="B148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -8337,26 +8311,22 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N148" t="s">
         <v>22</v>
       </c>
-      <c r="O148" t="n">
-        <v>7</v>
-      </c>
+      <c r="O148"/>
       <c r="P148" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q148"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8390,25 +8360,25 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N149" t="s">
         <v>26</v>
       </c>
       <c r="O149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P149" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q149" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="150">
@@ -8443,25 +8413,25 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N150" t="s">
         <v>26</v>
       </c>
       <c r="O150" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P150" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q150" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="151">
@@ -8496,25 +8466,25 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N151" t="s">
         <v>26</v>
       </c>
       <c r="O151" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P151" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q151" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152">
@@ -8549,7 +8519,7 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
@@ -8564,10 +8534,10 @@
         <v>4</v>
       </c>
       <c r="P152" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q152" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153">
@@ -8602,7 +8572,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
@@ -8617,10 +8587,10 @@
         <v>4</v>
       </c>
       <c r="P153" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q153" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="154">
@@ -8655,7 +8625,7 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
@@ -8670,10 +8640,10 @@
         <v>4</v>
       </c>
       <c r="P154" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q154" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="155">
@@ -8708,25 +8678,25 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N155" t="s">
         <v>32</v>
       </c>
       <c r="O155" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P155" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q155" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156">
@@ -8761,25 +8731,25 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N156" t="s">
         <v>32</v>
       </c>
       <c r="O156" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P156" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q156" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="157">
@@ -8814,25 +8784,25 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N157" t="s">
         <v>32</v>
       </c>
       <c r="O157" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P157" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q157" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="158">
@@ -8840,7 +8810,7 @@
         <v>313</v>
       </c>
       <c r="B158" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -8867,33 +8837,29 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N158" t="s">
         <v>22</v>
       </c>
-      <c r="O158" t="n">
-        <v>7</v>
-      </c>
+      <c r="O158"/>
       <c r="P158" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q158"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>314</v>
       </c>
       <c r="B159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
@@ -8920,33 +8886,29 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N159" t="s">
         <v>22</v>
       </c>
-      <c r="O159" t="n">
-        <v>7</v>
-      </c>
+      <c r="O159"/>
       <c r="P159" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q159"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>315</v>
       </c>
       <c r="B160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -8973,26 +8935,22 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N160" t="s">
         <v>22</v>
       </c>
-      <c r="O160" t="n">
-        <v>7</v>
-      </c>
+      <c r="O160"/>
       <c r="P160" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q160"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -9026,25 +8984,25 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N161" t="s">
         <v>26</v>
       </c>
       <c r="O161" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P161" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q161" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="162">
@@ -9079,25 +9037,25 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N162" t="s">
         <v>26</v>
       </c>
       <c r="O162" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P162" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q162" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163">
@@ -9132,25 +9090,25 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N163" t="s">
         <v>26</v>
       </c>
       <c r="O163" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P163" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q163" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="164">
@@ -9185,7 +9143,7 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
@@ -9200,10 +9158,10 @@
         <v>4</v>
       </c>
       <c r="P164" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q164" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="165">
@@ -9238,7 +9196,7 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
@@ -9253,10 +9211,10 @@
         <v>4</v>
       </c>
       <c r="P165" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q165" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="166">
@@ -9291,7 +9249,7 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9306,10 +9264,10 @@
         <v>4</v>
       </c>
       <c r="P166" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q166" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="167">
@@ -9317,7 +9275,7 @@
         <v>331</v>
       </c>
       <c r="B167" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
@@ -9344,25 +9302,25 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N167" t="s">
         <v>32</v>
       </c>
       <c r="O167" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P167" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q167" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="168">
@@ -9370,7 +9328,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
@@ -9397,25 +9355,25 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N168" t="s">
         <v>32</v>
       </c>
       <c r="O168" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P168" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q168" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="169">
@@ -9423,7 +9381,7 @@
         <v>333</v>
       </c>
       <c r="B169" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
@@ -9450,25 +9408,25 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N169" t="s">
         <v>32</v>
       </c>
       <c r="O169" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P169" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q169" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="170">
@@ -9476,7 +9434,7 @@
         <v>337</v>
       </c>
       <c r="B170" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -9503,33 +9461,29 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N170" t="s">
         <v>22</v>
       </c>
-      <c r="O170" t="n">
-        <v>7</v>
-      </c>
+      <c r="O170"/>
       <c r="P170" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q170"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>338</v>
       </c>
       <c r="B171" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -9556,33 +9510,29 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N171" t="s">
         <v>22</v>
       </c>
-      <c r="O171" t="n">
-        <v>7</v>
-      </c>
+      <c r="O171"/>
       <c r="P171" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q171"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>339</v>
       </c>
       <c r="B172" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
@@ -9609,26 +9559,22 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N172" t="s">
         <v>22</v>
       </c>
-      <c r="O172" t="n">
-        <v>7</v>
-      </c>
+      <c r="O172"/>
       <c r="P172" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q172"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9662,25 +9608,25 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N173" t="s">
         <v>26</v>
       </c>
       <c r="O173" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P173" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q173" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="174">
@@ -9715,25 +9661,25 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N174" t="s">
         <v>26</v>
       </c>
       <c r="O174" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P174" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q174" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="175">
@@ -9768,25 +9714,25 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N175" t="s">
         <v>26</v>
       </c>
       <c r="O175" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P175" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q175" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="176">
@@ -9821,7 +9767,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -9836,10 +9782,10 @@
         <v>4</v>
       </c>
       <c r="P176" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q176" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="177">
@@ -9874,7 +9820,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
@@ -9889,10 +9835,10 @@
         <v>4</v>
       </c>
       <c r="P177" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q177" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="178">
@@ -9927,7 +9873,7 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
@@ -9942,10 +9888,10 @@
         <v>4</v>
       </c>
       <c r="P178" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q178" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="179">
@@ -9980,25 +9926,25 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N179" t="s">
         <v>32</v>
       </c>
       <c r="O179" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P179" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q179" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="180">
@@ -10033,25 +9979,25 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N180" t="s">
         <v>32</v>
       </c>
       <c r="O180" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P180" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q180" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="181">
@@ -10086,25 +10032,25 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N181" t="s">
         <v>32</v>
       </c>
       <c r="O181" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P181" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q181" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="182">
@@ -10112,7 +10058,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -10139,33 +10085,29 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N182" t="s">
         <v>22</v>
       </c>
-      <c r="O182" t="n">
-        <v>7</v>
-      </c>
+      <c r="O182"/>
       <c r="P182" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q182"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>362</v>
       </c>
       <c r="B183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -10192,33 +10134,29 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N183" t="s">
         <v>22</v>
       </c>
-      <c r="O183" t="n">
-        <v>7</v>
-      </c>
+      <c r="O183"/>
       <c r="P183" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q183"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>363</v>
       </c>
       <c r="B184" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -10245,26 +10183,22 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="N184" t="s">
         <v>22</v>
       </c>
-      <c r="O184" t="n">
-        <v>7</v>
-      </c>
+      <c r="O184"/>
       <c r="P184" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>160</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q184"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10298,25 +10232,25 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N185" t="s">
         <v>26</v>
       </c>
       <c r="O185" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P185" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q185" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="186">
@@ -10351,25 +10285,25 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N186" t="s">
         <v>26</v>
       </c>
       <c r="O186" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P186" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q186" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="187">
@@ -10404,25 +10338,25 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N187" t="s">
         <v>26</v>
       </c>
       <c r="O187" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P187" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q187" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="188">
@@ -10457,7 +10391,7 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
@@ -10472,10 +10406,10 @@
         <v>4</v>
       </c>
       <c r="P188" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q188" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="189">
@@ -10510,7 +10444,7 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
@@ -10525,10 +10459,10 @@
         <v>4</v>
       </c>
       <c r="P189" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q189" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="190">
@@ -10563,7 +10497,7 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
@@ -10578,10 +10512,10 @@
         <v>4</v>
       </c>
       <c r="P190" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q190" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
     </row>
     <row r="191">
@@ -10589,7 +10523,7 @@
         <v>379</v>
       </c>
       <c r="B191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191" t="s">
         <v>17</v>
@@ -10616,25 +10550,25 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N191" t="s">
         <v>32</v>
       </c>
       <c r="O191" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P191" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q191" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="192">
@@ -10642,7 +10576,7 @@
         <v>380</v>
       </c>
       <c r="B192" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" t="s">
         <v>17</v>
@@ -10669,25 +10603,25 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N192" t="s">
         <v>32</v>
       </c>
       <c r="O192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P192" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q192" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="193">
@@ -10695,7 +10629,7 @@
         <v>381</v>
       </c>
       <c r="B193" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C193" t="s">
         <v>17</v>
@@ -10722,25 +10656,25 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N193" t="s">
         <v>32</v>
       </c>
       <c r="O193" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P193" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q193" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="194">
@@ -10748,7 +10682,7 @@
         <v>385</v>
       </c>
       <c r="B194" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C194" t="s">
         <v>17</v>
@@ -10775,33 +10709,29 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="N194" t="s">
         <v>22</v>
       </c>
-      <c r="O194" t="n">
-        <v>5</v>
-      </c>
+      <c r="O194"/>
       <c r="P194" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q194"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
         <v>386</v>
       </c>
       <c r="B195" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C195" t="s">
         <v>17</v>
@@ -10828,33 +10758,29 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="N195" t="s">
         <v>22</v>
       </c>
-      <c r="O195" t="n">
-        <v>5</v>
-      </c>
+      <c r="O195"/>
       <c r="P195" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q195"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
         <v>387</v>
       </c>
       <c r="B196" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C196" t="s">
         <v>17</v>
@@ -10881,26 +10807,22 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="N196" t="s">
         <v>22</v>
       </c>
-      <c r="O196" t="n">
-        <v>5</v>
-      </c>
+      <c r="O196"/>
       <c r="P196" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q196"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10934,25 +10856,25 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N197" t="s">
         <v>26</v>
       </c>
       <c r="O197" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P197" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q197" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="198">
@@ -10987,25 +10909,25 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N198" t="s">
         <v>26</v>
       </c>
       <c r="O198" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P198" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q198" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="199">
@@ -11040,25 +10962,25 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N199" t="s">
         <v>26</v>
       </c>
       <c r="O199" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P199" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q199" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="200">
@@ -11093,13 +11015,13 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N200" t="s">
         <v>29</v>
@@ -11108,10 +11030,10 @@
         <v>3</v>
       </c>
       <c r="P200" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q200" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="201">
@@ -11146,13 +11068,13 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N201" t="s">
         <v>29</v>
@@ -11161,10 +11083,10 @@
         <v>3</v>
       </c>
       <c r="P201" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q201" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="202">
@@ -11199,13 +11121,13 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N202" t="s">
         <v>29</v>
@@ -11214,10 +11136,10 @@
         <v>3</v>
       </c>
       <c r="P202" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q202" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="203">
@@ -11252,25 +11174,25 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N203" t="s">
         <v>32</v>
       </c>
       <c r="O203" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P203" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q203" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="204">
@@ -11305,25 +11227,25 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N204" t="s">
         <v>32</v>
       </c>
       <c r="O204" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P204" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q204" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="205">
@@ -11358,25 +11280,25 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N205" t="s">
         <v>32</v>
       </c>
       <c r="O205" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P205" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q205" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="206">
@@ -11384,7 +11306,7 @@
         <v>409</v>
       </c>
       <c r="B206" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" t="s">
         <v>17</v>
@@ -11411,33 +11333,29 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="N206" t="s">
         <v>22</v>
       </c>
-      <c r="O206" t="n">
-        <v>5</v>
-      </c>
+      <c r="O206"/>
       <c r="P206" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q206"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>410</v>
       </c>
       <c r="B207" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C207" t="s">
         <v>17</v>
@@ -11464,33 +11382,29 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="N207" t="s">
         <v>22</v>
       </c>
-      <c r="O207" t="n">
-        <v>5</v>
-      </c>
+      <c r="O207"/>
       <c r="P207" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q207"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>411</v>
       </c>
       <c r="B208" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C208" t="s">
         <v>17</v>
@@ -11517,26 +11431,22 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="N208" t="s">
         <v>22</v>
       </c>
-      <c r="O208" t="n">
-        <v>5</v>
-      </c>
+      <c r="O208"/>
       <c r="P208" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>140</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="Q208"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11570,25 +11480,25 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N209" t="s">
         <v>26</v>
       </c>
       <c r="O209" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P209" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q209" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="210">
@@ -11623,25 +11533,25 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N210" t="s">
         <v>26</v>
       </c>
       <c r="O210" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P210" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q210" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="211">
@@ -11676,25 +11586,25 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="N211" t="s">
         <v>26</v>
       </c>
       <c r="O211" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P211" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Q211" t="n">
-        <v>133</v>
+        <v>60</v>
       </c>
     </row>
     <row r="212">
@@ -11702,7 +11612,7 @@
         <v>421</v>
       </c>
       <c r="B212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C212" t="s">
         <v>17</v>
@@ -11729,13 +11639,13 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N212" t="s">
         <v>29</v>
@@ -11744,10 +11654,10 @@
         <v>3</v>
       </c>
       <c r="P212" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q212" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="213">
@@ -11755,7 +11665,7 @@
         <v>422</v>
       </c>
       <c r="B213" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C213" t="s">
         <v>17</v>
@@ -11782,13 +11692,13 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N213" t="s">
         <v>29</v>
@@ -11797,10 +11707,10 @@
         <v>3</v>
       </c>
       <c r="P213" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q213" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="214">
@@ -11808,7 +11718,7 @@
         <v>423</v>
       </c>
       <c r="B214" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C214" t="s">
         <v>17</v>
@@ -11835,13 +11745,13 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="N214" t="s">
         <v>29</v>
@@ -11850,10 +11760,10 @@
         <v>3</v>
       </c>
       <c r="P214" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q214" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="215">
@@ -11861,7 +11771,7 @@
         <v>427</v>
       </c>
       <c r="B215" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C215" t="s">
         <v>17</v>
@@ -11888,25 +11798,25 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N215" t="s">
         <v>32</v>
       </c>
       <c r="O215" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P215" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q215" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="216">
@@ -11914,7 +11824,7 @@
         <v>428</v>
       </c>
       <c r="B216" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C216" t="s">
         <v>17</v>
@@ -11941,25 +11851,25 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N216" t="s">
         <v>32</v>
       </c>
       <c r="O216" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P216" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q216" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
     <row r="217">
@@ -11967,7 +11877,7 @@
         <v>429</v>
       </c>
       <c r="B217" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C217" t="s">
         <v>17</v>
@@ -11994,25 +11904,25 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="N217" t="s">
         <v>32</v>
       </c>
       <c r="O217" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P217" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q217" t="n">
-        <v>459</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">c(74, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2050, 2051, 2052, 2053)</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e19", "e34", "e398", "e427", "e460")</t>
+    <t xml:space="preserve">c("e12", "e15", "e19", "e34", "e369", "e398", "e427", "e460", "e505")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 183, 184, 185, 186, 1890, 1891, 1892)</t>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e20", "e31", "e48", "e428")</t>
+    <t xml:space="preserve">c("e20", "e31", "e48", "e388", "e428", "e452")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1832, 1833, 1834, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">c("e407", "e408", "e445", "e476")</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 2321, 2322, 2323)</t>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e26", "e27", "e28", "e29", "e364", "e519")</t>
+    <t xml:space="preserve">c("e26", "e27", "e28", "e29", "e364", "e372", "e493", "e514", "e519")</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
@@ -134,40 +134,52 @@
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 122, 123, 124, 125, 1890, 1891, 1892)</t>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + NDF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 2321, 2322, 2323)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
   </si>
   <si>
     <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
 </sst>
 </file>
@@ -593,13 +605,13 @@
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q2" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3">
@@ -646,13 +658,13 @@
         <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
@@ -699,13 +711,13 @@
         <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P4" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5">
@@ -752,13 +764,13 @@
         <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q5" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6">
@@ -805,13 +817,13 @@
         <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7">
@@ -858,13 +870,13 @@
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8">
@@ -914,10 +926,10 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q8" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9">
@@ -967,10 +979,10 @@
         <v>4</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q9" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -1020,10 +1032,10 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q10" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -1070,13 +1082,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q11" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12">
@@ -1123,13 +1135,13 @@
         <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q12" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13">
@@ -1176,13 +1188,13 @@
         <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P13" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="14">
@@ -1229,13 +1241,13 @@
         <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P14" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q14" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15">
@@ -1282,13 +1294,13 @@
         <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P15" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16">
@@ -1335,13 +1347,13 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17">
@@ -1388,13 +1400,13 @@
         <v>26</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P17" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q17" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18">
@@ -1441,13 +1453,13 @@
         <v>26</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
@@ -1494,13 +1506,13 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20">
@@ -1550,10 +1562,10 @@
         <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q20" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
@@ -1603,10 +1615,10 @@
         <v>4</v>
       </c>
       <c r="P21" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q21" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="22">
@@ -1656,10 +1668,10 @@
         <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q22" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23">
@@ -1706,13 +1718,13 @@
         <v>32</v>
       </c>
       <c r="O23" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P23" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q23" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="24">
@@ -1759,13 +1771,13 @@
         <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P24" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q24" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="25">
@@ -1812,13 +1824,13 @@
         <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P25" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q25" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="26">
@@ -1865,13 +1877,13 @@
         <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P26" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27">
@@ -1918,13 +1930,13 @@
         <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P27" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28">
@@ -1971,13 +1983,13 @@
         <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P28" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29">
@@ -2024,13 +2036,13 @@
         <v>26</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P29" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q29" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
@@ -2077,13 +2089,13 @@
         <v>26</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P30" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q30" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31">
@@ -2130,13 +2142,13 @@
         <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P31" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q31" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32">
@@ -2186,10 +2198,10 @@
         <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q32" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33">
@@ -2239,10 +2251,10 @@
         <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34">
@@ -2292,10 +2304,10 @@
         <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q34" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35">
@@ -2342,13 +2354,13 @@
         <v>32</v>
       </c>
       <c r="O35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P35" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q35" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="36">
@@ -2395,13 +2407,13 @@
         <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P36" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q36" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="37">
@@ -2448,13 +2460,13 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P37" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q37" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="38">
@@ -2501,13 +2513,13 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P38" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q38" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39">
@@ -2554,13 +2566,13 @@
         <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P39" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q39" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40">
@@ -2607,13 +2619,13 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P40" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q40" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41">
@@ -2660,13 +2672,13 @@
         <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P41" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q41" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="42">
@@ -2713,13 +2725,13 @@
         <v>26</v>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P42" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="43">
@@ -2766,13 +2778,13 @@
         <v>26</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P43" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q43" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="44">
@@ -2822,10 +2834,10 @@
         <v>4</v>
       </c>
       <c r="P44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q44" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45">
@@ -2875,10 +2887,10 @@
         <v>4</v>
       </c>
       <c r="P45" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q45" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="46">
@@ -2928,10 +2940,10 @@
         <v>4</v>
       </c>
       <c r="P46" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q46" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="47">
@@ -2978,13 +2990,13 @@
         <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P47" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q47" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="48">
@@ -3031,13 +3043,13 @@
         <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P48" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q48" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="49">
@@ -3084,13 +3096,13 @@
         <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P49" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q49" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="50">
@@ -3137,13 +3149,13 @@
         <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P50" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q50" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="51">
@@ -3190,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P51" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q51" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="52">
@@ -3243,13 +3255,13 @@
         <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P52" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q52" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53">
@@ -3296,13 +3308,13 @@
         <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P53" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q53" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54">
@@ -3349,13 +3361,13 @@
         <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P54" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q54" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55">
@@ -3402,13 +3414,13 @@
         <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P55" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q55" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="56">
@@ -3458,10 +3470,10 @@
         <v>4</v>
       </c>
       <c r="P56" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q56" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
@@ -3511,10 +3523,10 @@
         <v>4</v>
       </c>
       <c r="P57" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q57" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58">
@@ -3564,10 +3576,10 @@
         <v>4</v>
       </c>
       <c r="P58" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q58" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59">
@@ -3614,13 +3626,13 @@
         <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P59" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q59" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="60">
@@ -3667,13 +3679,13 @@
         <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P60" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q60" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="61">
@@ -3720,13 +3732,13 @@
         <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P61" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q61" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="62">
@@ -3773,13 +3785,13 @@
         <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P62" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q62" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="63">
@@ -3826,13 +3838,13 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P63" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q63" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64">
@@ -3879,13 +3891,13 @@
         <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P64" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q64" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65">
@@ -3932,13 +3944,13 @@
         <v>26</v>
       </c>
       <c r="O65" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P65" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q65" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66">
@@ -3985,13 +3997,13 @@
         <v>26</v>
       </c>
       <c r="O66" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P66" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q66" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="67">
@@ -4038,13 +4050,13 @@
         <v>26</v>
       </c>
       <c r="O67" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P67" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q67" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68">
@@ -4094,10 +4106,10 @@
         <v>4</v>
       </c>
       <c r="P68" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q68" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69">
@@ -4147,10 +4159,10 @@
         <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q69" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="70">
@@ -4200,10 +4212,10 @@
         <v>4</v>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q70" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="71">
@@ -4250,13 +4262,13 @@
         <v>32</v>
       </c>
       <c r="O71" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P71" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q71" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="72">
@@ -4303,13 +4315,13 @@
         <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P72" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q72" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="73">
@@ -4356,13 +4368,13 @@
         <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P73" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q73" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="74">
@@ -4409,13 +4421,13 @@
         <v>22</v>
       </c>
       <c r="O74" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P74" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q74" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="75">
@@ -4462,13 +4474,13 @@
         <v>22</v>
       </c>
       <c r="O75" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P75" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q75" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76">
@@ -4515,13 +4527,13 @@
         <v>22</v>
       </c>
       <c r="O76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P76" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q76" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="77">
@@ -4568,13 +4580,13 @@
         <v>26</v>
       </c>
       <c r="O77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P77" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q77" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78">
@@ -4621,13 +4633,13 @@
         <v>26</v>
       </c>
       <c r="O78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P78" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q78" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79">
@@ -4674,13 +4686,13 @@
         <v>26</v>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P79" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q79" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80">
@@ -4730,10 +4742,10 @@
         <v>4</v>
       </c>
       <c r="P80" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q80" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="81">
@@ -4783,10 +4795,10 @@
         <v>4</v>
       </c>
       <c r="P81" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q81" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="82">
@@ -4836,10 +4848,10 @@
         <v>4</v>
       </c>
       <c r="P82" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q82" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="83">
@@ -4886,13 +4898,13 @@
         <v>32</v>
       </c>
       <c r="O83" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P83" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q83" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="84">
@@ -4939,13 +4951,13 @@
         <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P84" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q84" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="85">
@@ -4992,13 +5004,13 @@
         <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P85" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q85" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="86">
@@ -5045,13 +5057,13 @@
         <v>22</v>
       </c>
       <c r="O86" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P86" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q86" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="87">
@@ -5098,13 +5110,13 @@
         <v>22</v>
       </c>
       <c r="O87" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P87" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q87" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="88">
@@ -5151,13 +5163,13 @@
         <v>22</v>
       </c>
       <c r="O88" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P88" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q88" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="89">
@@ -5204,13 +5216,13 @@
         <v>26</v>
       </c>
       <c r="O89" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q89" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90">
@@ -5257,13 +5269,13 @@
         <v>26</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P90" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q90" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
@@ -5310,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="O91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P91" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q91" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92">
@@ -5366,10 +5378,10 @@
         <v>4</v>
       </c>
       <c r="P92" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q92" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="93">
@@ -5419,10 +5431,10 @@
         <v>4</v>
       </c>
       <c r="P93" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q93" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="94">
@@ -5472,10 +5484,10 @@
         <v>4</v>
       </c>
       <c r="P94" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q94" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="95">
@@ -5522,13 +5534,13 @@
         <v>32</v>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P95" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q95" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="96">
@@ -5575,13 +5587,13 @@
         <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P96" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q96" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="97">
@@ -5628,13 +5640,13 @@
         <v>32</v>
       </c>
       <c r="O97" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P97" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q97" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="98">
@@ -5681,13 +5693,13 @@
         <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P98" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q98" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="99">
@@ -5734,13 +5746,13 @@
         <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P99" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q99" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="100">
@@ -5787,13 +5799,13 @@
         <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P100" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q100" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="101">
@@ -5840,13 +5852,13 @@
         <v>26</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P101" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q101" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="102">
@@ -5893,13 +5905,13 @@
         <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P102" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q102" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="103">
@@ -5946,13 +5958,13 @@
         <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P103" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q103" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="104">
@@ -6002,10 +6014,10 @@
         <v>4</v>
       </c>
       <c r="P104" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q104" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105">
@@ -6055,10 +6067,10 @@
         <v>4</v>
       </c>
       <c r="P105" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q105" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106">
@@ -6108,10 +6120,10 @@
         <v>4</v>
       </c>
       <c r="P106" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q106" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107">
@@ -6158,13 +6170,13 @@
         <v>32</v>
       </c>
       <c r="O107" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P107" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q107" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="108">
@@ -6211,13 +6223,13 @@
         <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P108" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q108" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="109">
@@ -6264,13 +6276,13 @@
         <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P109" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q109" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="110">
@@ -6317,13 +6329,13 @@
         <v>22</v>
       </c>
       <c r="O110" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P110" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q110" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="111">
@@ -6370,13 +6382,13 @@
         <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P111" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q111" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="112">
@@ -6423,13 +6435,13 @@
         <v>22</v>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P112" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="Q112" t="n">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="113">
@@ -6476,13 +6488,13 @@
         <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P113" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q113" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="114">
@@ -6529,13 +6541,13 @@
         <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P114" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q114" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="115">
@@ -6582,13 +6594,13 @@
         <v>26</v>
       </c>
       <c r="O115" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P115" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q115" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="116">
@@ -6638,10 +6650,10 @@
         <v>4</v>
       </c>
       <c r="P116" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q116" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="117">
@@ -6691,10 +6703,10 @@
         <v>4</v>
       </c>
       <c r="P117" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q117" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="118">
@@ -6744,10 +6756,10 @@
         <v>4</v>
       </c>
       <c r="P118" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q118" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="119">
@@ -6794,13 +6806,13 @@
         <v>32</v>
       </c>
       <c r="O119" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P119" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q119" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="120">
@@ -6847,13 +6859,13 @@
         <v>32</v>
       </c>
       <c r="O120" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P120" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q120" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="121">
@@ -6900,13 +6912,13 @@
         <v>32</v>
       </c>
       <c r="O121" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P121" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q121" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="122">
@@ -6947,19 +6959,19 @@
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P122" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q122" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="123">
@@ -7000,19 +7012,19 @@
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P123" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q123" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="124">
@@ -7053,19 +7065,19 @@
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q124" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="125">
@@ -7100,7 +7112,7 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
@@ -7112,13 +7124,13 @@
         <v>26</v>
       </c>
       <c r="O125" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P125" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q125" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="126">
@@ -7153,7 +7165,7 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
@@ -7165,13 +7177,13 @@
         <v>26</v>
       </c>
       <c r="O126" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P126" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q126" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="127">
@@ -7206,7 +7218,7 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7218,13 +7230,13 @@
         <v>26</v>
       </c>
       <c r="O127" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P127" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q127" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="128">
@@ -7265,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
@@ -7274,10 +7286,10 @@
         <v>3</v>
       </c>
       <c r="P128" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q128" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="129">
@@ -7318,7 +7330,7 @@
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
@@ -7327,10 +7339,10 @@
         <v>3</v>
       </c>
       <c r="P129" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q129" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="130">
@@ -7371,7 +7383,7 @@
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
@@ -7380,10 +7392,10 @@
         <v>3</v>
       </c>
       <c r="P130" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q130" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131">
@@ -7418,7 +7430,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -7430,13 +7442,13 @@
         <v>32</v>
       </c>
       <c r="O131" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P131" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q131" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="132">
@@ -7471,7 +7483,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
@@ -7483,13 +7495,13 @@
         <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P132" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q132" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="133">
@@ -7524,7 +7536,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7536,13 +7548,13 @@
         <v>32</v>
       </c>
       <c r="O133" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P133" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q133" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="134">
@@ -7583,19 +7595,19 @@
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P134" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q134" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="135">
@@ -7636,19 +7648,19 @@
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q135" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="136">
@@ -7689,19 +7701,19 @@
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P136" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="Q136" t="n">
-        <v>237</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137">
@@ -7736,7 +7748,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
@@ -7748,13 +7760,13 @@
         <v>26</v>
       </c>
       <c r="O137" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P137" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q137" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="138">
@@ -7789,7 +7801,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
@@ -7801,13 +7813,13 @@
         <v>26</v>
       </c>
       <c r="O138" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P138" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q138" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="139">
@@ -7842,7 +7854,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
@@ -7854,13 +7866,13 @@
         <v>26</v>
       </c>
       <c r="O139" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P139" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Q139" t="n">
-        <v>100</v>
+        <v>173</v>
       </c>
     </row>
     <row r="140">
@@ -7868,7 +7880,7 @@
         <v>277</v>
       </c>
       <c r="B140" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C140" t="s">
         <v>17</v>
@@ -7901,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
@@ -7910,10 +7922,10 @@
         <v>3</v>
       </c>
       <c r="P140" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q140" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="141">
@@ -7921,7 +7933,7 @@
         <v>278</v>
       </c>
       <c r="B141" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141" t="s">
         <v>17</v>
@@ -7954,7 +7966,7 @@
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
@@ -7963,10 +7975,10 @@
         <v>3</v>
       </c>
       <c r="P141" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q141" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142">
@@ -7974,7 +7986,7 @@
         <v>279</v>
       </c>
       <c r="B142" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142" t="s">
         <v>17</v>
@@ -8007,7 +8019,7 @@
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
@@ -8016,10 +8028,10 @@
         <v>3</v>
       </c>
       <c r="P142" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q142" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="143">
@@ -8054,7 +8066,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
@@ -8066,13 +8078,13 @@
         <v>32</v>
       </c>
       <c r="O143" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P143" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q143" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="144">
@@ -8107,7 +8119,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
@@ -8119,13 +8131,13 @@
         <v>32</v>
       </c>
       <c r="O144" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P144" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q144" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="145">
@@ -8160,7 +8172,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -8172,13 +8184,13 @@
         <v>32</v>
       </c>
       <c r="O145" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P145" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="Q145" t="n">
-        <v>263</v>
+        <v>633</v>
       </c>
     </row>
     <row r="146">
@@ -8186,7 +8198,7 @@
         <v>289</v>
       </c>
       <c r="B146" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -8213,29 +8225,33 @@
         <v>3</v>
       </c>
       <c r="K146" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L146" t="n">
         <v>1</v>
       </c>
       <c r="M146" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N146" t="s">
         <v>22</v>
       </c>
-      <c r="O146"/>
+      <c r="O146" t="n">
+        <v>7</v>
+      </c>
       <c r="P146" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q146"/>
+        <v>17</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
         <v>290</v>
       </c>
       <c r="B147" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -8262,29 +8278,33 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L147" t="n">
         <v>2</v>
       </c>
       <c r="M147" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N147" t="s">
         <v>22</v>
       </c>
-      <c r="O147"/>
+      <c r="O147" t="n">
+        <v>7</v>
+      </c>
       <c r="P147" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q147"/>
+        <v>17</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
         <v>291</v>
       </c>
       <c r="B148" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -8311,22 +8331,26 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L148" t="n">
         <v>3</v>
       </c>
       <c r="M148" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N148" t="s">
         <v>22</v>
       </c>
-      <c r="O148"/>
+      <c r="O148" t="n">
+        <v>7</v>
+      </c>
       <c r="P148" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q148"/>
+        <v>17</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8360,25 +8384,25 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L149" t="n">
         <v>1</v>
       </c>
       <c r="M149" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N149" t="s">
         <v>26</v>
       </c>
       <c r="O149" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P149" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q149" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="150">
@@ -8413,25 +8437,25 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L150" t="n">
         <v>2</v>
       </c>
       <c r="M150" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N150" t="s">
         <v>26</v>
       </c>
       <c r="O150" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P150" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q150" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="151">
@@ -8466,25 +8490,25 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L151" t="n">
         <v>3</v>
       </c>
       <c r="M151" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N151" t="s">
         <v>26</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P151" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q151" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="152">
@@ -8519,7 +8543,7 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L152" t="n">
         <v>1</v>
@@ -8534,10 +8558,10 @@
         <v>4</v>
       </c>
       <c r="P152" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q152" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="153">
@@ -8572,7 +8596,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L153" t="n">
         <v>2</v>
@@ -8587,10 +8611,10 @@
         <v>4</v>
       </c>
       <c r="P153" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q153" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="154">
@@ -8625,7 +8649,7 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L154" t="n">
         <v>3</v>
@@ -8640,10 +8664,10 @@
         <v>4</v>
       </c>
       <c r="P154" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q154" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="155">
@@ -8678,25 +8702,25 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L155" t="n">
         <v>1</v>
       </c>
       <c r="M155" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N155" t="s">
         <v>32</v>
       </c>
       <c r="O155" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P155" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q155" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="156">
@@ -8731,25 +8755,25 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L156" t="n">
         <v>2</v>
       </c>
       <c r="M156" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N156" t="s">
         <v>32</v>
       </c>
       <c r="O156" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P156" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q156" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="157">
@@ -8784,25 +8808,25 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L157" t="n">
         <v>3</v>
       </c>
       <c r="M157" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N157" t="s">
         <v>32</v>
       </c>
       <c r="O157" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P157" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q157" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="158">
@@ -8810,7 +8834,7 @@
         <v>313</v>
       </c>
       <c r="B158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C158" t="s">
         <v>17</v>
@@ -8837,29 +8861,33 @@
         <v>3</v>
       </c>
       <c r="K158" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L158" t="n">
         <v>1</v>
       </c>
       <c r="M158" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N158" t="s">
         <v>22</v>
       </c>
-      <c r="O158"/>
+      <c r="O158" t="n">
+        <v>7</v>
+      </c>
       <c r="P158" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q158"/>
+        <v>17</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
         <v>314</v>
       </c>
       <c r="B159" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C159" t="s">
         <v>17</v>
@@ -8886,29 +8914,33 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L159" t="n">
         <v>2</v>
       </c>
       <c r="M159" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N159" t="s">
         <v>22</v>
       </c>
-      <c r="O159"/>
+      <c r="O159" t="n">
+        <v>7</v>
+      </c>
       <c r="P159" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q159"/>
+        <v>17</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
         <v>315</v>
       </c>
       <c r="B160" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C160" t="s">
         <v>17</v>
@@ -8935,22 +8967,26 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L160" t="n">
         <v>3</v>
       </c>
       <c r="M160" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N160" t="s">
         <v>22</v>
       </c>
-      <c r="O160"/>
+      <c r="O160" t="n">
+        <v>7</v>
+      </c>
       <c r="P160" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q160"/>
+        <v>17</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -8984,25 +9020,25 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
       </c>
       <c r="M161" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N161" t="s">
         <v>26</v>
       </c>
       <c r="O161" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P161" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q161" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="162">
@@ -9037,25 +9073,25 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L162" t="n">
         <v>2</v>
       </c>
       <c r="M162" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N162" t="s">
         <v>26</v>
       </c>
       <c r="O162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P162" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q162" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="163">
@@ -9090,25 +9126,25 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L163" t="n">
         <v>3</v>
       </c>
       <c r="M163" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N163" t="s">
         <v>26</v>
       </c>
       <c r="O163" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P163" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q163" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="164">
@@ -9143,7 +9179,7 @@
         <v>3</v>
       </c>
       <c r="K164" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
@@ -9158,10 +9194,10 @@
         <v>4</v>
       </c>
       <c r="P164" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q164" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="165">
@@ -9196,7 +9232,7 @@
         <v>3</v>
       </c>
       <c r="K165" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L165" t="n">
         <v>2</v>
@@ -9211,10 +9247,10 @@
         <v>4</v>
       </c>
       <c r="P165" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q165" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="166">
@@ -9249,7 +9285,7 @@
         <v>3</v>
       </c>
       <c r="K166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L166" t="n">
         <v>3</v>
@@ -9264,10 +9300,10 @@
         <v>4</v>
       </c>
       <c r="P166" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q166" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="167">
@@ -9275,7 +9311,7 @@
         <v>331</v>
       </c>
       <c r="B167" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C167" t="s">
         <v>17</v>
@@ -9302,25 +9338,25 @@
         <v>3</v>
       </c>
       <c r="K167" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L167" t="n">
         <v>1</v>
       </c>
       <c r="M167" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N167" t="s">
         <v>32</v>
       </c>
       <c r="O167" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P167" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q167" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="168">
@@ -9328,7 +9364,7 @@
         <v>332</v>
       </c>
       <c r="B168" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C168" t="s">
         <v>17</v>
@@ -9355,25 +9391,25 @@
         <v>3</v>
       </c>
       <c r="K168" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L168" t="n">
         <v>2</v>
       </c>
       <c r="M168" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N168" t="s">
         <v>32</v>
       </c>
       <c r="O168" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P168" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q168" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="169">
@@ -9381,7 +9417,7 @@
         <v>333</v>
       </c>
       <c r="B169" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169" t="s">
         <v>17</v>
@@ -9408,25 +9444,25 @@
         <v>3</v>
       </c>
       <c r="K169" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L169" t="n">
         <v>3</v>
       </c>
       <c r="M169" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N169" t="s">
         <v>32</v>
       </c>
       <c r="O169" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P169" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q169" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="170">
@@ -9434,7 +9470,7 @@
         <v>337</v>
       </c>
       <c r="B170" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170" t="s">
         <v>17</v>
@@ -9461,29 +9497,33 @@
         <v>3</v>
       </c>
       <c r="K170" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L170" t="n">
         <v>1</v>
       </c>
       <c r="M170" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N170" t="s">
         <v>22</v>
       </c>
-      <c r="O170"/>
+      <c r="O170" t="n">
+        <v>7</v>
+      </c>
       <c r="P170" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q170"/>
+        <v>17</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
         <v>338</v>
       </c>
       <c r="B171" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" t="s">
         <v>17</v>
@@ -9510,29 +9550,33 @@
         <v>3</v>
       </c>
       <c r="K171" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L171" t="n">
         <v>2</v>
       </c>
       <c r="M171" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N171" t="s">
         <v>22</v>
       </c>
-      <c r="O171"/>
+      <c r="O171" t="n">
+        <v>7</v>
+      </c>
       <c r="P171" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q171"/>
+        <v>17</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
         <v>339</v>
       </c>
       <c r="B172" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172" t="s">
         <v>17</v>
@@ -9559,22 +9603,26 @@
         <v>3</v>
       </c>
       <c r="K172" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L172" t="n">
         <v>3</v>
       </c>
       <c r="M172" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N172" t="s">
         <v>22</v>
       </c>
-      <c r="O172"/>
+      <c r="O172" t="n">
+        <v>7</v>
+      </c>
       <c r="P172" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q172"/>
+        <v>17</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -9608,25 +9656,25 @@
         <v>3</v>
       </c>
       <c r="K173" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L173" t="n">
         <v>1</v>
       </c>
       <c r="M173" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N173" t="s">
         <v>26</v>
       </c>
       <c r="O173" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P173" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q173" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="174">
@@ -9661,25 +9709,25 @@
         <v>3</v>
       </c>
       <c r="K174" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L174" t="n">
         <v>2</v>
       </c>
       <c r="M174" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N174" t="s">
         <v>26</v>
       </c>
       <c r="O174" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P174" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q174" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="175">
@@ -9714,25 +9762,25 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L175" t="n">
         <v>3</v>
       </c>
       <c r="M175" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N175" t="s">
         <v>26</v>
       </c>
       <c r="O175" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P175" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q175" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="176">
@@ -9767,7 +9815,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -9782,10 +9830,10 @@
         <v>4</v>
       </c>
       <c r="P176" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q176" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="177">
@@ -9820,7 +9868,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L177" t="n">
         <v>2</v>
@@ -9835,10 +9883,10 @@
         <v>4</v>
       </c>
       <c r="P177" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q177" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178">
@@ -9873,7 +9921,7 @@
         <v>3</v>
       </c>
       <c r="K178" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L178" t="n">
         <v>3</v>
@@ -9888,10 +9936,10 @@
         <v>4</v>
       </c>
       <c r="P178" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q178" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="179">
@@ -9926,25 +9974,25 @@
         <v>3</v>
       </c>
       <c r="K179" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L179" t="n">
         <v>1</v>
       </c>
       <c r="M179" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N179" t="s">
         <v>32</v>
       </c>
       <c r="O179" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P179" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q179" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="180">
@@ -9979,25 +10027,25 @@
         <v>3</v>
       </c>
       <c r="K180" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L180" t="n">
         <v>2</v>
       </c>
       <c r="M180" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N180" t="s">
         <v>32</v>
       </c>
       <c r="O180" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P180" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q180" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="181">
@@ -10032,25 +10080,25 @@
         <v>3</v>
       </c>
       <c r="K181" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L181" t="n">
         <v>3</v>
       </c>
       <c r="M181" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N181" t="s">
         <v>32</v>
       </c>
       <c r="O181" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P181" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q181" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182">
@@ -10058,7 +10106,7 @@
         <v>361</v>
       </c>
       <c r="B182" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C182" t="s">
         <v>17</v>
@@ -10085,29 +10133,33 @@
         <v>3</v>
       </c>
       <c r="K182" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N182" t="s">
         <v>22</v>
       </c>
-      <c r="O182"/>
+      <c r="O182" t="n">
+        <v>7</v>
+      </c>
       <c r="P182" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q182"/>
+        <v>17</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
         <v>362</v>
       </c>
       <c r="B183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C183" t="s">
         <v>17</v>
@@ -10134,29 +10186,33 @@
         <v>3</v>
       </c>
       <c r="K183" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L183" t="n">
         <v>2</v>
       </c>
       <c r="M183" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N183" t="s">
         <v>22</v>
       </c>
-      <c r="O183"/>
+      <c r="O183" t="n">
+        <v>7</v>
+      </c>
       <c r="P183" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q183"/>
+        <v>17</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
         <v>363</v>
       </c>
       <c r="B184" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C184" t="s">
         <v>17</v>
@@ -10183,22 +10239,26 @@
         <v>3</v>
       </c>
       <c r="K184" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L184" t="n">
         <v>3</v>
       </c>
       <c r="M184" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="N184" t="s">
         <v>22</v>
       </c>
-      <c r="O184"/>
+      <c r="O184" t="n">
+        <v>7</v>
+      </c>
       <c r="P184" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q184"/>
+        <v>17</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -10232,25 +10292,25 @@
         <v>3</v>
       </c>
       <c r="K185" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L185" t="n">
         <v>1</v>
       </c>
       <c r="M185" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N185" t="s">
         <v>26</v>
       </c>
       <c r="O185" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P185" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q185" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="186">
@@ -10285,25 +10345,25 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L186" t="n">
         <v>2</v>
       </c>
       <c r="M186" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N186" t="s">
         <v>26</v>
       </c>
       <c r="O186" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P186" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q186" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="187">
@@ -10338,25 +10398,25 @@
         <v>3</v>
       </c>
       <c r="K187" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L187" t="n">
         <v>3</v>
       </c>
       <c r="M187" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N187" t="s">
         <v>26</v>
       </c>
       <c r="O187" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P187" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q187" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="188">
@@ -10391,7 +10451,7 @@
         <v>3</v>
       </c>
       <c r="K188" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
@@ -10406,10 +10466,10 @@
         <v>4</v>
       </c>
       <c r="P188" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q188" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="189">
@@ -10444,7 +10504,7 @@
         <v>3</v>
       </c>
       <c r="K189" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L189" t="n">
         <v>2</v>
@@ -10459,10 +10519,10 @@
         <v>4</v>
       </c>
       <c r="P189" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q189" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="190">
@@ -10497,7 +10557,7 @@
         <v>3</v>
       </c>
       <c r="K190" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="L190" t="n">
         <v>3</v>
@@ -10512,10 +10572,10 @@
         <v>4</v>
       </c>
       <c r="P190" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q190" t="n">
-        <v>73</v>
+        <v>106</v>
       </c>
     </row>
     <row r="191">
@@ -10523,7 +10583,7 @@
         <v>379</v>
       </c>
       <c r="B191" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191" t="s">
         <v>17</v>
@@ -10550,25 +10610,25 @@
         <v>3</v>
       </c>
       <c r="K191" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L191" t="n">
         <v>1</v>
       </c>
       <c r="M191" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N191" t="s">
         <v>32</v>
       </c>
       <c r="O191" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P191" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q191" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="192">
@@ -10576,7 +10636,7 @@
         <v>380</v>
       </c>
       <c r="B192" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" t="s">
         <v>17</v>
@@ -10603,25 +10663,25 @@
         <v>3</v>
       </c>
       <c r="K192" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L192" t="n">
         <v>2</v>
       </c>
       <c r="M192" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N192" t="s">
         <v>32</v>
       </c>
       <c r="O192" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P192" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q192" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193">
@@ -10629,7 +10689,7 @@
         <v>381</v>
       </c>
       <c r="B193" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C193" t="s">
         <v>17</v>
@@ -10656,25 +10716,25 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L193" t="n">
         <v>3</v>
       </c>
       <c r="M193" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N193" t="s">
         <v>32</v>
       </c>
       <c r="O193" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P193" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q193" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194">
@@ -10682,7 +10742,7 @@
         <v>385</v>
       </c>
       <c r="B194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C194" t="s">
         <v>17</v>
@@ -10709,29 +10769,33 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
       </c>
       <c r="M194" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N194" t="s">
         <v>22</v>
       </c>
-      <c r="O194"/>
+      <c r="O194" t="n">
+        <v>5</v>
+      </c>
       <c r="P194" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q194"/>
+        <v>15</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
         <v>386</v>
       </c>
       <c r="B195" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C195" t="s">
         <v>17</v>
@@ -10758,29 +10822,33 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L195" t="n">
         <v>2</v>
       </c>
       <c r="M195" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N195" t="s">
         <v>22</v>
       </c>
-      <c r="O195"/>
+      <c r="O195" t="n">
+        <v>5</v>
+      </c>
       <c r="P195" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q195"/>
+        <v>15</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
         <v>387</v>
       </c>
       <c r="B196" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C196" t="s">
         <v>17</v>
@@ -10807,22 +10875,26 @@
         <v>3</v>
       </c>
       <c r="K196" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L196" t="n">
         <v>3</v>
       </c>
       <c r="M196" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N196" t="s">
         <v>22</v>
       </c>
-      <c r="O196"/>
+      <c r="O196" t="n">
+        <v>5</v>
+      </c>
       <c r="P196" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q196"/>
+        <v>15</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -10856,25 +10928,25 @@
         <v>3</v>
       </c>
       <c r="K197" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L197" t="n">
         <v>1</v>
       </c>
       <c r="M197" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N197" t="s">
         <v>26</v>
       </c>
       <c r="O197" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P197" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q197" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="198">
@@ -10909,25 +10981,25 @@
         <v>3</v>
       </c>
       <c r="K198" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L198" t="n">
         <v>2</v>
       </c>
       <c r="M198" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N198" t="s">
         <v>26</v>
       </c>
       <c r="O198" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P198" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q198" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="199">
@@ -10962,25 +11034,25 @@
         <v>3</v>
       </c>
       <c r="K199" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L199" t="n">
         <v>3</v>
       </c>
       <c r="M199" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N199" t="s">
         <v>26</v>
       </c>
       <c r="O199" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P199" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q199" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="200">
@@ -11015,13 +11087,13 @@
         <v>3</v>
       </c>
       <c r="K200" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L200" t="n">
         <v>1</v>
       </c>
       <c r="M200" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N200" t="s">
         <v>29</v>
@@ -11030,10 +11102,10 @@
         <v>3</v>
       </c>
       <c r="P200" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q200" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="201">
@@ -11068,13 +11140,13 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L201" t="n">
         <v>2</v>
       </c>
       <c r="M201" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N201" t="s">
         <v>29</v>
@@ -11083,10 +11155,10 @@
         <v>3</v>
       </c>
       <c r="P201" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q201" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="202">
@@ -11121,13 +11193,13 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L202" t="n">
         <v>3</v>
       </c>
       <c r="M202" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N202" t="s">
         <v>29</v>
@@ -11136,10 +11208,10 @@
         <v>3</v>
       </c>
       <c r="P202" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q202" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="203">
@@ -11174,25 +11246,25 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L203" t="n">
         <v>1</v>
       </c>
       <c r="M203" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N203" t="s">
         <v>32</v>
       </c>
       <c r="O203" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P203" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q203" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="204">
@@ -11227,25 +11299,25 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L204" t="n">
         <v>2</v>
       </c>
       <c r="M204" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N204" t="s">
         <v>32</v>
       </c>
       <c r="O204" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P204" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q204" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="205">
@@ -11280,25 +11352,25 @@
         <v>3</v>
       </c>
       <c r="K205" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L205" t="n">
         <v>3</v>
       </c>
       <c r="M205" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N205" t="s">
         <v>32</v>
       </c>
       <c r="O205" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P205" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q205" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="206">
@@ -11306,7 +11378,7 @@
         <v>409</v>
       </c>
       <c r="B206" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C206" t="s">
         <v>17</v>
@@ -11333,29 +11405,33 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L206" t="n">
         <v>1</v>
       </c>
       <c r="M206" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N206" t="s">
         <v>22</v>
       </c>
-      <c r="O206"/>
+      <c r="O206" t="n">
+        <v>5</v>
+      </c>
       <c r="P206" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q206"/>
+        <v>15</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
         <v>410</v>
       </c>
       <c r="B207" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C207" t="s">
         <v>17</v>
@@ -11382,29 +11458,33 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L207" t="n">
         <v>2</v>
       </c>
       <c r="M207" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N207" t="s">
         <v>22</v>
       </c>
-      <c r="O207"/>
+      <c r="O207" t="n">
+        <v>5</v>
+      </c>
       <c r="P207" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q207"/>
+        <v>15</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
         <v>411</v>
       </c>
       <c r="B208" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C208" t="s">
         <v>17</v>
@@ -11431,22 +11511,26 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L208" t="n">
         <v>3</v>
       </c>
       <c r="M208" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="N208" t="s">
         <v>22</v>
       </c>
-      <c r="O208"/>
+      <c r="O208" t="n">
+        <v>5</v>
+      </c>
       <c r="P208" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q208"/>
+        <v>15</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>140</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -11480,25 +11564,25 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L209" t="n">
         <v>1</v>
       </c>
       <c r="M209" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N209" t="s">
         <v>26</v>
       </c>
       <c r="O209" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P209" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q209" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="210">
@@ -11533,25 +11617,25 @@
         <v>3</v>
       </c>
       <c r="K210" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L210" t="n">
         <v>2</v>
       </c>
       <c r="M210" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N210" t="s">
         <v>26</v>
       </c>
       <c r="O210" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P210" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q210" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="211">
@@ -11586,25 +11670,25 @@
         <v>3</v>
       </c>
       <c r="K211" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L211" t="n">
         <v>3</v>
       </c>
       <c r="M211" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="N211" t="s">
         <v>26</v>
       </c>
       <c r="O211" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P211" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q211" t="n">
-        <v>60</v>
+        <v>133</v>
       </c>
     </row>
     <row r="212">
@@ -11612,7 +11696,7 @@
         <v>421</v>
       </c>
       <c r="B212" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C212" t="s">
         <v>17</v>
@@ -11639,13 +11723,13 @@
         <v>3</v>
       </c>
       <c r="K212" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L212" t="n">
         <v>1</v>
       </c>
       <c r="M212" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N212" t="s">
         <v>29</v>
@@ -11654,10 +11738,10 @@
         <v>3</v>
       </c>
       <c r="P212" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q212" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="213">
@@ -11665,7 +11749,7 @@
         <v>422</v>
       </c>
       <c r="B213" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C213" t="s">
         <v>17</v>
@@ -11692,13 +11776,13 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L213" t="n">
         <v>2</v>
       </c>
       <c r="M213" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N213" t="s">
         <v>29</v>
@@ -11707,10 +11791,10 @@
         <v>3</v>
       </c>
       <c r="P213" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q213" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="214">
@@ -11718,7 +11802,7 @@
         <v>423</v>
       </c>
       <c r="B214" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C214" t="s">
         <v>17</v>
@@ -11745,13 +11829,13 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L214" t="n">
         <v>3</v>
       </c>
       <c r="M214" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N214" t="s">
         <v>29</v>
@@ -11760,10 +11844,10 @@
         <v>3</v>
       </c>
       <c r="P214" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Q214" t="n">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="215">
@@ -11771,7 +11855,7 @@
         <v>427</v>
       </c>
       <c r="B215" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C215" t="s">
         <v>17</v>
@@ -11798,25 +11882,25 @@
         <v>3</v>
       </c>
       <c r="K215" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L215" t="n">
         <v>1</v>
       </c>
       <c r="M215" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N215" t="s">
         <v>32</v>
       </c>
       <c r="O215" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P215" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q215" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="216">
@@ -11824,7 +11908,7 @@
         <v>428</v>
       </c>
       <c r="B216" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" t="s">
         <v>17</v>
@@ -11851,25 +11935,25 @@
         <v>3</v>
       </c>
       <c r="K216" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L216" t="n">
         <v>2</v>
       </c>
       <c r="M216" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N216" t="s">
         <v>32</v>
       </c>
       <c r="O216" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P216" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q216" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
     <row r="217">
@@ -11877,7 +11961,7 @@
         <v>429</v>
       </c>
       <c r="B217" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C217" t="s">
         <v>17</v>
@@ -11904,25 +11988,25 @@
         <v>3</v>
       </c>
       <c r="K217" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L217" t="n">
         <v>3</v>
       </c>
       <c r="M217" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N217" t="s">
         <v>32</v>
       </c>
       <c r="O217" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P217" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q217" t="n">
-        <v>89</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
@@ -125,61 +125,37 @@
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
     <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + NDF_nutrition + EE_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + EE_nutrition</t>
   </si>
   <si>
     <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(115, 116, 117, 118, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + CP_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + ADF_nutrition + EE_nutrition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c(58, 59, 60, 61, 74, 75, 76, 77, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
 </sst>
 </file>
@@ -1865,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1918,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -1971,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L28" t="n">
         <v>3</v>
@@ -2183,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2236,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L33" t="n">
         <v>2</v>
@@ -2289,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L34" t="n">
         <v>3</v>
@@ -2501,7 +2477,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2554,7 +2530,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2607,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -2819,7 +2795,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -2872,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -2925,7 +2901,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
         <v>3</v>
@@ -3137,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3190,7 +3166,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3243,7 +3219,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3296,7 +3272,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3349,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3402,7 +3378,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3455,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3508,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3561,7 +3537,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3614,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3667,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3720,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3773,7 +3749,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3826,7 +3802,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3879,7 +3855,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3932,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3985,7 +3961,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -4038,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4091,7 +4067,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4144,7 +4120,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4197,7 +4173,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4250,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4303,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4356,7 +4332,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4409,7 +4385,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4462,7 +4438,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4515,7 +4491,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4568,13 +4544,13 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
@@ -4621,13 +4597,13 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
@@ -4674,13 +4650,13 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
@@ -4727,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4780,7 +4756,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4833,7 +4809,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4886,7 +4862,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -4939,7 +4915,7 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
@@ -4992,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -5045,7 +5021,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5098,7 +5074,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5151,7 +5127,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5204,13 +5180,13 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
@@ -5257,13 +5233,13 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
@@ -5310,13 +5286,13 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
@@ -5363,7 +5339,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5416,7 +5392,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5469,7 +5445,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5522,7 +5498,7 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -5575,7 +5551,7 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
@@ -5628,7 +5604,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
@@ -5681,7 +5657,7 @@
         <v>2</v>
       </c>
       <c r="K98" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -5734,7 +5710,7 @@
         <v>2</v>
       </c>
       <c r="K99" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L99" t="n">
         <v>2</v>
@@ -5787,7 +5763,7 @@
         <v>2</v>
       </c>
       <c r="K100" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L100" t="n">
         <v>3</v>
@@ -5840,7 +5816,7 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -5893,7 +5869,7 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
@@ -5946,7 +5922,7 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
@@ -5999,7 +5975,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6052,7 +6028,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L105" t="n">
         <v>2</v>
@@ -6105,7 +6081,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L106" t="n">
         <v>3</v>
@@ -6158,7 +6134,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
@@ -6211,7 +6187,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
@@ -6264,7 +6240,7 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
@@ -6317,7 +6293,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -6370,7 +6346,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L111" t="n">
         <v>2</v>
@@ -6423,7 +6399,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L112" t="n">
         <v>3</v>
@@ -6476,7 +6452,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -6529,7 +6505,7 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
@@ -6582,7 +6558,7 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
@@ -6635,7 +6611,7 @@
         <v>2</v>
       </c>
       <c r="K116" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -6688,7 +6664,7 @@
         <v>2</v>
       </c>
       <c r="K117" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L117" t="n">
         <v>2</v>
@@ -6741,7 +6717,7 @@
         <v>2</v>
       </c>
       <c r="K118" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L118" t="n">
         <v>3</v>
@@ -6794,7 +6770,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
@@ -6847,7 +6823,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
@@ -6900,7 +6876,7 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
@@ -6953,13 +6929,13 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
@@ -6968,10 +6944,10 @@
         <v>7</v>
       </c>
       <c r="P122" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q122" t="n">
-        <v>286</v>
+        <v>160</v>
       </c>
     </row>
     <row r="123">
@@ -7006,13 +6982,13 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
@@ -7021,10 +6997,10 @@
         <v>7</v>
       </c>
       <c r="P123" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q123" t="n">
-        <v>286</v>
+        <v>160</v>
       </c>
     </row>
     <row r="124">
@@ -7059,13 +7035,13 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
@@ -7074,10 +7050,10 @@
         <v>7</v>
       </c>
       <c r="P124" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q124" t="n">
-        <v>286</v>
+        <v>160</v>
       </c>
     </row>
     <row r="125">
@@ -7112,7 +7088,7 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
@@ -7165,7 +7141,7 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
@@ -7218,7 +7194,7 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
@@ -7271,25 +7247,25 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N128" t="s">
         <v>29</v>
       </c>
       <c r="O128" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P128" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q128" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129">
@@ -7324,25 +7300,25 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
       </c>
       <c r="M129" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N129" t="s">
         <v>29</v>
       </c>
       <c r="O129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P129" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q129" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="130">
@@ -7377,25 +7353,25 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
       </c>
       <c r="M130" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N130" t="s">
         <v>29</v>
       </c>
       <c r="O130" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P130" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q130" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="131">
@@ -7430,7 +7406,7 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -7483,7 +7459,7 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
@@ -7536,7 +7512,7 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
@@ -7589,13 +7565,13 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
@@ -7604,10 +7580,10 @@
         <v>7</v>
       </c>
       <c r="P134" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q134" t="n">
-        <v>286</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135">
@@ -7642,13 +7618,13 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
@@ -7657,10 +7633,10 @@
         <v>7</v>
       </c>
       <c r="P135" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q135" t="n">
-        <v>286</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136">
@@ -7695,13 +7671,13 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
@@ -7710,10 +7686,10 @@
         <v>7</v>
       </c>
       <c r="P136" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q136" t="n">
-        <v>286</v>
+        <v>160</v>
       </c>
     </row>
     <row r="137">
@@ -7748,7 +7724,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
@@ -7801,7 +7777,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
@@ -7854,7 +7830,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
@@ -7907,25 +7883,25 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N140" t="s">
         <v>29</v>
       </c>
       <c r="O140" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P140" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q140" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="141">
@@ -7960,25 +7936,25 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
       </c>
       <c r="M141" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N141" t="s">
         <v>29</v>
       </c>
       <c r="O141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P141" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q141" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="142">
@@ -8013,25 +7989,25 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
       </c>
       <c r="M142" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="N142" t="s">
         <v>29</v>
       </c>
       <c r="O142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P142" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Q142" t="n">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="143">
@@ -8066,7 +8042,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
@@ -8119,7 +8095,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
@@ -8172,7 +8148,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -8191,3822 +8167,6 @@
       </c>
       <c r="Q145" t="n">
         <v>633</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>289</v>
-      </c>
-      <c r="B146" t="b">
-        <v>0</v>
-      </c>
-      <c r="C146" t="s">
-        <v>17</v>
-      </c>
-      <c r="D146" t="s">
-        <v>18</v>
-      </c>
-      <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" t="n">
-        <v>1</v>
-      </c>
-      <c r="H146" t="s">
-        <v>19</v>
-      </c>
-      <c r="I146" t="n">
-        <v>7</v>
-      </c>
-      <c r="J146" t="n">
-        <v>3</v>
-      </c>
-      <c r="K146" t="s">
-        <v>48</v>
-      </c>
-      <c r="L146" t="n">
-        <v>1</v>
-      </c>
-      <c r="M146" t="s">
-        <v>49</v>
-      </c>
-      <c r="N146" t="s">
-        <v>22</v>
-      </c>
-      <c r="O146" t="n">
-        <v>7</v>
-      </c>
-      <c r="P146" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q146" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>290</v>
-      </c>
-      <c r="B147" t="b">
-        <v>0</v>
-      </c>
-      <c r="C147" t="s">
-        <v>17</v>
-      </c>
-      <c r="D147" t="s">
-        <v>18</v>
-      </c>
-      <c r="E147" t="n">
-        <v>1</v>
-      </c>
-      <c r="F147" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" t="n">
-        <v>1</v>
-      </c>
-      <c r="H147" t="s">
-        <v>19</v>
-      </c>
-      <c r="I147" t="n">
-        <v>7</v>
-      </c>
-      <c r="J147" t="n">
-        <v>3</v>
-      </c>
-      <c r="K147" t="s">
-        <v>48</v>
-      </c>
-      <c r="L147" t="n">
-        <v>2</v>
-      </c>
-      <c r="M147" t="s">
-        <v>49</v>
-      </c>
-      <c r="N147" t="s">
-        <v>22</v>
-      </c>
-      <c r="O147" t="n">
-        <v>7</v>
-      </c>
-      <c r="P147" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q147" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>291</v>
-      </c>
-      <c r="B148" t="b">
-        <v>0</v>
-      </c>
-      <c r="C148" t="s">
-        <v>17</v>
-      </c>
-      <c r="D148" t="s">
-        <v>18</v>
-      </c>
-      <c r="E148" t="n">
-        <v>1</v>
-      </c>
-      <c r="F148" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" t="n">
-        <v>1</v>
-      </c>
-      <c r="H148" t="s">
-        <v>19</v>
-      </c>
-      <c r="I148" t="n">
-        <v>7</v>
-      </c>
-      <c r="J148" t="n">
-        <v>3</v>
-      </c>
-      <c r="K148" t="s">
-        <v>48</v>
-      </c>
-      <c r="L148" t="n">
-        <v>3</v>
-      </c>
-      <c r="M148" t="s">
-        <v>49</v>
-      </c>
-      <c r="N148" t="s">
-        <v>22</v>
-      </c>
-      <c r="O148" t="n">
-        <v>7</v>
-      </c>
-      <c r="P148" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q148" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>295</v>
-      </c>
-      <c r="B149" t="b">
-        <v>0</v>
-      </c>
-      <c r="C149" t="s">
-        <v>17</v>
-      </c>
-      <c r="D149" t="s">
-        <v>18</v>
-      </c>
-      <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="n">
-        <v>2</v>
-      </c>
-      <c r="G149" t="n">
-        <v>1</v>
-      </c>
-      <c r="H149" t="s">
-        <v>23</v>
-      </c>
-      <c r="I149" t="n">
-        <v>7</v>
-      </c>
-      <c r="J149" t="n">
-        <v>3</v>
-      </c>
-      <c r="K149" t="s">
-        <v>50</v>
-      </c>
-      <c r="L149" t="n">
-        <v>1</v>
-      </c>
-      <c r="M149" t="s">
-        <v>51</v>
-      </c>
-      <c r="N149" t="s">
-        <v>26</v>
-      </c>
-      <c r="O149" t="n">
-        <v>5</v>
-      </c>
-      <c r="P149" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q149" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>296</v>
-      </c>
-      <c r="B150" t="b">
-        <v>0</v>
-      </c>
-      <c r="C150" t="s">
-        <v>17</v>
-      </c>
-      <c r="D150" t="s">
-        <v>18</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="n">
-        <v>2</v>
-      </c>
-      <c r="G150" t="n">
-        <v>1</v>
-      </c>
-      <c r="H150" t="s">
-        <v>23</v>
-      </c>
-      <c r="I150" t="n">
-        <v>7</v>
-      </c>
-      <c r="J150" t="n">
-        <v>3</v>
-      </c>
-      <c r="K150" t="s">
-        <v>50</v>
-      </c>
-      <c r="L150" t="n">
-        <v>2</v>
-      </c>
-      <c r="M150" t="s">
-        <v>51</v>
-      </c>
-      <c r="N150" t="s">
-        <v>26</v>
-      </c>
-      <c r="O150" t="n">
-        <v>5</v>
-      </c>
-      <c r="P150" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q150" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>297</v>
-      </c>
-      <c r="B151" t="b">
-        <v>0</v>
-      </c>
-      <c r="C151" t="s">
-        <v>17</v>
-      </c>
-      <c r="D151" t="s">
-        <v>18</v>
-      </c>
-      <c r="E151" t="n">
-        <v>1</v>
-      </c>
-      <c r="F151" t="n">
-        <v>2</v>
-      </c>
-      <c r="G151" t="n">
-        <v>1</v>
-      </c>
-      <c r="H151" t="s">
-        <v>23</v>
-      </c>
-      <c r="I151" t="n">
-        <v>7</v>
-      </c>
-      <c r="J151" t="n">
-        <v>3</v>
-      </c>
-      <c r="K151" t="s">
-        <v>50</v>
-      </c>
-      <c r="L151" t="n">
-        <v>3</v>
-      </c>
-      <c r="M151" t="s">
-        <v>51</v>
-      </c>
-      <c r="N151" t="s">
-        <v>26</v>
-      </c>
-      <c r="O151" t="n">
-        <v>5</v>
-      </c>
-      <c r="P151" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q151" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>301</v>
-      </c>
-      <c r="B152" t="b">
-        <v>0</v>
-      </c>
-      <c r="C152" t="s">
-        <v>17</v>
-      </c>
-      <c r="D152" t="s">
-        <v>18</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2</v>
-      </c>
-      <c r="F152" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" t="n">
-        <v>1</v>
-      </c>
-      <c r="H152" t="s">
-        <v>27</v>
-      </c>
-      <c r="I152" t="n">
-        <v>7</v>
-      </c>
-      <c r="J152" t="n">
-        <v>3</v>
-      </c>
-      <c r="K152" t="s">
-        <v>48</v>
-      </c>
-      <c r="L152" t="n">
-        <v>1</v>
-      </c>
-      <c r="M152" t="s">
-        <v>28</v>
-      </c>
-      <c r="N152" t="s">
-        <v>29</v>
-      </c>
-      <c r="O152" t="n">
-        <v>4</v>
-      </c>
-      <c r="P152" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q152" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>302</v>
-      </c>
-      <c r="B153" t="b">
-        <v>0</v>
-      </c>
-      <c r="C153" t="s">
-        <v>17</v>
-      </c>
-      <c r="D153" t="s">
-        <v>18</v>
-      </c>
-      <c r="E153" t="n">
-        <v>2</v>
-      </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="s">
-        <v>27</v>
-      </c>
-      <c r="I153" t="n">
-        <v>7</v>
-      </c>
-      <c r="J153" t="n">
-        <v>3</v>
-      </c>
-      <c r="K153" t="s">
-        <v>48</v>
-      </c>
-      <c r="L153" t="n">
-        <v>2</v>
-      </c>
-      <c r="M153" t="s">
-        <v>28</v>
-      </c>
-      <c r="N153" t="s">
-        <v>29</v>
-      </c>
-      <c r="O153" t="n">
-        <v>4</v>
-      </c>
-      <c r="P153" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q153" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>303</v>
-      </c>
-      <c r="B154" t="b">
-        <v>0</v>
-      </c>
-      <c r="C154" t="s">
-        <v>17</v>
-      </c>
-      <c r="D154" t="s">
-        <v>18</v>
-      </c>
-      <c r="E154" t="n">
-        <v>2</v>
-      </c>
-      <c r="F154" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" t="s">
-        <v>27</v>
-      </c>
-      <c r="I154" t="n">
-        <v>7</v>
-      </c>
-      <c r="J154" t="n">
-        <v>3</v>
-      </c>
-      <c r="K154" t="s">
-        <v>48</v>
-      </c>
-      <c r="L154" t="n">
-        <v>3</v>
-      </c>
-      <c r="M154" t="s">
-        <v>28</v>
-      </c>
-      <c r="N154" t="s">
-        <v>29</v>
-      </c>
-      <c r="O154" t="n">
-        <v>4</v>
-      </c>
-      <c r="P154" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q154" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>307</v>
-      </c>
-      <c r="B155" t="b">
-        <v>0</v>
-      </c>
-      <c r="C155" t="s">
-        <v>17</v>
-      </c>
-      <c r="D155" t="s">
-        <v>18</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2</v>
-      </c>
-      <c r="F155" t="n">
-        <v>2</v>
-      </c>
-      <c r="G155" t="n">
-        <v>1</v>
-      </c>
-      <c r="H155" t="s">
-        <v>30</v>
-      </c>
-      <c r="I155" t="n">
-        <v>7</v>
-      </c>
-      <c r="J155" t="n">
-        <v>3</v>
-      </c>
-      <c r="K155" t="s">
-        <v>50</v>
-      </c>
-      <c r="L155" t="n">
-        <v>1</v>
-      </c>
-      <c r="M155" t="s">
-        <v>52</v>
-      </c>
-      <c r="N155" t="s">
-        <v>32</v>
-      </c>
-      <c r="O155" t="n">
-        <v>5</v>
-      </c>
-      <c r="P155" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>308</v>
-      </c>
-      <c r="B156" t="b">
-        <v>0</v>
-      </c>
-      <c r="C156" t="s">
-        <v>17</v>
-      </c>
-      <c r="D156" t="s">
-        <v>18</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2</v>
-      </c>
-      <c r="F156" t="n">
-        <v>2</v>
-      </c>
-      <c r="G156" t="n">
-        <v>1</v>
-      </c>
-      <c r="H156" t="s">
-        <v>30</v>
-      </c>
-      <c r="I156" t="n">
-        <v>7</v>
-      </c>
-      <c r="J156" t="n">
-        <v>3</v>
-      </c>
-      <c r="K156" t="s">
-        <v>50</v>
-      </c>
-      <c r="L156" t="n">
-        <v>2</v>
-      </c>
-      <c r="M156" t="s">
-        <v>52</v>
-      </c>
-      <c r="N156" t="s">
-        <v>32</v>
-      </c>
-      <c r="O156" t="n">
-        <v>5</v>
-      </c>
-      <c r="P156" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q156" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>309</v>
-      </c>
-      <c r="B157" t="b">
-        <v>0</v>
-      </c>
-      <c r="C157" t="s">
-        <v>17</v>
-      </c>
-      <c r="D157" t="s">
-        <v>18</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2</v>
-      </c>
-      <c r="F157" t="n">
-        <v>2</v>
-      </c>
-      <c r="G157" t="n">
-        <v>1</v>
-      </c>
-      <c r="H157" t="s">
-        <v>30</v>
-      </c>
-      <c r="I157" t="n">
-        <v>7</v>
-      </c>
-      <c r="J157" t="n">
-        <v>3</v>
-      </c>
-      <c r="K157" t="s">
-        <v>50</v>
-      </c>
-      <c r="L157" t="n">
-        <v>3</v>
-      </c>
-      <c r="M157" t="s">
-        <v>52</v>
-      </c>
-      <c r="N157" t="s">
-        <v>32</v>
-      </c>
-      <c r="O157" t="n">
-        <v>5</v>
-      </c>
-      <c r="P157" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q157" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>313</v>
-      </c>
-      <c r="B158" t="b">
-        <v>0</v>
-      </c>
-      <c r="C158" t="s">
-        <v>17</v>
-      </c>
-      <c r="D158" t="s">
-        <v>18</v>
-      </c>
-      <c r="E158" t="n">
-        <v>1</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" t="n">
-        <v>2</v>
-      </c>
-      <c r="H158" t="s">
-        <v>33</v>
-      </c>
-      <c r="I158" t="n">
-        <v>7</v>
-      </c>
-      <c r="J158" t="n">
-        <v>3</v>
-      </c>
-      <c r="K158" t="s">
-        <v>48</v>
-      </c>
-      <c r="L158" t="n">
-        <v>1</v>
-      </c>
-      <c r="M158" t="s">
-        <v>49</v>
-      </c>
-      <c r="N158" t="s">
-        <v>22</v>
-      </c>
-      <c r="O158" t="n">
-        <v>7</v>
-      </c>
-      <c r="P158" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q158" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>314</v>
-      </c>
-      <c r="B159" t="b">
-        <v>0</v>
-      </c>
-      <c r="C159" t="s">
-        <v>17</v>
-      </c>
-      <c r="D159" t="s">
-        <v>18</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" t="n">
-        <v>2</v>
-      </c>
-      <c r="H159" t="s">
-        <v>33</v>
-      </c>
-      <c r="I159" t="n">
-        <v>7</v>
-      </c>
-      <c r="J159" t="n">
-        <v>3</v>
-      </c>
-      <c r="K159" t="s">
-        <v>48</v>
-      </c>
-      <c r="L159" t="n">
-        <v>2</v>
-      </c>
-      <c r="M159" t="s">
-        <v>49</v>
-      </c>
-      <c r="N159" t="s">
-        <v>22</v>
-      </c>
-      <c r="O159" t="n">
-        <v>7</v>
-      </c>
-      <c r="P159" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q159" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>315</v>
-      </c>
-      <c r="B160" t="b">
-        <v>0</v>
-      </c>
-      <c r="C160" t="s">
-        <v>17</v>
-      </c>
-      <c r="D160" t="s">
-        <v>18</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1</v>
-      </c>
-      <c r="F160" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" t="n">
-        <v>2</v>
-      </c>
-      <c r="H160" t="s">
-        <v>33</v>
-      </c>
-      <c r="I160" t="n">
-        <v>7</v>
-      </c>
-      <c r="J160" t="n">
-        <v>3</v>
-      </c>
-      <c r="K160" t="s">
-        <v>48</v>
-      </c>
-      <c r="L160" t="n">
-        <v>3</v>
-      </c>
-      <c r="M160" t="s">
-        <v>49</v>
-      </c>
-      <c r="N160" t="s">
-        <v>22</v>
-      </c>
-      <c r="O160" t="n">
-        <v>7</v>
-      </c>
-      <c r="P160" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q160" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>319</v>
-      </c>
-      <c r="B161" t="b">
-        <v>0</v>
-      </c>
-      <c r="C161" t="s">
-        <v>17</v>
-      </c>
-      <c r="D161" t="s">
-        <v>18</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1</v>
-      </c>
-      <c r="F161" t="n">
-        <v>2</v>
-      </c>
-      <c r="G161" t="n">
-        <v>2</v>
-      </c>
-      <c r="H161" t="s">
-        <v>34</v>
-      </c>
-      <c r="I161" t="n">
-        <v>7</v>
-      </c>
-      <c r="J161" t="n">
-        <v>3</v>
-      </c>
-      <c r="K161" t="s">
-        <v>50</v>
-      </c>
-      <c r="L161" t="n">
-        <v>1</v>
-      </c>
-      <c r="M161" t="s">
-        <v>51</v>
-      </c>
-      <c r="N161" t="s">
-        <v>26</v>
-      </c>
-      <c r="O161" t="n">
-        <v>5</v>
-      </c>
-      <c r="P161" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q161" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="n">
-        <v>320</v>
-      </c>
-      <c r="B162" t="b">
-        <v>0</v>
-      </c>
-      <c r="C162" t="s">
-        <v>17</v>
-      </c>
-      <c r="D162" t="s">
-        <v>18</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" t="n">
-        <v>2</v>
-      </c>
-      <c r="G162" t="n">
-        <v>2</v>
-      </c>
-      <c r="H162" t="s">
-        <v>34</v>
-      </c>
-      <c r="I162" t="n">
-        <v>7</v>
-      </c>
-      <c r="J162" t="n">
-        <v>3</v>
-      </c>
-      <c r="K162" t="s">
-        <v>50</v>
-      </c>
-      <c r="L162" t="n">
-        <v>2</v>
-      </c>
-      <c r="M162" t="s">
-        <v>51</v>
-      </c>
-      <c r="N162" t="s">
-        <v>26</v>
-      </c>
-      <c r="O162" t="n">
-        <v>5</v>
-      </c>
-      <c r="P162" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>321</v>
-      </c>
-      <c r="B163" t="b">
-        <v>0</v>
-      </c>
-      <c r="C163" t="s">
-        <v>17</v>
-      </c>
-      <c r="D163" t="s">
-        <v>18</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="n">
-        <v>2</v>
-      </c>
-      <c r="G163" t="n">
-        <v>2</v>
-      </c>
-      <c r="H163" t="s">
-        <v>34</v>
-      </c>
-      <c r="I163" t="n">
-        <v>7</v>
-      </c>
-      <c r="J163" t="n">
-        <v>3</v>
-      </c>
-      <c r="K163" t="s">
-        <v>50</v>
-      </c>
-      <c r="L163" t="n">
-        <v>3</v>
-      </c>
-      <c r="M163" t="s">
-        <v>51</v>
-      </c>
-      <c r="N163" t="s">
-        <v>26</v>
-      </c>
-      <c r="O163" t="n">
-        <v>5</v>
-      </c>
-      <c r="P163" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>325</v>
-      </c>
-      <c r="B164" t="b">
-        <v>0</v>
-      </c>
-      <c r="C164" t="s">
-        <v>17</v>
-      </c>
-      <c r="D164" t="s">
-        <v>18</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" t="n">
-        <v>2</v>
-      </c>
-      <c r="H164" t="s">
-        <v>35</v>
-      </c>
-      <c r="I164" t="n">
-        <v>7</v>
-      </c>
-      <c r="J164" t="n">
-        <v>3</v>
-      </c>
-      <c r="K164" t="s">
-        <v>48</v>
-      </c>
-      <c r="L164" t="n">
-        <v>1</v>
-      </c>
-      <c r="M164" t="s">
-        <v>28</v>
-      </c>
-      <c r="N164" t="s">
-        <v>29</v>
-      </c>
-      <c r="O164" t="n">
-        <v>4</v>
-      </c>
-      <c r="P164" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q164" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>326</v>
-      </c>
-      <c r="B165" t="b">
-        <v>0</v>
-      </c>
-      <c r="C165" t="s">
-        <v>17</v>
-      </c>
-      <c r="D165" t="s">
-        <v>18</v>
-      </c>
-      <c r="E165" t="n">
-        <v>2</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" t="n">
-        <v>2</v>
-      </c>
-      <c r="H165" t="s">
-        <v>35</v>
-      </c>
-      <c r="I165" t="n">
-        <v>7</v>
-      </c>
-      <c r="J165" t="n">
-        <v>3</v>
-      </c>
-      <c r="K165" t="s">
-        <v>48</v>
-      </c>
-      <c r="L165" t="n">
-        <v>2</v>
-      </c>
-      <c r="M165" t="s">
-        <v>28</v>
-      </c>
-      <c r="N165" t="s">
-        <v>29</v>
-      </c>
-      <c r="O165" t="n">
-        <v>4</v>
-      </c>
-      <c r="P165" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q165" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>327</v>
-      </c>
-      <c r="B166" t="b">
-        <v>0</v>
-      </c>
-      <c r="C166" t="s">
-        <v>17</v>
-      </c>
-      <c r="D166" t="s">
-        <v>18</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2</v>
-      </c>
-      <c r="F166" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" t="n">
-        <v>2</v>
-      </c>
-      <c r="H166" t="s">
-        <v>35</v>
-      </c>
-      <c r="I166" t="n">
-        <v>7</v>
-      </c>
-      <c r="J166" t="n">
-        <v>3</v>
-      </c>
-      <c r="K166" t="s">
-        <v>48</v>
-      </c>
-      <c r="L166" t="n">
-        <v>3</v>
-      </c>
-      <c r="M166" t="s">
-        <v>28</v>
-      </c>
-      <c r="N166" t="s">
-        <v>29</v>
-      </c>
-      <c r="O166" t="n">
-        <v>4</v>
-      </c>
-      <c r="P166" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q166" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>331</v>
-      </c>
-      <c r="B167" t="b">
-        <v>0</v>
-      </c>
-      <c r="C167" t="s">
-        <v>17</v>
-      </c>
-      <c r="D167" t="s">
-        <v>18</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2</v>
-      </c>
-      <c r="F167" t="n">
-        <v>2</v>
-      </c>
-      <c r="G167" t="n">
-        <v>2</v>
-      </c>
-      <c r="H167" t="s">
-        <v>36</v>
-      </c>
-      <c r="I167" t="n">
-        <v>7</v>
-      </c>
-      <c r="J167" t="n">
-        <v>3</v>
-      </c>
-      <c r="K167" t="s">
-        <v>50</v>
-      </c>
-      <c r="L167" t="n">
-        <v>1</v>
-      </c>
-      <c r="M167" t="s">
-        <v>52</v>
-      </c>
-      <c r="N167" t="s">
-        <v>32</v>
-      </c>
-      <c r="O167" t="n">
-        <v>5</v>
-      </c>
-      <c r="P167" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q167" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="n">
-        <v>332</v>
-      </c>
-      <c r="B168" t="b">
-        <v>0</v>
-      </c>
-      <c r="C168" t="s">
-        <v>17</v>
-      </c>
-      <c r="D168" t="s">
-        <v>18</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2</v>
-      </c>
-      <c r="F168" t="n">
-        <v>2</v>
-      </c>
-      <c r="G168" t="n">
-        <v>2</v>
-      </c>
-      <c r="H168" t="s">
-        <v>36</v>
-      </c>
-      <c r="I168" t="n">
-        <v>7</v>
-      </c>
-      <c r="J168" t="n">
-        <v>3</v>
-      </c>
-      <c r="K168" t="s">
-        <v>50</v>
-      </c>
-      <c r="L168" t="n">
-        <v>2</v>
-      </c>
-      <c r="M168" t="s">
-        <v>52</v>
-      </c>
-      <c r="N168" t="s">
-        <v>32</v>
-      </c>
-      <c r="O168" t="n">
-        <v>5</v>
-      </c>
-      <c r="P168" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q168" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>333</v>
-      </c>
-      <c r="B169" t="b">
-        <v>0</v>
-      </c>
-      <c r="C169" t="s">
-        <v>17</v>
-      </c>
-      <c r="D169" t="s">
-        <v>18</v>
-      </c>
-      <c r="E169" t="n">
-        <v>2</v>
-      </c>
-      <c r="F169" t="n">
-        <v>2</v>
-      </c>
-      <c r="G169" t="n">
-        <v>2</v>
-      </c>
-      <c r="H169" t="s">
-        <v>36</v>
-      </c>
-      <c r="I169" t="n">
-        <v>7</v>
-      </c>
-      <c r="J169" t="n">
-        <v>3</v>
-      </c>
-      <c r="K169" t="s">
-        <v>50</v>
-      </c>
-      <c r="L169" t="n">
-        <v>3</v>
-      </c>
-      <c r="M169" t="s">
-        <v>52</v>
-      </c>
-      <c r="N169" t="s">
-        <v>32</v>
-      </c>
-      <c r="O169" t="n">
-        <v>5</v>
-      </c>
-      <c r="P169" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q169" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="n">
-        <v>337</v>
-      </c>
-      <c r="B170" t="b">
-        <v>0</v>
-      </c>
-      <c r="C170" t="s">
-        <v>17</v>
-      </c>
-      <c r="D170" t="s">
-        <v>18</v>
-      </c>
-      <c r="E170" t="n">
-        <v>1</v>
-      </c>
-      <c r="F170" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" t="n">
-        <v>1</v>
-      </c>
-      <c r="H170" t="s">
-        <v>19</v>
-      </c>
-      <c r="I170" t="n">
-        <v>8</v>
-      </c>
-      <c r="J170" t="n">
-        <v>3</v>
-      </c>
-      <c r="K170" t="s">
-        <v>53</v>
-      </c>
-      <c r="L170" t="n">
-        <v>1</v>
-      </c>
-      <c r="M170" t="s">
-        <v>49</v>
-      </c>
-      <c r="N170" t="s">
-        <v>22</v>
-      </c>
-      <c r="O170" t="n">
-        <v>7</v>
-      </c>
-      <c r="P170" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q170" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>338</v>
-      </c>
-      <c r="B171" t="b">
-        <v>0</v>
-      </c>
-      <c r="C171" t="s">
-        <v>17</v>
-      </c>
-      <c r="D171" t="s">
-        <v>18</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" t="n">
-        <v>1</v>
-      </c>
-      <c r="H171" t="s">
-        <v>19</v>
-      </c>
-      <c r="I171" t="n">
-        <v>8</v>
-      </c>
-      <c r="J171" t="n">
-        <v>3</v>
-      </c>
-      <c r="K171" t="s">
-        <v>53</v>
-      </c>
-      <c r="L171" t="n">
-        <v>2</v>
-      </c>
-      <c r="M171" t="s">
-        <v>49</v>
-      </c>
-      <c r="N171" t="s">
-        <v>22</v>
-      </c>
-      <c r="O171" t="n">
-        <v>7</v>
-      </c>
-      <c r="P171" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>339</v>
-      </c>
-      <c r="B172" t="b">
-        <v>0</v>
-      </c>
-      <c r="C172" t="s">
-        <v>17</v>
-      </c>
-      <c r="D172" t="s">
-        <v>18</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1</v>
-      </c>
-      <c r="F172" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" t="n">
-        <v>1</v>
-      </c>
-      <c r="H172" t="s">
-        <v>19</v>
-      </c>
-      <c r="I172" t="n">
-        <v>8</v>
-      </c>
-      <c r="J172" t="n">
-        <v>3</v>
-      </c>
-      <c r="K172" t="s">
-        <v>53</v>
-      </c>
-      <c r="L172" t="n">
-        <v>3</v>
-      </c>
-      <c r="M172" t="s">
-        <v>49</v>
-      </c>
-      <c r="N172" t="s">
-        <v>22</v>
-      </c>
-      <c r="O172" t="n">
-        <v>7</v>
-      </c>
-      <c r="P172" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q172" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>343</v>
-      </c>
-      <c r="B173" t="b">
-        <v>0</v>
-      </c>
-      <c r="C173" t="s">
-        <v>17</v>
-      </c>
-      <c r="D173" t="s">
-        <v>18</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" t="n">
-        <v>2</v>
-      </c>
-      <c r="G173" t="n">
-        <v>1</v>
-      </c>
-      <c r="H173" t="s">
-        <v>23</v>
-      </c>
-      <c r="I173" t="n">
-        <v>8</v>
-      </c>
-      <c r="J173" t="n">
-        <v>3</v>
-      </c>
-      <c r="K173" t="s">
-        <v>50</v>
-      </c>
-      <c r="L173" t="n">
-        <v>1</v>
-      </c>
-      <c r="M173" t="s">
-        <v>51</v>
-      </c>
-      <c r="N173" t="s">
-        <v>26</v>
-      </c>
-      <c r="O173" t="n">
-        <v>5</v>
-      </c>
-      <c r="P173" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q173" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>344</v>
-      </c>
-      <c r="B174" t="b">
-        <v>0</v>
-      </c>
-      <c r="C174" t="s">
-        <v>17</v>
-      </c>
-      <c r="D174" t="s">
-        <v>18</v>
-      </c>
-      <c r="E174" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" t="n">
-        <v>2</v>
-      </c>
-      <c r="G174" t="n">
-        <v>1</v>
-      </c>
-      <c r="H174" t="s">
-        <v>23</v>
-      </c>
-      <c r="I174" t="n">
-        <v>8</v>
-      </c>
-      <c r="J174" t="n">
-        <v>3</v>
-      </c>
-      <c r="K174" t="s">
-        <v>50</v>
-      </c>
-      <c r="L174" t="n">
-        <v>2</v>
-      </c>
-      <c r="M174" t="s">
-        <v>51</v>
-      </c>
-      <c r="N174" t="s">
-        <v>26</v>
-      </c>
-      <c r="O174" t="n">
-        <v>5</v>
-      </c>
-      <c r="P174" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q174" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>345</v>
-      </c>
-      <c r="B175" t="b">
-        <v>0</v>
-      </c>
-      <c r="C175" t="s">
-        <v>17</v>
-      </c>
-      <c r="D175" t="s">
-        <v>18</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" t="n">
-        <v>2</v>
-      </c>
-      <c r="G175" t="n">
-        <v>1</v>
-      </c>
-      <c r="H175" t="s">
-        <v>23</v>
-      </c>
-      <c r="I175" t="n">
-        <v>8</v>
-      </c>
-      <c r="J175" t="n">
-        <v>3</v>
-      </c>
-      <c r="K175" t="s">
-        <v>50</v>
-      </c>
-      <c r="L175" t="n">
-        <v>3</v>
-      </c>
-      <c r="M175" t="s">
-        <v>51</v>
-      </c>
-      <c r="N175" t="s">
-        <v>26</v>
-      </c>
-      <c r="O175" t="n">
-        <v>5</v>
-      </c>
-      <c r="P175" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q175" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="n">
-        <v>349</v>
-      </c>
-      <c r="B176" t="b">
-        <v>0</v>
-      </c>
-      <c r="C176" t="s">
-        <v>17</v>
-      </c>
-      <c r="D176" t="s">
-        <v>18</v>
-      </c>
-      <c r="E176" t="n">
-        <v>2</v>
-      </c>
-      <c r="F176" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" t="n">
-        <v>1</v>
-      </c>
-      <c r="H176" t="s">
-        <v>27</v>
-      </c>
-      <c r="I176" t="n">
-        <v>8</v>
-      </c>
-      <c r="J176" t="n">
-        <v>3</v>
-      </c>
-      <c r="K176" t="s">
-        <v>53</v>
-      </c>
-      <c r="L176" t="n">
-        <v>1</v>
-      </c>
-      <c r="M176" t="s">
-        <v>28</v>
-      </c>
-      <c r="N176" t="s">
-        <v>29</v>
-      </c>
-      <c r="O176" t="n">
-        <v>4</v>
-      </c>
-      <c r="P176" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q176" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="n">
-        <v>350</v>
-      </c>
-      <c r="B177" t="b">
-        <v>0</v>
-      </c>
-      <c r="C177" t="s">
-        <v>17</v>
-      </c>
-      <c r="D177" t="s">
-        <v>18</v>
-      </c>
-      <c r="E177" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" t="n">
-        <v>1</v>
-      </c>
-      <c r="H177" t="s">
-        <v>27</v>
-      </c>
-      <c r="I177" t="n">
-        <v>8</v>
-      </c>
-      <c r="J177" t="n">
-        <v>3</v>
-      </c>
-      <c r="K177" t="s">
-        <v>53</v>
-      </c>
-      <c r="L177" t="n">
-        <v>2</v>
-      </c>
-      <c r="M177" t="s">
-        <v>28</v>
-      </c>
-      <c r="N177" t="s">
-        <v>29</v>
-      </c>
-      <c r="O177" t="n">
-        <v>4</v>
-      </c>
-      <c r="P177" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q177" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="n">
-        <v>351</v>
-      </c>
-      <c r="B178" t="b">
-        <v>0</v>
-      </c>
-      <c r="C178" t="s">
-        <v>17</v>
-      </c>
-      <c r="D178" t="s">
-        <v>18</v>
-      </c>
-      <c r="E178" t="n">
-        <v>2</v>
-      </c>
-      <c r="F178" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" t="n">
-        <v>1</v>
-      </c>
-      <c r="H178" t="s">
-        <v>27</v>
-      </c>
-      <c r="I178" t="n">
-        <v>8</v>
-      </c>
-      <c r="J178" t="n">
-        <v>3</v>
-      </c>
-      <c r="K178" t="s">
-        <v>53</v>
-      </c>
-      <c r="L178" t="n">
-        <v>3</v>
-      </c>
-      <c r="M178" t="s">
-        <v>28</v>
-      </c>
-      <c r="N178" t="s">
-        <v>29</v>
-      </c>
-      <c r="O178" t="n">
-        <v>4</v>
-      </c>
-      <c r="P178" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q178" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="n">
-        <v>355</v>
-      </c>
-      <c r="B179" t="b">
-        <v>0</v>
-      </c>
-      <c r="C179" t="s">
-        <v>17</v>
-      </c>
-      <c r="D179" t="s">
-        <v>18</v>
-      </c>
-      <c r="E179" t="n">
-        <v>2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>2</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="s">
-        <v>30</v>
-      </c>
-      <c r="I179" t="n">
-        <v>8</v>
-      </c>
-      <c r="J179" t="n">
-        <v>3</v>
-      </c>
-      <c r="K179" t="s">
-        <v>50</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="s">
-        <v>52</v>
-      </c>
-      <c r="N179" t="s">
-        <v>32</v>
-      </c>
-      <c r="O179" t="n">
-        <v>5</v>
-      </c>
-      <c r="P179" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q179" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="n">
-        <v>356</v>
-      </c>
-      <c r="B180" t="b">
-        <v>0</v>
-      </c>
-      <c r="C180" t="s">
-        <v>17</v>
-      </c>
-      <c r="D180" t="s">
-        <v>18</v>
-      </c>
-      <c r="E180" t="n">
-        <v>2</v>
-      </c>
-      <c r="F180" t="n">
-        <v>2</v>
-      </c>
-      <c r="G180" t="n">
-        <v>1</v>
-      </c>
-      <c r="H180" t="s">
-        <v>30</v>
-      </c>
-      <c r="I180" t="n">
-        <v>8</v>
-      </c>
-      <c r="J180" t="n">
-        <v>3</v>
-      </c>
-      <c r="K180" t="s">
-        <v>50</v>
-      </c>
-      <c r="L180" t="n">
-        <v>2</v>
-      </c>
-      <c r="M180" t="s">
-        <v>52</v>
-      </c>
-      <c r="N180" t="s">
-        <v>32</v>
-      </c>
-      <c r="O180" t="n">
-        <v>5</v>
-      </c>
-      <c r="P180" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q180" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="n">
-        <v>357</v>
-      </c>
-      <c r="B181" t="b">
-        <v>0</v>
-      </c>
-      <c r="C181" t="s">
-        <v>17</v>
-      </c>
-      <c r="D181" t="s">
-        <v>18</v>
-      </c>
-      <c r="E181" t="n">
-        <v>2</v>
-      </c>
-      <c r="F181" t="n">
-        <v>2</v>
-      </c>
-      <c r="G181" t="n">
-        <v>1</v>
-      </c>
-      <c r="H181" t="s">
-        <v>30</v>
-      </c>
-      <c r="I181" t="n">
-        <v>8</v>
-      </c>
-      <c r="J181" t="n">
-        <v>3</v>
-      </c>
-      <c r="K181" t="s">
-        <v>50</v>
-      </c>
-      <c r="L181" t="n">
-        <v>3</v>
-      </c>
-      <c r="M181" t="s">
-        <v>52</v>
-      </c>
-      <c r="N181" t="s">
-        <v>32</v>
-      </c>
-      <c r="O181" t="n">
-        <v>5</v>
-      </c>
-      <c r="P181" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q181" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="n">
-        <v>361</v>
-      </c>
-      <c r="B182" t="b">
-        <v>0</v>
-      </c>
-      <c r="C182" t="s">
-        <v>17</v>
-      </c>
-      <c r="D182" t="s">
-        <v>18</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1</v>
-      </c>
-      <c r="F182" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" t="n">
-        <v>2</v>
-      </c>
-      <c r="H182" t="s">
-        <v>33</v>
-      </c>
-      <c r="I182" t="n">
-        <v>8</v>
-      </c>
-      <c r="J182" t="n">
-        <v>3</v>
-      </c>
-      <c r="K182" t="s">
-        <v>53</v>
-      </c>
-      <c r="L182" t="n">
-        <v>1</v>
-      </c>
-      <c r="M182" t="s">
-        <v>49</v>
-      </c>
-      <c r="N182" t="s">
-        <v>22</v>
-      </c>
-      <c r="O182" t="n">
-        <v>7</v>
-      </c>
-      <c r="P182" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="n">
-        <v>362</v>
-      </c>
-      <c r="B183" t="b">
-        <v>0</v>
-      </c>
-      <c r="C183" t="s">
-        <v>17</v>
-      </c>
-      <c r="D183" t="s">
-        <v>18</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" t="n">
-        <v>2</v>
-      </c>
-      <c r="H183" t="s">
-        <v>33</v>
-      </c>
-      <c r="I183" t="n">
-        <v>8</v>
-      </c>
-      <c r="J183" t="n">
-        <v>3</v>
-      </c>
-      <c r="K183" t="s">
-        <v>53</v>
-      </c>
-      <c r="L183" t="n">
-        <v>2</v>
-      </c>
-      <c r="M183" t="s">
-        <v>49</v>
-      </c>
-      <c r="N183" t="s">
-        <v>22</v>
-      </c>
-      <c r="O183" t="n">
-        <v>7</v>
-      </c>
-      <c r="P183" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q183" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="n">
-        <v>363</v>
-      </c>
-      <c r="B184" t="b">
-        <v>0</v>
-      </c>
-      <c r="C184" t="s">
-        <v>17</v>
-      </c>
-      <c r="D184" t="s">
-        <v>18</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" t="n">
-        <v>2</v>
-      </c>
-      <c r="H184" t="s">
-        <v>33</v>
-      </c>
-      <c r="I184" t="n">
-        <v>8</v>
-      </c>
-      <c r="J184" t="n">
-        <v>3</v>
-      </c>
-      <c r="K184" t="s">
-        <v>53</v>
-      </c>
-      <c r="L184" t="n">
-        <v>3</v>
-      </c>
-      <c r="M184" t="s">
-        <v>49</v>
-      </c>
-      <c r="N184" t="s">
-        <v>22</v>
-      </c>
-      <c r="O184" t="n">
-        <v>7</v>
-      </c>
-      <c r="P184" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="n">
-        <v>367</v>
-      </c>
-      <c r="B185" t="b">
-        <v>0</v>
-      </c>
-      <c r="C185" t="s">
-        <v>17</v>
-      </c>
-      <c r="D185" t="s">
-        <v>18</v>
-      </c>
-      <c r="E185" t="n">
-        <v>1</v>
-      </c>
-      <c r="F185" t="n">
-        <v>2</v>
-      </c>
-      <c r="G185" t="n">
-        <v>2</v>
-      </c>
-      <c r="H185" t="s">
-        <v>34</v>
-      </c>
-      <c r="I185" t="n">
-        <v>8</v>
-      </c>
-      <c r="J185" t="n">
-        <v>3</v>
-      </c>
-      <c r="K185" t="s">
-        <v>50</v>
-      </c>
-      <c r="L185" t="n">
-        <v>1</v>
-      </c>
-      <c r="M185" t="s">
-        <v>51</v>
-      </c>
-      <c r="N185" t="s">
-        <v>26</v>
-      </c>
-      <c r="O185" t="n">
-        <v>5</v>
-      </c>
-      <c r="P185" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q185" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="n">
-        <v>368</v>
-      </c>
-      <c r="B186" t="b">
-        <v>0</v>
-      </c>
-      <c r="C186" t="s">
-        <v>17</v>
-      </c>
-      <c r="D186" t="s">
-        <v>18</v>
-      </c>
-      <c r="E186" t="n">
-        <v>1</v>
-      </c>
-      <c r="F186" t="n">
-        <v>2</v>
-      </c>
-      <c r="G186" t="n">
-        <v>2</v>
-      </c>
-      <c r="H186" t="s">
-        <v>34</v>
-      </c>
-      <c r="I186" t="n">
-        <v>8</v>
-      </c>
-      <c r="J186" t="n">
-        <v>3</v>
-      </c>
-      <c r="K186" t="s">
-        <v>50</v>
-      </c>
-      <c r="L186" t="n">
-        <v>2</v>
-      </c>
-      <c r="M186" t="s">
-        <v>51</v>
-      </c>
-      <c r="N186" t="s">
-        <v>26</v>
-      </c>
-      <c r="O186" t="n">
-        <v>5</v>
-      </c>
-      <c r="P186" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q186" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="n">
-        <v>369</v>
-      </c>
-      <c r="B187" t="b">
-        <v>0</v>
-      </c>
-      <c r="C187" t="s">
-        <v>17</v>
-      </c>
-      <c r="D187" t="s">
-        <v>18</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1</v>
-      </c>
-      <c r="F187" t="n">
-        <v>2</v>
-      </c>
-      <c r="G187" t="n">
-        <v>2</v>
-      </c>
-      <c r="H187" t="s">
-        <v>34</v>
-      </c>
-      <c r="I187" t="n">
-        <v>8</v>
-      </c>
-      <c r="J187" t="n">
-        <v>3</v>
-      </c>
-      <c r="K187" t="s">
-        <v>50</v>
-      </c>
-      <c r="L187" t="n">
-        <v>3</v>
-      </c>
-      <c r="M187" t="s">
-        <v>51</v>
-      </c>
-      <c r="N187" t="s">
-        <v>26</v>
-      </c>
-      <c r="O187" t="n">
-        <v>5</v>
-      </c>
-      <c r="P187" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q187" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="n">
-        <v>373</v>
-      </c>
-      <c r="B188" t="b">
-        <v>0</v>
-      </c>
-      <c r="C188" t="s">
-        <v>17</v>
-      </c>
-      <c r="D188" t="s">
-        <v>18</v>
-      </c>
-      <c r="E188" t="n">
-        <v>2</v>
-      </c>
-      <c r="F188" t="n">
-        <v>1</v>
-      </c>
-      <c r="G188" t="n">
-        <v>2</v>
-      </c>
-      <c r="H188" t="s">
-        <v>35</v>
-      </c>
-      <c r="I188" t="n">
-        <v>8</v>
-      </c>
-      <c r="J188" t="n">
-        <v>3</v>
-      </c>
-      <c r="K188" t="s">
-        <v>53</v>
-      </c>
-      <c r="L188" t="n">
-        <v>1</v>
-      </c>
-      <c r="M188" t="s">
-        <v>28</v>
-      </c>
-      <c r="N188" t="s">
-        <v>29</v>
-      </c>
-      <c r="O188" t="n">
-        <v>4</v>
-      </c>
-      <c r="P188" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q188" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="n">
-        <v>374</v>
-      </c>
-      <c r="B189" t="b">
-        <v>0</v>
-      </c>
-      <c r="C189" t="s">
-        <v>17</v>
-      </c>
-      <c r="D189" t="s">
-        <v>18</v>
-      </c>
-      <c r="E189" t="n">
-        <v>2</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" t="n">
-        <v>2</v>
-      </c>
-      <c r="H189" t="s">
-        <v>35</v>
-      </c>
-      <c r="I189" t="n">
-        <v>8</v>
-      </c>
-      <c r="J189" t="n">
-        <v>3</v>
-      </c>
-      <c r="K189" t="s">
-        <v>53</v>
-      </c>
-      <c r="L189" t="n">
-        <v>2</v>
-      </c>
-      <c r="M189" t="s">
-        <v>28</v>
-      </c>
-      <c r="N189" t="s">
-        <v>29</v>
-      </c>
-      <c r="O189" t="n">
-        <v>4</v>
-      </c>
-      <c r="P189" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q189" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="n">
-        <v>375</v>
-      </c>
-      <c r="B190" t="b">
-        <v>0</v>
-      </c>
-      <c r="C190" t="s">
-        <v>17</v>
-      </c>
-      <c r="D190" t="s">
-        <v>18</v>
-      </c>
-      <c r="E190" t="n">
-        <v>2</v>
-      </c>
-      <c r="F190" t="n">
-        <v>1</v>
-      </c>
-      <c r="G190" t="n">
-        <v>2</v>
-      </c>
-      <c r="H190" t="s">
-        <v>35</v>
-      </c>
-      <c r="I190" t="n">
-        <v>8</v>
-      </c>
-      <c r="J190" t="n">
-        <v>3</v>
-      </c>
-      <c r="K190" t="s">
-        <v>53</v>
-      </c>
-      <c r="L190" t="n">
-        <v>3</v>
-      </c>
-      <c r="M190" t="s">
-        <v>28</v>
-      </c>
-      <c r="N190" t="s">
-        <v>29</v>
-      </c>
-      <c r="O190" t="n">
-        <v>4</v>
-      </c>
-      <c r="P190" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q190" t="n">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="n">
-        <v>379</v>
-      </c>
-      <c r="B191" t="b">
-        <v>0</v>
-      </c>
-      <c r="C191" t="s">
-        <v>17</v>
-      </c>
-      <c r="D191" t="s">
-        <v>18</v>
-      </c>
-      <c r="E191" t="n">
-        <v>2</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2</v>
-      </c>
-      <c r="G191" t="n">
-        <v>2</v>
-      </c>
-      <c r="H191" t="s">
-        <v>36</v>
-      </c>
-      <c r="I191" t="n">
-        <v>8</v>
-      </c>
-      <c r="J191" t="n">
-        <v>3</v>
-      </c>
-      <c r="K191" t="s">
-        <v>50</v>
-      </c>
-      <c r="L191" t="n">
-        <v>1</v>
-      </c>
-      <c r="M191" t="s">
-        <v>52</v>
-      </c>
-      <c r="N191" t="s">
-        <v>32</v>
-      </c>
-      <c r="O191" t="n">
-        <v>5</v>
-      </c>
-      <c r="P191" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q191" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="n">
-        <v>380</v>
-      </c>
-      <c r="B192" t="b">
-        <v>0</v>
-      </c>
-      <c r="C192" t="s">
-        <v>17</v>
-      </c>
-      <c r="D192" t="s">
-        <v>18</v>
-      </c>
-      <c r="E192" t="n">
-        <v>2</v>
-      </c>
-      <c r="F192" t="n">
-        <v>2</v>
-      </c>
-      <c r="G192" t="n">
-        <v>2</v>
-      </c>
-      <c r="H192" t="s">
-        <v>36</v>
-      </c>
-      <c r="I192" t="n">
-        <v>8</v>
-      </c>
-      <c r="J192" t="n">
-        <v>3</v>
-      </c>
-      <c r="K192" t="s">
-        <v>50</v>
-      </c>
-      <c r="L192" t="n">
-        <v>2</v>
-      </c>
-      <c r="M192" t="s">
-        <v>52</v>
-      </c>
-      <c r="N192" t="s">
-        <v>32</v>
-      </c>
-      <c r="O192" t="n">
-        <v>5</v>
-      </c>
-      <c r="P192" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q192" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="n">
-        <v>381</v>
-      </c>
-      <c r="B193" t="b">
-        <v>0</v>
-      </c>
-      <c r="C193" t="s">
-        <v>17</v>
-      </c>
-      <c r="D193" t="s">
-        <v>18</v>
-      </c>
-      <c r="E193" t="n">
-        <v>2</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="n">
-        <v>2</v>
-      </c>
-      <c r="H193" t="s">
-        <v>36</v>
-      </c>
-      <c r="I193" t="n">
-        <v>8</v>
-      </c>
-      <c r="J193" t="n">
-        <v>3</v>
-      </c>
-      <c r="K193" t="s">
-        <v>50</v>
-      </c>
-      <c r="L193" t="n">
-        <v>3</v>
-      </c>
-      <c r="M193" t="s">
-        <v>52</v>
-      </c>
-      <c r="N193" t="s">
-        <v>32</v>
-      </c>
-      <c r="O193" t="n">
-        <v>5</v>
-      </c>
-      <c r="P193" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q193" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="n">
-        <v>385</v>
-      </c>
-      <c r="B194" t="b">
-        <v>0</v>
-      </c>
-      <c r="C194" t="s">
-        <v>17</v>
-      </c>
-      <c r="D194" t="s">
-        <v>18</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" t="n">
-        <v>1</v>
-      </c>
-      <c r="G194" t="n">
-        <v>1</v>
-      </c>
-      <c r="H194" t="s">
-        <v>19</v>
-      </c>
-      <c r="I194" t="n">
-        <v>9</v>
-      </c>
-      <c r="J194" t="n">
-        <v>3</v>
-      </c>
-      <c r="K194" t="s">
-        <v>54</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
-      <c r="M194" t="s">
-        <v>55</v>
-      </c>
-      <c r="N194" t="s">
-        <v>22</v>
-      </c>
-      <c r="O194" t="n">
-        <v>5</v>
-      </c>
-      <c r="P194" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q194" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="n">
-        <v>386</v>
-      </c>
-      <c r="B195" t="b">
-        <v>0</v>
-      </c>
-      <c r="C195" t="s">
-        <v>17</v>
-      </c>
-      <c r="D195" t="s">
-        <v>18</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" t="n">
-        <v>1</v>
-      </c>
-      <c r="H195" t="s">
-        <v>19</v>
-      </c>
-      <c r="I195" t="n">
-        <v>9</v>
-      </c>
-      <c r="J195" t="n">
-        <v>3</v>
-      </c>
-      <c r="K195" t="s">
-        <v>54</v>
-      </c>
-      <c r="L195" t="n">
-        <v>2</v>
-      </c>
-      <c r="M195" t="s">
-        <v>55</v>
-      </c>
-      <c r="N195" t="s">
-        <v>22</v>
-      </c>
-      <c r="O195" t="n">
-        <v>5</v>
-      </c>
-      <c r="P195" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q195" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="n">
-        <v>387</v>
-      </c>
-      <c r="B196" t="b">
-        <v>0</v>
-      </c>
-      <c r="C196" t="s">
-        <v>17</v>
-      </c>
-      <c r="D196" t="s">
-        <v>18</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" t="s">
-        <v>19</v>
-      </c>
-      <c r="I196" t="n">
-        <v>9</v>
-      </c>
-      <c r="J196" t="n">
-        <v>3</v>
-      </c>
-      <c r="K196" t="s">
-        <v>54</v>
-      </c>
-      <c r="L196" t="n">
-        <v>3</v>
-      </c>
-      <c r="M196" t="s">
-        <v>55</v>
-      </c>
-      <c r="N196" t="s">
-        <v>22</v>
-      </c>
-      <c r="O196" t="n">
-        <v>5</v>
-      </c>
-      <c r="P196" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="n">
-        <v>391</v>
-      </c>
-      <c r="B197" t="b">
-        <v>0</v>
-      </c>
-      <c r="C197" t="s">
-        <v>17</v>
-      </c>
-      <c r="D197" t="s">
-        <v>18</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="s">
-        <v>23</v>
-      </c>
-      <c r="I197" t="n">
-        <v>9</v>
-      </c>
-      <c r="J197" t="n">
-        <v>3</v>
-      </c>
-      <c r="K197" t="s">
-        <v>50</v>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
-      </c>
-      <c r="M197" t="s">
-        <v>51</v>
-      </c>
-      <c r="N197" t="s">
-        <v>26</v>
-      </c>
-      <c r="O197" t="n">
-        <v>5</v>
-      </c>
-      <c r="P197" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q197" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="n">
-        <v>392</v>
-      </c>
-      <c r="B198" t="b">
-        <v>0</v>
-      </c>
-      <c r="C198" t="s">
-        <v>17</v>
-      </c>
-      <c r="D198" t="s">
-        <v>18</v>
-      </c>
-      <c r="E198" t="n">
-        <v>1</v>
-      </c>
-      <c r="F198" t="n">
-        <v>2</v>
-      </c>
-      <c r="G198" t="n">
-        <v>1</v>
-      </c>
-      <c r="H198" t="s">
-        <v>23</v>
-      </c>
-      <c r="I198" t="n">
-        <v>9</v>
-      </c>
-      <c r="J198" t="n">
-        <v>3</v>
-      </c>
-      <c r="K198" t="s">
-        <v>50</v>
-      </c>
-      <c r="L198" t="n">
-        <v>2</v>
-      </c>
-      <c r="M198" t="s">
-        <v>51</v>
-      </c>
-      <c r="N198" t="s">
-        <v>26</v>
-      </c>
-      <c r="O198" t="n">
-        <v>5</v>
-      </c>
-      <c r="P198" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q198" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="n">
-        <v>393</v>
-      </c>
-      <c r="B199" t="b">
-        <v>0</v>
-      </c>
-      <c r="C199" t="s">
-        <v>17</v>
-      </c>
-      <c r="D199" t="s">
-        <v>18</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1</v>
-      </c>
-      <c r="H199" t="s">
-        <v>23</v>
-      </c>
-      <c r="I199" t="n">
-        <v>9</v>
-      </c>
-      <c r="J199" t="n">
-        <v>3</v>
-      </c>
-      <c r="K199" t="s">
-        <v>50</v>
-      </c>
-      <c r="L199" t="n">
-        <v>3</v>
-      </c>
-      <c r="M199" t="s">
-        <v>51</v>
-      </c>
-      <c r="N199" t="s">
-        <v>26</v>
-      </c>
-      <c r="O199" t="n">
-        <v>5</v>
-      </c>
-      <c r="P199" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q199" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="n">
-        <v>397</v>
-      </c>
-      <c r="B200" t="b">
-        <v>0</v>
-      </c>
-      <c r="C200" t="s">
-        <v>17</v>
-      </c>
-      <c r="D200" t="s">
-        <v>18</v>
-      </c>
-      <c r="E200" t="n">
-        <v>2</v>
-      </c>
-      <c r="F200" t="n">
-        <v>1</v>
-      </c>
-      <c r="G200" t="n">
-        <v>1</v>
-      </c>
-      <c r="H200" t="s">
-        <v>27</v>
-      </c>
-      <c r="I200" t="n">
-        <v>9</v>
-      </c>
-      <c r="J200" t="n">
-        <v>3</v>
-      </c>
-      <c r="K200" t="s">
-        <v>54</v>
-      </c>
-      <c r="L200" t="n">
-        <v>1</v>
-      </c>
-      <c r="M200" t="s">
-        <v>47</v>
-      </c>
-      <c r="N200" t="s">
-        <v>29</v>
-      </c>
-      <c r="O200" t="n">
-        <v>3</v>
-      </c>
-      <c r="P200" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q200" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="n">
-        <v>398</v>
-      </c>
-      <c r="B201" t="b">
-        <v>0</v>
-      </c>
-      <c r="C201" t="s">
-        <v>17</v>
-      </c>
-      <c r="D201" t="s">
-        <v>18</v>
-      </c>
-      <c r="E201" t="n">
-        <v>2</v>
-      </c>
-      <c r="F201" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" t="n">
-        <v>1</v>
-      </c>
-      <c r="H201" t="s">
-        <v>27</v>
-      </c>
-      <c r="I201" t="n">
-        <v>9</v>
-      </c>
-      <c r="J201" t="n">
-        <v>3</v>
-      </c>
-      <c r="K201" t="s">
-        <v>54</v>
-      </c>
-      <c r="L201" t="n">
-        <v>2</v>
-      </c>
-      <c r="M201" t="s">
-        <v>47</v>
-      </c>
-      <c r="N201" t="s">
-        <v>29</v>
-      </c>
-      <c r="O201" t="n">
-        <v>3</v>
-      </c>
-      <c r="P201" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q201" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="n">
-        <v>399</v>
-      </c>
-      <c r="B202" t="b">
-        <v>0</v>
-      </c>
-      <c r="C202" t="s">
-        <v>17</v>
-      </c>
-      <c r="D202" t="s">
-        <v>18</v>
-      </c>
-      <c r="E202" t="n">
-        <v>2</v>
-      </c>
-      <c r="F202" t="n">
-        <v>1</v>
-      </c>
-      <c r="G202" t="n">
-        <v>1</v>
-      </c>
-      <c r="H202" t="s">
-        <v>27</v>
-      </c>
-      <c r="I202" t="n">
-        <v>9</v>
-      </c>
-      <c r="J202" t="n">
-        <v>3</v>
-      </c>
-      <c r="K202" t="s">
-        <v>54</v>
-      </c>
-      <c r="L202" t="n">
-        <v>3</v>
-      </c>
-      <c r="M202" t="s">
-        <v>47</v>
-      </c>
-      <c r="N202" t="s">
-        <v>29</v>
-      </c>
-      <c r="O202" t="n">
-        <v>3</v>
-      </c>
-      <c r="P202" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q202" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="n">
-        <v>403</v>
-      </c>
-      <c r="B203" t="b">
-        <v>0</v>
-      </c>
-      <c r="C203" t="s">
-        <v>17</v>
-      </c>
-      <c r="D203" t="s">
-        <v>18</v>
-      </c>
-      <c r="E203" t="n">
-        <v>2</v>
-      </c>
-      <c r="F203" t="n">
-        <v>2</v>
-      </c>
-      <c r="G203" t="n">
-        <v>1</v>
-      </c>
-      <c r="H203" t="s">
-        <v>30</v>
-      </c>
-      <c r="I203" t="n">
-        <v>9</v>
-      </c>
-      <c r="J203" t="n">
-        <v>3</v>
-      </c>
-      <c r="K203" t="s">
-        <v>50</v>
-      </c>
-      <c r="L203" t="n">
-        <v>1</v>
-      </c>
-      <c r="M203" t="s">
-        <v>52</v>
-      </c>
-      <c r="N203" t="s">
-        <v>32</v>
-      </c>
-      <c r="O203" t="n">
-        <v>5</v>
-      </c>
-      <c r="P203" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="n">
-        <v>404</v>
-      </c>
-      <c r="B204" t="b">
-        <v>0</v>
-      </c>
-      <c r="C204" t="s">
-        <v>17</v>
-      </c>
-      <c r="D204" t="s">
-        <v>18</v>
-      </c>
-      <c r="E204" t="n">
-        <v>2</v>
-      </c>
-      <c r="F204" t="n">
-        <v>2</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="s">
-        <v>30</v>
-      </c>
-      <c r="I204" t="n">
-        <v>9</v>
-      </c>
-      <c r="J204" t="n">
-        <v>3</v>
-      </c>
-      <c r="K204" t="s">
-        <v>50</v>
-      </c>
-      <c r="L204" t="n">
-        <v>2</v>
-      </c>
-      <c r="M204" t="s">
-        <v>52</v>
-      </c>
-      <c r="N204" t="s">
-        <v>32</v>
-      </c>
-      <c r="O204" t="n">
-        <v>5</v>
-      </c>
-      <c r="P204" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q204" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="n">
-        <v>405</v>
-      </c>
-      <c r="B205" t="b">
-        <v>0</v>
-      </c>
-      <c r="C205" t="s">
-        <v>17</v>
-      </c>
-      <c r="D205" t="s">
-        <v>18</v>
-      </c>
-      <c r="E205" t="n">
-        <v>2</v>
-      </c>
-      <c r="F205" t="n">
-        <v>2</v>
-      </c>
-      <c r="G205" t="n">
-        <v>1</v>
-      </c>
-      <c r="H205" t="s">
-        <v>30</v>
-      </c>
-      <c r="I205" t="n">
-        <v>9</v>
-      </c>
-      <c r="J205" t="n">
-        <v>3</v>
-      </c>
-      <c r="K205" t="s">
-        <v>50</v>
-      </c>
-      <c r="L205" t="n">
-        <v>3</v>
-      </c>
-      <c r="M205" t="s">
-        <v>52</v>
-      </c>
-      <c r="N205" t="s">
-        <v>32</v>
-      </c>
-      <c r="O205" t="n">
-        <v>5</v>
-      </c>
-      <c r="P205" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q205" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="n">
-        <v>409</v>
-      </c>
-      <c r="B206" t="b">
-        <v>0</v>
-      </c>
-      <c r="C206" t="s">
-        <v>17</v>
-      </c>
-      <c r="D206" t="s">
-        <v>18</v>
-      </c>
-      <c r="E206" t="n">
-        <v>1</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1</v>
-      </c>
-      <c r="G206" t="n">
-        <v>2</v>
-      </c>
-      <c r="H206" t="s">
-        <v>33</v>
-      </c>
-      <c r="I206" t="n">
-        <v>9</v>
-      </c>
-      <c r="J206" t="n">
-        <v>3</v>
-      </c>
-      <c r="K206" t="s">
-        <v>54</v>
-      </c>
-      <c r="L206" t="n">
-        <v>1</v>
-      </c>
-      <c r="M206" t="s">
-        <v>55</v>
-      </c>
-      <c r="N206" t="s">
-        <v>22</v>
-      </c>
-      <c r="O206" t="n">
-        <v>5</v>
-      </c>
-      <c r="P206" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q206" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="n">
-        <v>410</v>
-      </c>
-      <c r="B207" t="b">
-        <v>0</v>
-      </c>
-      <c r="C207" t="s">
-        <v>17</v>
-      </c>
-      <c r="D207" t="s">
-        <v>18</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" t="n">
-        <v>2</v>
-      </c>
-      <c r="H207" t="s">
-        <v>33</v>
-      </c>
-      <c r="I207" t="n">
-        <v>9</v>
-      </c>
-      <c r="J207" t="n">
-        <v>3</v>
-      </c>
-      <c r="K207" t="s">
-        <v>54</v>
-      </c>
-      <c r="L207" t="n">
-        <v>2</v>
-      </c>
-      <c r="M207" t="s">
-        <v>55</v>
-      </c>
-      <c r="N207" t="s">
-        <v>22</v>
-      </c>
-      <c r="O207" t="n">
-        <v>5</v>
-      </c>
-      <c r="P207" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q207" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="n">
-        <v>411</v>
-      </c>
-      <c r="B208" t="b">
-        <v>0</v>
-      </c>
-      <c r="C208" t="s">
-        <v>17</v>
-      </c>
-      <c r="D208" t="s">
-        <v>18</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="n">
-        <v>2</v>
-      </c>
-      <c r="H208" t="s">
-        <v>33</v>
-      </c>
-      <c r="I208" t="n">
-        <v>9</v>
-      </c>
-      <c r="J208" t="n">
-        <v>3</v>
-      </c>
-      <c r="K208" t="s">
-        <v>54</v>
-      </c>
-      <c r="L208" t="n">
-        <v>3</v>
-      </c>
-      <c r="M208" t="s">
-        <v>55</v>
-      </c>
-      <c r="N208" t="s">
-        <v>22</v>
-      </c>
-      <c r="O208" t="n">
-        <v>5</v>
-      </c>
-      <c r="P208" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q208" t="n">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="n">
-        <v>415</v>
-      </c>
-      <c r="B209" t="b">
-        <v>0</v>
-      </c>
-      <c r="C209" t="s">
-        <v>17</v>
-      </c>
-      <c r="D209" t="s">
-        <v>18</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" t="n">
-        <v>2</v>
-      </c>
-      <c r="G209" t="n">
-        <v>2</v>
-      </c>
-      <c r="H209" t="s">
-        <v>34</v>
-      </c>
-      <c r="I209" t="n">
-        <v>9</v>
-      </c>
-      <c r="J209" t="n">
-        <v>3</v>
-      </c>
-      <c r="K209" t="s">
-        <v>50</v>
-      </c>
-      <c r="L209" t="n">
-        <v>1</v>
-      </c>
-      <c r="M209" t="s">
-        <v>51</v>
-      </c>
-      <c r="N209" t="s">
-        <v>26</v>
-      </c>
-      <c r="O209" t="n">
-        <v>5</v>
-      </c>
-      <c r="P209" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q209" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="n">
-        <v>416</v>
-      </c>
-      <c r="B210" t="b">
-        <v>0</v>
-      </c>
-      <c r="C210" t="s">
-        <v>17</v>
-      </c>
-      <c r="D210" t="s">
-        <v>18</v>
-      </c>
-      <c r="E210" t="n">
-        <v>1</v>
-      </c>
-      <c r="F210" t="n">
-        <v>2</v>
-      </c>
-      <c r="G210" t="n">
-        <v>2</v>
-      </c>
-      <c r="H210" t="s">
-        <v>34</v>
-      </c>
-      <c r="I210" t="n">
-        <v>9</v>
-      </c>
-      <c r="J210" t="n">
-        <v>3</v>
-      </c>
-      <c r="K210" t="s">
-        <v>50</v>
-      </c>
-      <c r="L210" t="n">
-        <v>2</v>
-      </c>
-      <c r="M210" t="s">
-        <v>51</v>
-      </c>
-      <c r="N210" t="s">
-        <v>26</v>
-      </c>
-      <c r="O210" t="n">
-        <v>5</v>
-      </c>
-      <c r="P210" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q210" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="n">
-        <v>417</v>
-      </c>
-      <c r="B211" t="b">
-        <v>0</v>
-      </c>
-      <c r="C211" t="s">
-        <v>17</v>
-      </c>
-      <c r="D211" t="s">
-        <v>18</v>
-      </c>
-      <c r="E211" t="n">
-        <v>1</v>
-      </c>
-      <c r="F211" t="n">
-        <v>2</v>
-      </c>
-      <c r="G211" t="n">
-        <v>2</v>
-      </c>
-      <c r="H211" t="s">
-        <v>34</v>
-      </c>
-      <c r="I211" t="n">
-        <v>9</v>
-      </c>
-      <c r="J211" t="n">
-        <v>3</v>
-      </c>
-      <c r="K211" t="s">
-        <v>50</v>
-      </c>
-      <c r="L211" t="n">
-        <v>3</v>
-      </c>
-      <c r="M211" t="s">
-        <v>51</v>
-      </c>
-      <c r="N211" t="s">
-        <v>26</v>
-      </c>
-      <c r="O211" t="n">
-        <v>5</v>
-      </c>
-      <c r="P211" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>421</v>
-      </c>
-      <c r="B212" t="b">
-        <v>0</v>
-      </c>
-      <c r="C212" t="s">
-        <v>17</v>
-      </c>
-      <c r="D212" t="s">
-        <v>18</v>
-      </c>
-      <c r="E212" t="n">
-        <v>2</v>
-      </c>
-      <c r="F212" t="n">
-        <v>1</v>
-      </c>
-      <c r="G212" t="n">
-        <v>2</v>
-      </c>
-      <c r="H212" t="s">
-        <v>35</v>
-      </c>
-      <c r="I212" t="n">
-        <v>9</v>
-      </c>
-      <c r="J212" t="n">
-        <v>3</v>
-      </c>
-      <c r="K212" t="s">
-        <v>54</v>
-      </c>
-      <c r="L212" t="n">
-        <v>1</v>
-      </c>
-      <c r="M212" t="s">
-        <v>47</v>
-      </c>
-      <c r="N212" t="s">
-        <v>29</v>
-      </c>
-      <c r="O212" t="n">
-        <v>3</v>
-      </c>
-      <c r="P212" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q212" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="n">
-        <v>422</v>
-      </c>
-      <c r="B213" t="b">
-        <v>0</v>
-      </c>
-      <c r="C213" t="s">
-        <v>17</v>
-      </c>
-      <c r="D213" t="s">
-        <v>18</v>
-      </c>
-      <c r="E213" t="n">
-        <v>2</v>
-      </c>
-      <c r="F213" t="n">
-        <v>1</v>
-      </c>
-      <c r="G213" t="n">
-        <v>2</v>
-      </c>
-      <c r="H213" t="s">
-        <v>35</v>
-      </c>
-      <c r="I213" t="n">
-        <v>9</v>
-      </c>
-      <c r="J213" t="n">
-        <v>3</v>
-      </c>
-      <c r="K213" t="s">
-        <v>54</v>
-      </c>
-      <c r="L213" t="n">
-        <v>2</v>
-      </c>
-      <c r="M213" t="s">
-        <v>47</v>
-      </c>
-      <c r="N213" t="s">
-        <v>29</v>
-      </c>
-      <c r="O213" t="n">
-        <v>3</v>
-      </c>
-      <c r="P213" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q213" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="n">
-        <v>423</v>
-      </c>
-      <c r="B214" t="b">
-        <v>0</v>
-      </c>
-      <c r="C214" t="s">
-        <v>17</v>
-      </c>
-      <c r="D214" t="s">
-        <v>18</v>
-      </c>
-      <c r="E214" t="n">
-        <v>2</v>
-      </c>
-      <c r="F214" t="n">
-        <v>1</v>
-      </c>
-      <c r="G214" t="n">
-        <v>2</v>
-      </c>
-      <c r="H214" t="s">
-        <v>35</v>
-      </c>
-      <c r="I214" t="n">
-        <v>9</v>
-      </c>
-      <c r="J214" t="n">
-        <v>3</v>
-      </c>
-      <c r="K214" t="s">
-        <v>54</v>
-      </c>
-      <c r="L214" t="n">
-        <v>3</v>
-      </c>
-      <c r="M214" t="s">
-        <v>47</v>
-      </c>
-      <c r="N214" t="s">
-        <v>29</v>
-      </c>
-      <c r="O214" t="n">
-        <v>3</v>
-      </c>
-      <c r="P214" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q214" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="n">
-        <v>427</v>
-      </c>
-      <c r="B215" t="b">
-        <v>0</v>
-      </c>
-      <c r="C215" t="s">
-        <v>17</v>
-      </c>
-      <c r="D215" t="s">
-        <v>18</v>
-      </c>
-      <c r="E215" t="n">
-        <v>2</v>
-      </c>
-      <c r="F215" t="n">
-        <v>2</v>
-      </c>
-      <c r="G215" t="n">
-        <v>2</v>
-      </c>
-      <c r="H215" t="s">
-        <v>36</v>
-      </c>
-      <c r="I215" t="n">
-        <v>9</v>
-      </c>
-      <c r="J215" t="n">
-        <v>3</v>
-      </c>
-      <c r="K215" t="s">
-        <v>50</v>
-      </c>
-      <c r="L215" t="n">
-        <v>1</v>
-      </c>
-      <c r="M215" t="s">
-        <v>52</v>
-      </c>
-      <c r="N215" t="s">
-        <v>32</v>
-      </c>
-      <c r="O215" t="n">
-        <v>5</v>
-      </c>
-      <c r="P215" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q215" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="n">
-        <v>428</v>
-      </c>
-      <c r="B216" t="b">
-        <v>0</v>
-      </c>
-      <c r="C216" t="s">
-        <v>17</v>
-      </c>
-      <c r="D216" t="s">
-        <v>18</v>
-      </c>
-      <c r="E216" t="n">
-        <v>2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>2</v>
-      </c>
-      <c r="G216" t="n">
-        <v>2</v>
-      </c>
-      <c r="H216" t="s">
-        <v>36</v>
-      </c>
-      <c r="I216" t="n">
-        <v>9</v>
-      </c>
-      <c r="J216" t="n">
-        <v>3</v>
-      </c>
-      <c r="K216" t="s">
-        <v>50</v>
-      </c>
-      <c r="L216" t="n">
-        <v>2</v>
-      </c>
-      <c r="M216" t="s">
-        <v>52</v>
-      </c>
-      <c r="N216" t="s">
-        <v>32</v>
-      </c>
-      <c r="O216" t="n">
-        <v>5</v>
-      </c>
-      <c r="P216" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q216" t="n">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="n">
-        <v>429</v>
-      </c>
-      <c r="B217" t="b">
-        <v>0</v>
-      </c>
-      <c r="C217" t="s">
-        <v>17</v>
-      </c>
-      <c r="D217" t="s">
-        <v>18</v>
-      </c>
-      <c r="E217" t="n">
-        <v>2</v>
-      </c>
-      <c r="F217" t="n">
-        <v>2</v>
-      </c>
-      <c r="G217" t="n">
-        <v>2</v>
-      </c>
-      <c r="H217" t="s">
-        <v>36</v>
-      </c>
-      <c r="I217" t="n">
-        <v>9</v>
-      </c>
-      <c r="J217" t="n">
-        <v>3</v>
-      </c>
-      <c r="K217" t="s">
-        <v>50</v>
-      </c>
-      <c r="L217" t="n">
-        <v>3</v>
-      </c>
-      <c r="M217" t="s">
-        <v>52</v>
-      </c>
-      <c r="N217" t="s">
-        <v>32</v>
-      </c>
-      <c r="O217" t="n">
-        <v>5</v>
-      </c>
-      <c r="P217" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q217" t="n">
-        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
+++ b/Results/Results.out/Bovines/Data/reg_out_bv_lon_sample.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">loop.iter</t>
   </si>
@@ -74,43 +74,43 @@
     <t xml:space="preserve">1.1.1.1.1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1671, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+    <t xml:space="preserve">c(16, 17, 18, 19, 31, 32, 33, 34, 35, 51, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1670, 1671, 1771, 1772, 1773, 1774, 1787, 1788, 1789, 1790, 1792, 1793, 1794, 1795, 1888, 2049, 2050, 2051, 2052, 2053, 2227, 2229, 2231, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e12", "e15", "e19", "e34", "e369", "e398", "e427", "e460", "e505")</t>
+    <t xml:space="preserve">c("e5", "e9", "e12", "e15", "e19", "e34", "e369", "e394", "e398", "e427", "e460", "e497", "e505")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1747, 1748, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 78, 79, 80, 81, 82, 122, 123, 124, 125, 183, 184, 185, 186, 1749, 1890, 1891, 1892, 2006, 2007, 2008, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e20", "e31", "e48", "e388", "e428", "e452")</t>
+    <t xml:space="preserve">c("e10", "e20", "e31", "e48", "e388", "e428", "e452", "e496")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1979, 1980, 2144, 2145, 2146, 2147, 2148)</t>
+    <t xml:space="preserve">c(1828, 1829, 1830, 1831, 1832, 1833, 1834, 1978, 1979, 1980, 2144, 2145, 2146, 2147, 2148, 2230, 2232)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e407", "e408", "e445", "e476")</t>
+    <t xml:space="preserve">c("e407", "e408", "e445", "e476", "e497")</t>
   </si>
   <si>
     <t xml:space="preserve">1.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 1645, 1646, 1647, 1648, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2321, 2322, 2323)</t>
+    <t xml:space="preserve">c(100, 101, 102, 103, 104, 105, 106, 107, 108, 109, 110, 111, 112, 113, 114, 115, 116, 117, 118, 229, 230, 231, 232, 233, 234, 235, 236, 1645, 1646, 1647, 1648, 1676, 1677, 1716, 1717, 1718, 1866, 1867, 2137, 2138, 2139, 2211, 2212, 2213, 2222, 2223, 2225, 2226, 2296, 2297, 2298, 2299, 2320, 2321, 2322, 2323)</t>
   </si>
   <si>
-    <t xml:space="preserve">c("e26", "e27", "e28", "e29", "e364", "e372", "e493", "e514", "e519")</t>
+    <t xml:space="preserve">c("e26", "e27", "e28", "e29", "e56", "e57", "e364", "e372", "e381", "e421", "e474", "e493", "e496", "e514", "e519")</t>
   </si>
   <si>
     <t xml:space="preserve">2.1.1.1.1.1</t>
@@ -125,37 +125,67 @@
     <t xml:space="preserve">2.1.1.1.2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + Met_bw_kg + adg_kg_day + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + milk_prod_kg_d + adg_kg_day + adg_kg_day.sqd</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + BW_frac_Mat</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + Met_bw_kg + adg_kg_day + milk_prod_kg_d + adg_kg_day.sqd</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + ADF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + CP_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1747, 1748, 1749, 1890, 1891, 1892)</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + Ash_nutrition</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + CP_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">c(16, 17, 18, 19, 31, 32, 33, 34, 35, 58, 59, 60, 61, 74, 75, 76, 77, 133, 134, 135, 136, 137, 1670, 1671, 1771, 1772, 1773, 1774, 1888, 2049, 2050, 2051, 2052, 2053, 2227, 2229, 2231, 2262)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + adg_kg_day.sqd + EE_nutrition</t>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + Ash_nutrition + milk_prod_kg_d</t>
   </si>
   <si>
-    <t xml:space="preserve">c(51, 58, 59, 60, 61, 74, 75, 76, 77, 1671, 1888, 2049, 2050, 2051, 2052, 2053, 2262)</t>
+    <t xml:space="preserve">c(41, 42, 43, 44, 78, 79, 80, 81, 82, 122, 123, 124, 125, 1749, 1890, 1891, 1892, 2006, 2007, 2008, 2221, 2224)</t>
   </si>
   <si>
-    <t xml:space="preserve">feed_intake_g_d ~ Met_bw_kg + BW_frac_Mat + bw_kg + adg_kg_day + NDF_nutrition + milk_prod_kg_d</t>
+    <t xml:space="preserve">c(115, 116, 117, 118, 229, 230, 231, 232, 233, 234, 235, 236, 1645, 1646, 1647, 1648, 1676, 1677, 1716, 1717, 1718, 1866, 1867, 2137, 2138, 2139, 2211, 2212, 2213, 2222, 2223, 2225, 2226, 2296, 2297, 2298, 2299, 2320, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + NDF_nutrition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + EE_nutrition + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(78, 79, 80, 81, 82, 122, 123, 124, 125, 1749, 1890, 1891, 1892, 2006, 2007, 2008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c(115, 116, 117, 118, 229, 230, 231, 232, 233, 234, 235, 236, 1676, 1677, 2211, 2212, 2213, 2296, 2297, 2298, 2299, 2320, 2321, 2322, 2323)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + Ash_nutrition.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + Ash_nutrition.cbd + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + NDF_nutrition.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + EE_nutrition.cbd + milk_prod_kg_d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ bw_kg + adg_kg_day + adg_kg_day.sqd + CP_nutrition.cbd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">feed_intake_g_d ~ BW_frac_Mat + adg_kg_day + NDF_nutrition.cbd + milk_prod_kg_d</t>
   </si>
 </sst>
 </file>
@@ -581,13 +611,13 @@
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q2" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3">
@@ -634,13 +664,13 @@
         <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="4">
@@ -687,13 +717,13 @@
         <v>22</v>
       </c>
       <c r="O4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q4" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5">
@@ -740,13 +770,13 @@
         <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q5" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
@@ -793,13 +823,13 @@
         <v>26</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
@@ -846,13 +876,13 @@
         <v>26</v>
       </c>
       <c r="O7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q7" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
@@ -899,13 +929,13 @@
         <v>29</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9">
@@ -952,13 +982,13 @@
         <v>29</v>
       </c>
       <c r="O9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q9" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -1005,13 +1035,13 @@
         <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -1058,13 +1088,13 @@
         <v>32</v>
       </c>
       <c r="O11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P11" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q11" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="12">
@@ -1111,13 +1141,13 @@
         <v>32</v>
       </c>
       <c r="O12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P12" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q12" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="13">
@@ -1164,13 +1194,13 @@
         <v>32</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P13" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q13" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="14">
@@ -1217,13 +1247,13 @@
         <v>22</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P14" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q14" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="15">
@@ -1270,13 +1300,13 @@
         <v>22</v>
       </c>
       <c r="O15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P15" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q15" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="16">
@@ -1323,13 +1353,13 @@
         <v>22</v>
       </c>
       <c r="O16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P16" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q16" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="17">
@@ -1376,13 +1406,13 @@
         <v>26</v>
       </c>
       <c r="O17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q17" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18">
@@ -1429,13 +1459,13 @@
         <v>26</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q18" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
@@ -1482,13 +1512,13 @@
         <v>26</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
@@ -1535,13 +1565,13 @@
         <v>29</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q20" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21">
@@ -1588,13 +1618,13 @@
         <v>29</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q21" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -1641,13 +1671,13 @@
         <v>29</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q22" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23">
@@ -1694,13 +1724,13 @@
         <v>32</v>
       </c>
       <c r="O23" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P23" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q23" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="24">
@@ -1747,13 +1777,13 @@
         <v>32</v>
       </c>
       <c r="O24" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P24" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q24" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="25">
@@ -1800,13 +1830,13 @@
         <v>32</v>
       </c>
       <c r="O25" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P25" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q25" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="26">
@@ -1853,13 +1883,13 @@
         <v>22</v>
       </c>
       <c r="O26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P26" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q26" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27">
@@ -1906,13 +1936,13 @@
         <v>22</v>
       </c>
       <c r="O27" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P27" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q27" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="28">
@@ -1959,13 +1989,13 @@
         <v>22</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P28" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q28" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29">
@@ -2000,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2012,13 +2042,13 @@
         <v>26</v>
       </c>
       <c r="O29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P29" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q29" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="30">
@@ -2053,7 +2083,7 @@
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2065,13 +2095,13 @@
         <v>26</v>
       </c>
       <c r="O30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P30" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q30" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31">
@@ -2106,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L31" t="n">
         <v>3</v>
@@ -2118,13 +2148,13 @@
         <v>26</v>
       </c>
       <c r="O31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P31" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q31" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="32">
@@ -2171,13 +2201,13 @@
         <v>29</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q32" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="33">
@@ -2224,13 +2254,13 @@
         <v>29</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q33" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34">
@@ -2277,13 +2307,13 @@
         <v>29</v>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P34" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q34" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35">
@@ -2318,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2330,13 +2360,13 @@
         <v>32</v>
       </c>
       <c r="O35" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P35" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q35" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="36">
@@ -2371,7 +2401,7 @@
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2383,13 +2413,13 @@
         <v>32</v>
       </c>
       <c r="O36" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P36" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q36" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="37">
@@ -2424,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -2436,13 +2466,13 @@
         <v>32</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P37" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q37" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="38">
@@ -2489,13 +2519,13 @@
         <v>22</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P38" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q38" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="39">
@@ -2542,13 +2572,13 @@
         <v>22</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P39" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q39" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="40">
@@ -2595,13 +2625,13 @@
         <v>22</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P40" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q40" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="41">
@@ -2636,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2648,13 +2678,13 @@
         <v>26</v>
       </c>
       <c r="O41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P41" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q41" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42">
@@ -2689,7 +2719,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2701,13 +2731,13 @@
         <v>26</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q42" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43">
@@ -2742,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L43" t="n">
         <v>3</v>
@@ -2754,13 +2784,13 @@
         <v>26</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P43" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q43" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44">
@@ -2807,13 +2837,13 @@
         <v>29</v>
       </c>
       <c r="O44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P44" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q44" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
@@ -2860,13 +2890,13 @@
         <v>29</v>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q45" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46">
@@ -2913,13 +2943,13 @@
         <v>29</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P46" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q46" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47">
@@ -2954,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -2966,13 +2996,13 @@
         <v>32</v>
       </c>
       <c r="O47" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P47" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q47" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="48">
@@ -3007,7 +3037,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L48" t="n">
         <v>2</v>
@@ -3019,13 +3049,13 @@
         <v>32</v>
       </c>
       <c r="O48" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P48" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q48" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="49">
@@ -3060,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -3072,13 +3102,13 @@
         <v>32</v>
       </c>
       <c r="O49" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P49" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q49" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="50">
@@ -3113,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3125,13 +3155,13 @@
         <v>22</v>
       </c>
       <c r="O50" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P50" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q50" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="51">
@@ -3166,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L51" t="n">
         <v>2</v>
@@ -3178,13 +3208,13 @@
         <v>22</v>
       </c>
       <c r="O51" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P51" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q51" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="52">
@@ -3219,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -3231,13 +3261,13 @@
         <v>22</v>
       </c>
       <c r="O52" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P52" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q52" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53">
@@ -3272,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3284,13 +3314,13 @@
         <v>26</v>
       </c>
       <c r="O53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P53" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q53" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54">
@@ -3325,7 +3355,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
         <v>2</v>
@@ -3337,13 +3367,13 @@
         <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P54" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q54" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55">
@@ -3378,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3390,13 +3420,13 @@
         <v>26</v>
       </c>
       <c r="O55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P55" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q55" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="56">
@@ -3431,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3443,13 +3473,13 @@
         <v>29</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P56" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q56" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57">
@@ -3484,7 +3514,7 @@
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3496,13 +3526,13 @@
         <v>29</v>
       </c>
       <c r="O57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P57" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q57" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58">
@@ -3537,7 +3567,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L58" t="n">
         <v>3</v>
@@ -3549,13 +3579,13 @@
         <v>29</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q58" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59">
@@ -3590,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -3602,13 +3632,13 @@
         <v>32</v>
       </c>
       <c r="O59" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P59" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q59" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="60">
@@ -3643,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L60" t="n">
         <v>2</v>
@@ -3655,13 +3685,13 @@
         <v>32</v>
       </c>
       <c r="O60" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P60" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q60" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="61">
@@ -3696,7 +3726,7 @@
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L61" t="n">
         <v>3</v>
@@ -3708,13 +3738,13 @@
         <v>32</v>
       </c>
       <c r="O61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P61" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q61" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="62">
@@ -3749,7 +3779,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -3761,13 +3791,13 @@
         <v>22</v>
       </c>
       <c r="O62" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P62" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q62" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="63">
@@ -3802,7 +3832,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -3814,13 +3844,13 @@
         <v>22</v>
       </c>
       <c r="O63" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P63" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q63" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="64">
@@ -3855,7 +3885,7 @@
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L64" t="n">
         <v>3</v>
@@ -3867,13 +3897,13 @@
         <v>22</v>
       </c>
       <c r="O64" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P64" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q64" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65">
@@ -3908,7 +3938,7 @@
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -3920,13 +3950,13 @@
         <v>26</v>
       </c>
       <c r="O65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P65" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q65" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="66">
@@ -3961,7 +3991,7 @@
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L66" t="n">
         <v>2</v>
@@ -3973,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="O66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P66" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q66" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="67">
@@ -4014,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L67" t="n">
         <v>3</v>
@@ -4026,13 +4056,13 @@
         <v>26</v>
       </c>
       <c r="O67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P67" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="Q67" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68">
@@ -4067,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4079,13 +4109,13 @@
         <v>29</v>
       </c>
       <c r="O68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P68" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q68" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69">
@@ -4120,7 +4150,7 @@
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L69" t="n">
         <v>2</v>
@@ -4132,13 +4162,13 @@
         <v>29</v>
       </c>
       <c r="O69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P69" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q69" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70">
@@ -4173,7 +4203,7 @@
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L70" t="n">
         <v>3</v>
@@ -4185,13 +4215,13 @@
         <v>29</v>
       </c>
       <c r="O70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P70" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q70" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71">
@@ -4226,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4238,13 +4268,13 @@
         <v>32</v>
       </c>
       <c r="O71" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P71" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q71" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="72">
@@ -4279,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L72" t="n">
         <v>2</v>
@@ -4291,13 +4321,13 @@
         <v>32</v>
       </c>
       <c r="O72" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P72" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q72" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="73">
@@ -4332,7 +4362,7 @@
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L73" t="n">
         <v>3</v>
@@ -4344,13 +4374,13 @@
         <v>32</v>
       </c>
       <c r="O73" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P73" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q73" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="74">
@@ -4385,7 +4415,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4397,13 +4427,13 @@
         <v>22</v>
       </c>
       <c r="O74" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P74" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q74" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75">
@@ -4438,7 +4468,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L75" t="n">
         <v>2</v>
@@ -4450,13 +4480,13 @@
         <v>22</v>
       </c>
       <c r="O75" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P75" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q75" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76">
@@ -4491,7 +4521,7 @@
         <v>2</v>
       </c>
       <c r="K76" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L76" t="n">
         <v>3</v>
@@ -4503,13 +4533,13 @@
         <v>22</v>
       </c>
       <c r="O76" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P76" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q76" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="77">
@@ -4544,25 +4574,25 @@
         <v>2</v>
       </c>
       <c r="K77" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L77" t="n">
         <v>1</v>
       </c>
       <c r="M77" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N77" t="s">
         <v>26</v>
       </c>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P77" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q77" t="n">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="78">
@@ -4597,25 +4627,25 @@
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N78" t="s">
         <v>26</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P78" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q78" t="n">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79">
@@ -4650,25 +4680,25 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L79" t="n">
         <v>3</v>
       </c>
       <c r="M79" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N79" t="s">
         <v>26</v>
       </c>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P79" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q79" t="n">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="80">
@@ -4703,7 +4733,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -4715,13 +4745,13 @@
         <v>29</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P80" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q80" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81">
@@ -4756,7 +4786,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L81" t="n">
         <v>2</v>
@@ -4768,13 +4798,13 @@
         <v>29</v>
       </c>
       <c r="O81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P81" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q81" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="82">
@@ -4809,7 +4839,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L82" t="n">
         <v>3</v>
@@ -4821,13 +4851,13 @@
         <v>29</v>
       </c>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P82" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q82" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="83">
@@ -4862,7 +4892,7 @@
         <v>2</v>
       </c>
       <c r="K83" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -4874,13 +4904,13 @@
         <v>32</v>
       </c>
       <c r="O83" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P83" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q83" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="84">
@@ -4915,7 +4945,7 @@
         <v>2</v>
       </c>
       <c r="K84" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
@@ -4927,13 +4957,13 @@
         <v>32</v>
       </c>
       <c r="O84" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P84" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q84" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="85">
@@ -4968,7 +4998,7 @@
         <v>2</v>
       </c>
       <c r="K85" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L85" t="n">
         <v>3</v>
@@ -4980,13 +5010,13 @@
         <v>32</v>
       </c>
       <c r="O85" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P85" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q85" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="86">
@@ -5021,7 +5051,7 @@
         <v>2</v>
       </c>
       <c r="K86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5033,13 +5063,13 @@
         <v>22</v>
       </c>
       <c r="O86" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P86" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q86" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="87">
@@ -5074,7 +5104,7 @@
         <v>2</v>
       </c>
       <c r="K87" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L87" t="n">
         <v>2</v>
@@ -5086,13 +5116,13 @@
         <v>22</v>
       </c>
       <c r="O87" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P87" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q87" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="88">
@@ -5127,7 +5157,7 @@
         <v>2</v>
       </c>
       <c r="K88" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L88" t="n">
         <v>3</v>
@@ -5139,13 +5169,13 @@
         <v>22</v>
       </c>
       <c r="O88" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="P88" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="Q88" t="n">
-        <v>306</v>
+        <v>446</v>
       </c>
     </row>
     <row r="89">
@@ -5180,25 +5210,25 @@
         <v>2</v>
       </c>
       <c r="K89" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
       </c>
       <c r="M89" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N89" t="s">
         <v>26</v>
       </c>
       <c r="O89" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P89" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q89" t="n">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90">
@@ -5233,25 +5263,25 @@
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L90" t="n">
         <v>2</v>
       </c>
       <c r="M90" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N90" t="s">
         <v>26</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P90" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q90" t="n">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="91">
@@ -5286,25 +5316,25 @@
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L91" t="n">
         <v>3</v>
       </c>
       <c r="M91" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="N91" t="s">
         <v>26</v>
       </c>
       <c r="O91" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P91" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="Q91" t="n">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92">
@@ -5339,7 +5369,7 @@
         <v>2</v>
       </c>
       <c r="K92" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -5351,13 +5381,13 @@
         <v>29</v>
       </c>
       <c r="O92" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P92" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q92" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="93">
@@ -5392,7 +5422,7 @@
         <v>2</v>
       </c>
       <c r="K93" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L93" t="n">
         <v>2</v>
@@ -5404,13 +5434,13 @@
         <v>29</v>
       </c>
       <c r="O93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P93" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q93" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94">
@@ -5445,7 +5475,7 @@
         <v>2</v>
       </c>
       <c r="K94" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L94" t="n">
         <v>3</v>
@@ -5457,13 +5487,13 @@
         <v>29</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P94" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q94" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="95">
@@ -5498,7 +5528,7 @@
         <v>2</v>
       </c>
       <c r="K95" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -5510,13 +5540,13 @@
         <v>32</v>
       </c>
       <c r="O95" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P95" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q95" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="96">
@@ -5551,7 +5581,7 @@
         <v>2</v>
       </c>
       <c r="K96" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L96" t="n">
         <v>2</v>
@@ -5563,13 +5593,13 @@
         <v>32</v>
       </c>
       <c r="O96" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P96" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q96" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="97">
@@ -5604,7 +5634,7 @@
         <v>2</v>
       </c>
       <c r="K97" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L97" t="n">
         <v>3</v>
@@ -5616,13 +5646,13 @@
         <v>32</v>
       </c>
       <c r="O97" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="P97" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="Q97" t="n">
-        <v>633</v>
+        <v>837</v>
       </c>
     </row>
     <row r="98">
@@ -5663,19 +5693,19 @@
         <v>1</v>
       </c>
       <c r="M98" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N98" t="s">
         <v>22</v>
       </c>
       <c r="O98" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P98" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q98" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="99">
@@ -5716,19 +5746,19 @@
         <v>2</v>
       </c>
       <c r="M99" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N99" t="s">
         <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P99" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q99" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="100">
@@ -5769,19 +5799,19 @@
         <v>3</v>
       </c>
       <c r="M100" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N100" t="s">
         <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P100" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q100" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="101">
@@ -5816,25 +5846,25 @@
         <v>2</v>
       </c>
       <c r="K101" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
       </c>
       <c r="M101" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N101" t="s">
         <v>26</v>
       </c>
       <c r="O101" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P101" t="n">
         <v>22</v>
       </c>
       <c r="Q101" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="102">
@@ -5869,25 +5899,25 @@
         <v>2</v>
       </c>
       <c r="K102" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L102" t="n">
         <v>2</v>
       </c>
       <c r="M102" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N102" t="s">
         <v>26</v>
       </c>
       <c r="O102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P102" t="n">
         <v>22</v>
       </c>
       <c r="Q102" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="103">
@@ -5922,25 +5952,25 @@
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L103" t="n">
         <v>3</v>
       </c>
       <c r="M103" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N103" t="s">
         <v>26</v>
       </c>
       <c r="O103" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P103" t="n">
         <v>22</v>
       </c>
       <c r="Q103" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="104">
@@ -5987,13 +6017,13 @@
         <v>29</v>
       </c>
       <c r="O104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P104" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q104" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="105">
@@ -6040,13 +6070,13 @@
         <v>29</v>
       </c>
       <c r="O105" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P105" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q105" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="106">
@@ -6093,13 +6123,13 @@
         <v>29</v>
       </c>
       <c r="O106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P106" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q106" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="107">
@@ -6134,25 +6164,25 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L107" t="n">
         <v>1</v>
       </c>
       <c r="M107" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N107" t="s">
         <v>32</v>
       </c>
       <c r="O107" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P107" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q107" t="n">
-        <v>633</v>
+        <v>687</v>
       </c>
     </row>
     <row r="108">
@@ -6187,25 +6217,25 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L108" t="n">
         <v>2</v>
       </c>
       <c r="M108" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N108" t="s">
         <v>32</v>
       </c>
       <c r="O108" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P108" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q108" t="n">
-        <v>633</v>
+        <v>687</v>
       </c>
     </row>
     <row r="109">
@@ -6240,25 +6270,25 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L109" t="n">
         <v>3</v>
       </c>
       <c r="M109" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N109" t="s">
         <v>32</v>
       </c>
       <c r="O109" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P109" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q109" t="n">
-        <v>633</v>
+        <v>687</v>
       </c>
     </row>
     <row r="110">
@@ -6299,19 +6329,19 @@
         <v>1</v>
       </c>
       <c r="M110" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N110" t="s">
         <v>22</v>
       </c>
       <c r="O110" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P110" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q110" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111">
@@ -6352,19 +6382,19 @@
         <v>2</v>
       </c>
       <c r="M111" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N111" t="s">
         <v>22</v>
       </c>
       <c r="O111" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P111" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q111" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112">
@@ -6405,19 +6435,19 @@
         <v>3</v>
       </c>
       <c r="M112" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N112" t="s">
         <v>22</v>
       </c>
       <c r="O112" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P112" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q112" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
     </row>
     <row r="113">
@@ -6452,25 +6482,25 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
       <c r="M113" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N113" t="s">
         <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P113" t="n">
         <v>22</v>
       </c>
       <c r="Q113" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="114">
@@ -6505,25 +6535,25 @@
         <v>2</v>
       </c>
       <c r="K114" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L114" t="n">
         <v>2</v>
       </c>
       <c r="M114" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N114" t="s">
         <v>26</v>
       </c>
       <c r="O114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P114" t="n">
         <v>22</v>
       </c>
       <c r="Q114" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="115">
@@ -6558,25 +6588,25 @@
         <v>2</v>
       </c>
       <c r="K115" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L115" t="n">
         <v>3</v>
       </c>
       <c r="M115" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="N115" t="s">
         <v>26</v>
       </c>
       <c r="O115" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P115" t="n">
         <v>22</v>
       </c>
       <c r="Q115" t="n">
-        <v>173</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116">
@@ -6623,13 +6653,13 @@
         <v>29</v>
       </c>
       <c r="O116" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P116" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q116" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="117">
@@ -6676,13 +6706,13 @@
         <v>29</v>
       </c>
       <c r="O117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P117" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q117" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="118">
@@ -6729,13 +6759,13 @@
         <v>29</v>
       </c>
       <c r="O118" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P118" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q118" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="119">
@@ -6770,25 +6800,25 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L119" t="n">
         <v>1</v>
       </c>
       <c r="M119" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N119" t="s">
         <v>32</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P119" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q119" t="n">
-        <v>633</v>
+        <v>687</v>
       </c>
     </row>
     <row r="120">
@@ -6823,25 +6853,25 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L120" t="n">
         <v>2</v>
       </c>
       <c r="M120" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N120" t="s">
         <v>32</v>
       </c>
       <c r="O120" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P120" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q120" t="n">
-        <v>633</v>
+        <v>687</v>
       </c>
     </row>
     <row r="121">
@@ -6876,25 +6906,25 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L121" t="n">
         <v>3</v>
       </c>
       <c r="M121" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N121" t="s">
         <v>32</v>
       </c>
       <c r="O121" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P121" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="Q121" t="n">
-        <v>633</v>
+        <v>687</v>
       </c>
     </row>
     <row r="122">
@@ -6929,25 +6959,25 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
       </c>
       <c r="M122" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N122" t="s">
         <v>22</v>
       </c>
       <c r="O122" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P122" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q122" t="n">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="123">
@@ -6982,25 +7012,25 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L123" t="n">
         <v>2</v>
       </c>
       <c r="M123" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N123" t="s">
         <v>22</v>
       </c>
       <c r="O123" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P123" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q123" t="n">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="124">
@@ -7035,25 +7065,25 @@
         <v>2</v>
       </c>
       <c r="K124" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L124" t="n">
         <v>3</v>
       </c>
       <c r="M124" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N124" t="s">
         <v>22</v>
       </c>
       <c r="O124" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P124" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q124" t="n">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="125">
@@ -7088,25 +7118,25 @@
         <v>2</v>
       </c>
       <c r="K125" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L125" t="n">
         <v>1</v>
       </c>
       <c r="M125" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N125" t="s">
         <v>26</v>
       </c>
       <c r="O125" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P125" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q125" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
     </row>
     <row r="126">
@@ -7141,25 +7171,25 @@
         <v>2</v>
       </c>
       <c r="K126" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L126" t="n">
         <v>2</v>
       </c>
       <c r="M126" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N126" t="s">
         <v>26</v>
       </c>
       <c r="O126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P126" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q126" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
     </row>
     <row r="127">
@@ -7194,25 +7224,25 @@
         <v>2</v>
       </c>
       <c r="K127" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L127" t="n">
         <v>3</v>
       </c>
       <c r="M127" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N127" t="s">
         <v>26</v>
       </c>
       <c r="O127" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P127" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q127" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
     </row>
     <row r="128">
@@ -7247,7 +7277,7 @@
         <v>2</v>
       </c>
       <c r="K128" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -7259,13 +7289,13 @@
         <v>29</v>
       </c>
       <c r="O128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P128" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q128" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="129">
@@ -7300,7 +7330,7 @@
         <v>2</v>
       </c>
       <c r="K129" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L129" t="n">
         <v>2</v>
@@ -7312,13 +7342,13 @@
         <v>29</v>
       </c>
       <c r="O129" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P129" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q129" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="130">
@@ -7353,7 +7383,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L130" t="n">
         <v>3</v>
@@ -7365,13 +7395,13 @@
         <v>29</v>
       </c>
       <c r="O130" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P130" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q130" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="131">
@@ -7406,25 +7436,25 @@
         <v>2</v>
       </c>
       <c r="K131" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
       </c>
       <c r="M131" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N131" t="s">
         <v>32</v>
       </c>
       <c r="O131" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P131" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q131" t="n">
-        <v>633</v>
+        <v>558</v>
       </c>
     </row>
     <row r="132">
@@ -7459,25 +7489,25 @@
         <v>2</v>
       </c>
       <c r="K132" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L132" t="n">
         <v>2</v>
       </c>
       <c r="M132" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N132" t="s">
         <v>32</v>
       </c>
       <c r="O132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P132" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q132" t="n">
-        <v>633</v>
+        <v>558</v>
       </c>
     </row>
     <row r="133">
@@ -7512,25 +7542,25 @@
         <v>2</v>
       </c>
       <c r="K133" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L133" t="n">
         <v>3</v>
       </c>
       <c r="M133" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N133" t="s">
         <v>32</v>
       </c>
       <c r="O133" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P133" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q133" t="n">
-        <v>633</v>
+        <v>558</v>
       </c>
     </row>
     <row r="134">
@@ -7565,25 +7595,25 @@
         <v>2</v>
       </c>
       <c r="K134" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
       </c>
       <c r="M134" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N134" t="s">
         <v>22</v>
       </c>
       <c r="O134" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P134" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q134" t="n">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="135">
@@ -7618,25 +7648,25 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L135" t="n">
         <v>2</v>
       </c>
       <c r="M135" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N135" t="s">
         <v>22</v>
       </c>
       <c r="O135" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P135" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q135" t="n">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="136">
@@ -7671,25 +7701,25 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L136" t="n">
         <v>3</v>
       </c>
       <c r="M136" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="N136" t="s">
         <v>22</v>
       </c>
       <c r="O136" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="P136" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="Q136" t="n">
-        <v>160</v>
+        <v>446</v>
       </c>
     </row>
     <row r="137">
@@ -7724,25 +7754,25 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L137" t="n">
         <v>1</v>
       </c>
       <c r="M137" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N137" t="s">
         <v>26</v>
       </c>
       <c r="O137" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P137" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q137" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
     </row>
     <row r="138">
@@ -7777,25 +7807,25 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L138" t="n">
         <v>2</v>
       </c>
       <c r="M138" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N138" t="s">
         <v>26</v>
       </c>
       <c r="O138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P138" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q138" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
     </row>
     <row r="139">
@@ -7830,25 +7860,25 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L139" t="n">
         <v>3</v>
       </c>
       <c r="M139" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="N139" t="s">
         <v>26</v>
       </c>
       <c r="O139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P139" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q139" t="n">
-        <v>173</v>
+        <v>117</v>
       </c>
     </row>
     <row r="140">
@@ -7883,7 +7913,7 @@
         <v>2</v>
       </c>
       <c r="K140" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
@@ -7895,13 +7925,13 @@
         <v>29</v>
       </c>
       <c r="O140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P140" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q140" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="141">
@@ -7936,7 +7966,7 @@
         <v>2</v>
       </c>
       <c r="K141" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L141" t="n">
         <v>2</v>
@@ -7948,13 +7978,13 @@
         <v>29</v>
       </c>
       <c r="O141" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P141" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q141" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="142">
@@ -7989,7 +8019,7 @@
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L142" t="n">
         <v>3</v>
@@ -8001,13 +8031,13 @@
         <v>29</v>
       </c>
       <c r="O142" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P142" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q142" t="n">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143">
@@ -8042,25 +8072,25 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L143" t="n">
         <v>1</v>
       </c>
       <c r="M143" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N143" t="s">
         <v>32</v>
       </c>
       <c r="O143" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P143" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q143" t="n">
-        <v>633</v>
+        <v>558</v>
       </c>
     </row>
     <row r="144">
@@ -8095,25 +8125,25 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L144" t="n">
         <v>2</v>
       </c>
       <c r="M144" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N144" t="s">
         <v>32</v>
       </c>
       <c r="O144" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P144" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q144" t="n">
-        <v>633</v>
+        <v>558</v>
       </c>
     </row>
     <row r="145">
@@ -8148,25 +8178,3841 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
       </c>
       <c r="M145" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="N145" t="s">
         <v>32</v>
       </c>
       <c r="O145" t="n">
+        <v>7</v>
+      </c>
+      <c r="P145" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>289</v>
+      </c>
+      <c r="B146" t="b">
+        <v>0</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>18</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" t="n">
+        <v>1</v>
+      </c>
+      <c r="H146" t="s">
+        <v>19</v>
+      </c>
+      <c r="I146" t="n">
+        <v>7</v>
+      </c>
+      <c r="J146" t="n">
+        <v>3</v>
+      </c>
+      <c r="K146" t="s">
+        <v>52</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="s">
+        <v>44</v>
+      </c>
+      <c r="N146" t="s">
+        <v>22</v>
+      </c>
+      <c r="O146" t="n">
+        <v>11</v>
+      </c>
+      <c r="P146" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>290</v>
+      </c>
+      <c r="B147" t="b">
+        <v>0</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>18</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" t="s">
+        <v>19</v>
+      </c>
+      <c r="I147" t="n">
+        <v>7</v>
+      </c>
+      <c r="J147" t="n">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>52</v>
+      </c>
+      <c r="L147" t="n">
+        <v>2</v>
+      </c>
+      <c r="M147" t="s">
+        <v>44</v>
+      </c>
+      <c r="N147" t="s">
+        <v>22</v>
+      </c>
+      <c r="O147" t="n">
+        <v>11</v>
+      </c>
+      <c r="P147" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>291</v>
+      </c>
+      <c r="B148" t="b">
+        <v>0</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>18</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" t="s">
+        <v>19</v>
+      </c>
+      <c r="I148" t="n">
+        <v>7</v>
+      </c>
+      <c r="J148" t="n">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>52</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="s">
+        <v>44</v>
+      </c>
+      <c r="N148" t="s">
+        <v>22</v>
+      </c>
+      <c r="O148" t="n">
+        <v>11</v>
+      </c>
+      <c r="P148" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>295</v>
+      </c>
+      <c r="B149" t="b">
+        <v>0</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>18</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" t="n">
+        <v>7</v>
+      </c>
+      <c r="J149" t="n">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>53</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="s">
+        <v>46</v>
+      </c>
+      <c r="N149" t="s">
+        <v>26</v>
+      </c>
+      <c r="O149" t="n">
+        <v>7</v>
+      </c>
+      <c r="P149" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>296</v>
+      </c>
+      <c r="B150" t="b">
+        <v>0</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>18</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2</v>
+      </c>
+      <c r="G150" t="n">
+        <v>1</v>
+      </c>
+      <c r="H150" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" t="n">
+        <v>7</v>
+      </c>
+      <c r="J150" t="n">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>53</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="s">
+        <v>46</v>
+      </c>
+      <c r="N150" t="s">
+        <v>26</v>
+      </c>
+      <c r="O150" t="n">
+        <v>7</v>
+      </c>
+      <c r="P150" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>297</v>
+      </c>
+      <c r="B151" t="b">
+        <v>0</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>18</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2</v>
+      </c>
+      <c r="G151" t="n">
+        <v>1</v>
+      </c>
+      <c r="H151" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" t="n">
+        <v>7</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>53</v>
+      </c>
+      <c r="L151" t="n">
+        <v>3</v>
+      </c>
+      <c r="M151" t="s">
+        <v>46</v>
+      </c>
+      <c r="N151" t="s">
+        <v>26</v>
+      </c>
+      <c r="O151" t="n">
+        <v>7</v>
+      </c>
+      <c r="P151" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>301</v>
+      </c>
+      <c r="B152" t="b">
+        <v>0</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>18</v>
+      </c>
+      <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>1</v>
+      </c>
+      <c r="H152" t="s">
+        <v>27</v>
+      </c>
+      <c r="I152" t="n">
+        <v>7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>52</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="s">
+        <v>28</v>
+      </c>
+      <c r="N152" t="s">
+        <v>29</v>
+      </c>
+      <c r="O152" t="n">
+        <v>5</v>
+      </c>
+      <c r="P152" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>302</v>
+      </c>
+      <c r="B153" t="b">
+        <v>0</v>
+      </c>
+      <c r="C153" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" t="s">
+        <v>18</v>
+      </c>
+      <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="s">
+        <v>27</v>
+      </c>
+      <c r="I153" t="n">
+        <v>7</v>
+      </c>
+      <c r="J153" t="n">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>52</v>
+      </c>
+      <c r="L153" t="n">
+        <v>2</v>
+      </c>
+      <c r="M153" t="s">
+        <v>28</v>
+      </c>
+      <c r="N153" t="s">
+        <v>29</v>
+      </c>
+      <c r="O153" t="n">
+        <v>5</v>
+      </c>
+      <c r="P153" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>303</v>
+      </c>
+      <c r="B154" t="b">
+        <v>0</v>
+      </c>
+      <c r="C154" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" t="s">
+        <v>18</v>
+      </c>
+      <c r="E154" t="n">
+        <v>2</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" t="n">
+        <v>7</v>
+      </c>
+      <c r="J154" t="n">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>52</v>
+      </c>
+      <c r="L154" t="n">
+        <v>3</v>
+      </c>
+      <c r="M154" t="s">
+        <v>28</v>
+      </c>
+      <c r="N154" t="s">
+        <v>29</v>
+      </c>
+      <c r="O154" t="n">
+        <v>5</v>
+      </c>
+      <c r="P154" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>307</v>
+      </c>
+      <c r="B155" t="b">
+        <v>0</v>
+      </c>
+      <c r="C155" t="s">
+        <v>17</v>
+      </c>
+      <c r="D155" t="s">
+        <v>18</v>
+      </c>
+      <c r="E155" t="n">
+        <v>2</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="s">
+        <v>30</v>
+      </c>
+      <c r="I155" t="n">
+        <v>7</v>
+      </c>
+      <c r="J155" t="n">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>53</v>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="s">
+        <v>47</v>
+      </c>
+      <c r="N155" t="s">
+        <v>32</v>
+      </c>
+      <c r="O155" t="n">
+        <v>12</v>
+      </c>
+      <c r="P155" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>308</v>
+      </c>
+      <c r="B156" t="b">
+        <v>0</v>
+      </c>
+      <c r="C156" t="s">
+        <v>17</v>
+      </c>
+      <c r="D156" t="s">
+        <v>18</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2</v>
+      </c>
+      <c r="G156" t="n">
+        <v>1</v>
+      </c>
+      <c r="H156" t="s">
+        <v>30</v>
+      </c>
+      <c r="I156" t="n">
+        <v>7</v>
+      </c>
+      <c r="J156" t="n">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>53</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2</v>
+      </c>
+      <c r="M156" t="s">
+        <v>47</v>
+      </c>
+      <c r="N156" t="s">
+        <v>32</v>
+      </c>
+      <c r="O156" t="n">
+        <v>12</v>
+      </c>
+      <c r="P156" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>309</v>
+      </c>
+      <c r="B157" t="b">
+        <v>0</v>
+      </c>
+      <c r="C157" t="s">
+        <v>17</v>
+      </c>
+      <c r="D157" t="s">
+        <v>18</v>
+      </c>
+      <c r="E157" t="n">
+        <v>2</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2</v>
+      </c>
+      <c r="G157" t="n">
+        <v>1</v>
+      </c>
+      <c r="H157" t="s">
+        <v>30</v>
+      </c>
+      <c r="I157" t="n">
+        <v>7</v>
+      </c>
+      <c r="J157" t="n">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>53</v>
+      </c>
+      <c r="L157" t="n">
+        <v>3</v>
+      </c>
+      <c r="M157" t="s">
+        <v>47</v>
+      </c>
+      <c r="N157" t="s">
+        <v>32</v>
+      </c>
+      <c r="O157" t="n">
+        <v>12</v>
+      </c>
+      <c r="P157" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q157" t="n">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>313</v>
+      </c>
+      <c r="B158" t="b">
+        <v>0</v>
+      </c>
+      <c r="C158" t="s">
+        <v>17</v>
+      </c>
+      <c r="D158" t="s">
+        <v>18</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>2</v>
+      </c>
+      <c r="H158" t="s">
+        <v>33</v>
+      </c>
+      <c r="I158" t="n">
+        <v>7</v>
+      </c>
+      <c r="J158" t="n">
+        <v>3</v>
+      </c>
+      <c r="K158" t="s">
+        <v>52</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="s">
+        <v>44</v>
+      </c>
+      <c r="N158" t="s">
+        <v>22</v>
+      </c>
+      <c r="O158" t="n">
+        <v>11</v>
+      </c>
+      <c r="P158" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>314</v>
+      </c>
+      <c r="B159" t="b">
+        <v>0</v>
+      </c>
+      <c r="C159" t="s">
+        <v>17</v>
+      </c>
+      <c r="D159" t="s">
+        <v>18</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>2</v>
+      </c>
+      <c r="H159" t="s">
+        <v>33</v>
+      </c>
+      <c r="I159" t="n">
+        <v>7</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>52</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="s">
+        <v>44</v>
+      </c>
+      <c r="N159" t="s">
+        <v>22</v>
+      </c>
+      <c r="O159" t="n">
+        <v>11</v>
+      </c>
+      <c r="P159" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>315</v>
+      </c>
+      <c r="B160" t="b">
+        <v>0</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160" t="s">
+        <v>18</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2</v>
+      </c>
+      <c r="H160" t="s">
+        <v>33</v>
+      </c>
+      <c r="I160" t="n">
+        <v>7</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>52</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="s">
+        <v>44</v>
+      </c>
+      <c r="N160" t="s">
+        <v>22</v>
+      </c>
+      <c r="O160" t="n">
+        <v>11</v>
+      </c>
+      <c r="P160" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>319</v>
+      </c>
+      <c r="B161" t="b">
+        <v>0</v>
+      </c>
+      <c r="C161" t="s">
+        <v>17</v>
+      </c>
+      <c r="D161" t="s">
+        <v>18</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2</v>
+      </c>
+      <c r="G161" t="n">
+        <v>2</v>
+      </c>
+      <c r="H161" t="s">
+        <v>34</v>
+      </c>
+      <c r="I161" t="n">
+        <v>7</v>
+      </c>
+      <c r="J161" t="n">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>53</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="s">
+        <v>46</v>
+      </c>
+      <c r="N161" t="s">
+        <v>26</v>
+      </c>
+      <c r="O161" t="n">
+        <v>7</v>
+      </c>
+      <c r="P161" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>320</v>
+      </c>
+      <c r="B162" t="b">
+        <v>0</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>18</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2</v>
+      </c>
+      <c r="H162" t="s">
+        <v>34</v>
+      </c>
+      <c r="I162" t="n">
+        <v>7</v>
+      </c>
+      <c r="J162" t="n">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>53</v>
+      </c>
+      <c r="L162" t="n">
+        <v>2</v>
+      </c>
+      <c r="M162" t="s">
+        <v>46</v>
+      </c>
+      <c r="N162" t="s">
+        <v>26</v>
+      </c>
+      <c r="O162" t="n">
+        <v>7</v>
+      </c>
+      <c r="P162" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>321</v>
+      </c>
+      <c r="B163" t="b">
+        <v>0</v>
+      </c>
+      <c r="C163" t="s">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>18</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2</v>
+      </c>
+      <c r="G163" t="n">
+        <v>2</v>
+      </c>
+      <c r="H163" t="s">
+        <v>34</v>
+      </c>
+      <c r="I163" t="n">
+        <v>7</v>
+      </c>
+      <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>53</v>
+      </c>
+      <c r="L163" t="n">
+        <v>3</v>
+      </c>
+      <c r="M163" t="s">
+        <v>46</v>
+      </c>
+      <c r="N163" t="s">
+        <v>26</v>
+      </c>
+      <c r="O163" t="n">
+        <v>7</v>
+      </c>
+      <c r="P163" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>325</v>
+      </c>
+      <c r="B164" t="b">
+        <v>0</v>
+      </c>
+      <c r="C164" t="s">
+        <v>17</v>
+      </c>
+      <c r="D164" t="s">
+        <v>18</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" t="n">
+        <v>2</v>
+      </c>
+      <c r="H164" t="s">
+        <v>35</v>
+      </c>
+      <c r="I164" t="n">
+        <v>7</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3</v>
+      </c>
+      <c r="K164" t="s">
+        <v>52</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="s">
+        <v>28</v>
+      </c>
+      <c r="N164" t="s">
+        <v>29</v>
+      </c>
+      <c r="O164" t="n">
+        <v>5</v>
+      </c>
+      <c r="P164" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>326</v>
+      </c>
+      <c r="B165" t="b">
+        <v>0</v>
+      </c>
+      <c r="C165" t="s">
+        <v>17</v>
+      </c>
+      <c r="D165" t="s">
+        <v>18</v>
+      </c>
+      <c r="E165" t="n">
+        <v>2</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>2</v>
+      </c>
+      <c r="H165" t="s">
+        <v>35</v>
+      </c>
+      <c r="I165" t="n">
+        <v>7</v>
+      </c>
+      <c r="J165" t="n">
+        <v>3</v>
+      </c>
+      <c r="K165" t="s">
+        <v>52</v>
+      </c>
+      <c r="L165" t="n">
+        <v>2</v>
+      </c>
+      <c r="M165" t="s">
+        <v>28</v>
+      </c>
+      <c r="N165" t="s">
+        <v>29</v>
+      </c>
+      <c r="O165" t="n">
+        <v>5</v>
+      </c>
+      <c r="P165" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>327</v>
+      </c>
+      <c r="B166" t="b">
+        <v>0</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>18</v>
+      </c>
+      <c r="E166" t="n">
+        <v>2</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" t="n">
+        <v>2</v>
+      </c>
+      <c r="H166" t="s">
+        <v>35</v>
+      </c>
+      <c r="I166" t="n">
+        <v>7</v>
+      </c>
+      <c r="J166" t="n">
+        <v>3</v>
+      </c>
+      <c r="K166" t="s">
+        <v>52</v>
+      </c>
+      <c r="L166" t="n">
+        <v>3</v>
+      </c>
+      <c r="M166" t="s">
+        <v>28</v>
+      </c>
+      <c r="N166" t="s">
+        <v>29</v>
+      </c>
+      <c r="O166" t="n">
+        <v>5</v>
+      </c>
+      <c r="P166" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>331</v>
+      </c>
+      <c r="B167" t="b">
+        <v>0</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167" t="s">
+        <v>18</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="s">
+        <v>36</v>
+      </c>
+      <c r="I167" t="n">
+        <v>7</v>
+      </c>
+      <c r="J167" t="n">
+        <v>3</v>
+      </c>
+      <c r="K167" t="s">
+        <v>53</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="s">
+        <v>47</v>
+      </c>
+      <c r="N167" t="s">
+        <v>32</v>
+      </c>
+      <c r="O167" t="n">
+        <v>12</v>
+      </c>
+      <c r="P167" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>332</v>
+      </c>
+      <c r="B168" t="b">
+        <v>0</v>
+      </c>
+      <c r="C168" t="s">
+        <v>17</v>
+      </c>
+      <c r="D168" t="s">
+        <v>18</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2</v>
+      </c>
+      <c r="F168" t="n">
+        <v>2</v>
+      </c>
+      <c r="G168" t="n">
+        <v>2</v>
+      </c>
+      <c r="H168" t="s">
+        <v>36</v>
+      </c>
+      <c r="I168" t="n">
+        <v>7</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="s">
+        <v>53</v>
+      </c>
+      <c r="L168" t="n">
+        <v>2</v>
+      </c>
+      <c r="M168" t="s">
+        <v>47</v>
+      </c>
+      <c r="N168" t="s">
+        <v>32</v>
+      </c>
+      <c r="O168" t="n">
+        <v>12</v>
+      </c>
+      <c r="P168" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>333</v>
+      </c>
+      <c r="B169" t="b">
+        <v>0</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169" t="s">
+        <v>18</v>
+      </c>
+      <c r="E169" t="n">
+        <v>2</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2</v>
+      </c>
+      <c r="G169" t="n">
+        <v>2</v>
+      </c>
+      <c r="H169" t="s">
+        <v>36</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7</v>
+      </c>
+      <c r="J169" t="n">
+        <v>3</v>
+      </c>
+      <c r="K169" t="s">
+        <v>53</v>
+      </c>
+      <c r="L169" t="n">
+        <v>3</v>
+      </c>
+      <c r="M169" t="s">
+        <v>47</v>
+      </c>
+      <c r="N169" t="s">
+        <v>32</v>
+      </c>
+      <c r="O169" t="n">
+        <v>12</v>
+      </c>
+      <c r="P169" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>337</v>
+      </c>
+      <c r="B170" t="b">
+        <v>0</v>
+      </c>
+      <c r="C170" t="s">
+        <v>17</v>
+      </c>
+      <c r="D170" t="s">
+        <v>18</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>1</v>
+      </c>
+      <c r="H170" t="s">
+        <v>19</v>
+      </c>
+      <c r="I170" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="s">
+        <v>54</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="s">
+        <v>21</v>
+      </c>
+      <c r="N170" t="s">
+        <v>22</v>
+      </c>
+      <c r="O170" t="n">
+        <v>13</v>
+      </c>
+      <c r="P170" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>338</v>
+      </c>
+      <c r="B171" t="b">
+        <v>0</v>
+      </c>
+      <c r="C171" t="s">
+        <v>17</v>
+      </c>
+      <c r="D171" t="s">
+        <v>18</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" t="n">
+        <v>1</v>
+      </c>
+      <c r="H171" t="s">
+        <v>19</v>
+      </c>
+      <c r="I171" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" t="n">
+        <v>3</v>
+      </c>
+      <c r="K171" t="s">
+        <v>54</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="s">
+        <v>21</v>
+      </c>
+      <c r="N171" t="s">
+        <v>22</v>
+      </c>
+      <c r="O171" t="n">
+        <v>13</v>
+      </c>
+      <c r="P171" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>339</v>
+      </c>
+      <c r="B172" t="b">
+        <v>0</v>
+      </c>
+      <c r="C172" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" t="s">
+        <v>18</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" t="n">
+        <v>1</v>
+      </c>
+      <c r="H172" t="s">
+        <v>19</v>
+      </c>
+      <c r="I172" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" t="n">
+        <v>3</v>
+      </c>
+      <c r="K172" t="s">
+        <v>54</v>
+      </c>
+      <c r="L172" t="n">
+        <v>3</v>
+      </c>
+      <c r="M172" t="s">
+        <v>21</v>
+      </c>
+      <c r="N172" t="s">
+        <v>22</v>
+      </c>
+      <c r="O172" t="n">
+        <v>13</v>
+      </c>
+      <c r="P172" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>343</v>
+      </c>
+      <c r="B173" t="b">
+        <v>0</v>
+      </c>
+      <c r="C173" t="s">
+        <v>17</v>
+      </c>
+      <c r="D173" t="s">
+        <v>18</v>
+      </c>
+      <c r="E173" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>1</v>
+      </c>
+      <c r="H173" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" t="n">
+        <v>3</v>
+      </c>
+      <c r="K173" t="s">
+        <v>55</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="s">
+        <v>50</v>
+      </c>
+      <c r="N173" t="s">
+        <v>26</v>
+      </c>
+      <c r="O173" t="n">
+        <v>5</v>
+      </c>
+      <c r="P173" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>344</v>
+      </c>
+      <c r="B174" t="b">
+        <v>0</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174" t="s">
+        <v>18</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>2</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1</v>
+      </c>
+      <c r="H174" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" t="n">
+        <v>3</v>
+      </c>
+      <c r="K174" t="s">
+        <v>55</v>
+      </c>
+      <c r="L174" t="n">
+        <v>2</v>
+      </c>
+      <c r="M174" t="s">
+        <v>50</v>
+      </c>
+      <c r="N174" t="s">
+        <v>26</v>
+      </c>
+      <c r="O174" t="n">
+        <v>5</v>
+      </c>
+      <c r="P174" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>345</v>
+      </c>
+      <c r="B175" t="b">
+        <v>0</v>
+      </c>
+      <c r="C175" t="s">
+        <v>17</v>
+      </c>
+      <c r="D175" t="s">
+        <v>18</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>1</v>
+      </c>
+      <c r="H175" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" t="n">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>55</v>
+      </c>
+      <c r="L175" t="n">
+        <v>3</v>
+      </c>
+      <c r="M175" t="s">
+        <v>50</v>
+      </c>
+      <c r="N175" t="s">
+        <v>26</v>
+      </c>
+      <c r="O175" t="n">
+        <v>5</v>
+      </c>
+      <c r="P175" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>349</v>
+      </c>
+      <c r="B176" t="b">
+        <v>0</v>
+      </c>
+      <c r="C176" t="s">
+        <v>17</v>
+      </c>
+      <c r="D176" t="s">
+        <v>18</v>
+      </c>
+      <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1</v>
+      </c>
+      <c r="H176" t="s">
+        <v>27</v>
+      </c>
+      <c r="I176" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" t="n">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>54</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="s">
+        <v>28</v>
+      </c>
+      <c r="N176" t="s">
+        <v>29</v>
+      </c>
+      <c r="O176" t="n">
+        <v>5</v>
+      </c>
+      <c r="P176" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>350</v>
+      </c>
+      <c r="B177" t="b">
+        <v>0</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177" t="s">
+        <v>18</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>1</v>
+      </c>
+      <c r="H177" t="s">
+        <v>27</v>
+      </c>
+      <c r="I177" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" t="n">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>54</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2</v>
+      </c>
+      <c r="M177" t="s">
+        <v>28</v>
+      </c>
+      <c r="N177" t="s">
+        <v>29</v>
+      </c>
+      <c r="O177" t="n">
+        <v>5</v>
+      </c>
+      <c r="P177" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>351</v>
+      </c>
+      <c r="B178" t="b">
+        <v>0</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178" t="s">
+        <v>18</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>27</v>
+      </c>
+      <c r="I178" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>3</v>
+      </c>
+      <c r="K178" t="s">
+        <v>54</v>
+      </c>
+      <c r="L178" t="n">
+        <v>3</v>
+      </c>
+      <c r="M178" t="s">
+        <v>28</v>
+      </c>
+      <c r="N178" t="s">
+        <v>29</v>
+      </c>
+      <c r="O178" t="n">
+        <v>5</v>
+      </c>
+      <c r="P178" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>355</v>
+      </c>
+      <c r="B179" t="b">
+        <v>0</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2</v>
+      </c>
+      <c r="F179" t="n">
+        <v>2</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="s">
+        <v>30</v>
+      </c>
+      <c r="I179" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="s">
+        <v>55</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="s">
+        <v>51</v>
+      </c>
+      <c r="N179" t="s">
+        <v>32</v>
+      </c>
+      <c r="O179" t="n">
+        <v>7</v>
+      </c>
+      <c r="P179" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q179" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>356</v>
+      </c>
+      <c r="B180" t="b">
+        <v>0</v>
+      </c>
+      <c r="C180" t="s">
+        <v>17</v>
+      </c>
+      <c r="D180" t="s">
+        <v>18</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>1</v>
+      </c>
+      <c r="H180" t="s">
+        <v>30</v>
+      </c>
+      <c r="I180" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" t="n">
+        <v>3</v>
+      </c>
+      <c r="K180" t="s">
+        <v>55</v>
+      </c>
+      <c r="L180" t="n">
+        <v>2</v>
+      </c>
+      <c r="M180" t="s">
+        <v>51</v>
+      </c>
+      <c r="N180" t="s">
+        <v>32</v>
+      </c>
+      <c r="O180" t="n">
+        <v>7</v>
+      </c>
+      <c r="P180" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>357</v>
+      </c>
+      <c r="B181" t="b">
+        <v>0</v>
+      </c>
+      <c r="C181" t="s">
+        <v>17</v>
+      </c>
+      <c r="D181" t="s">
+        <v>18</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>2</v>
+      </c>
+      <c r="G181" t="n">
+        <v>1</v>
+      </c>
+      <c r="H181" t="s">
+        <v>30</v>
+      </c>
+      <c r="I181" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" t="n">
+        <v>3</v>
+      </c>
+      <c r="K181" t="s">
+        <v>55</v>
+      </c>
+      <c r="L181" t="n">
+        <v>3</v>
+      </c>
+      <c r="M181" t="s">
+        <v>51</v>
+      </c>
+      <c r="N181" t="s">
+        <v>32</v>
+      </c>
+      <c r="O181" t="n">
+        <v>7</v>
+      </c>
+      <c r="P181" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>361</v>
+      </c>
+      <c r="B182" t="b">
+        <v>0</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>18</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" t="n">
+        <v>2</v>
+      </c>
+      <c r="H182" t="s">
+        <v>33</v>
+      </c>
+      <c r="I182" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" t="n">
+        <v>3</v>
+      </c>
+      <c r="K182" t="s">
+        <v>54</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="s">
+        <v>21</v>
+      </c>
+      <c r="N182" t="s">
+        <v>22</v>
+      </c>
+      <c r="O182" t="n">
+        <v>13</v>
+      </c>
+      <c r="P182" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>362</v>
+      </c>
+      <c r="B183" t="b">
+        <v>0</v>
+      </c>
+      <c r="C183" t="s">
+        <v>17</v>
+      </c>
+      <c r="D183" t="s">
+        <v>18</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="s">
+        <v>33</v>
+      </c>
+      <c r="I183" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" t="n">
+        <v>3</v>
+      </c>
+      <c r="K183" t="s">
+        <v>54</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="s">
+        <v>21</v>
+      </c>
+      <c r="N183" t="s">
+        <v>22</v>
+      </c>
+      <c r="O183" t="n">
+        <v>13</v>
+      </c>
+      <c r="P183" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>363</v>
+      </c>
+      <c r="B184" t="b">
+        <v>0</v>
+      </c>
+      <c r="C184" t="s">
+        <v>17</v>
+      </c>
+      <c r="D184" t="s">
+        <v>18</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" t="n">
+        <v>2</v>
+      </c>
+      <c r="H184" t="s">
+        <v>33</v>
+      </c>
+      <c r="I184" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" t="n">
+        <v>3</v>
+      </c>
+      <c r="K184" t="s">
+        <v>54</v>
+      </c>
+      <c r="L184" t="n">
+        <v>3</v>
+      </c>
+      <c r="M184" t="s">
+        <v>21</v>
+      </c>
+      <c r="N184" t="s">
+        <v>22</v>
+      </c>
+      <c r="O184" t="n">
+        <v>13</v>
+      </c>
+      <c r="P184" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>367</v>
+      </c>
+      <c r="B185" t="b">
+        <v>0</v>
+      </c>
+      <c r="C185" t="s">
+        <v>17</v>
+      </c>
+      <c r="D185" t="s">
+        <v>18</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2</v>
+      </c>
+      <c r="G185" t="n">
+        <v>2</v>
+      </c>
+      <c r="H185" t="s">
+        <v>34</v>
+      </c>
+      <c r="I185" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" t="n">
+        <v>3</v>
+      </c>
+      <c r="K185" t="s">
+        <v>55</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="s">
+        <v>50</v>
+      </c>
+      <c r="N185" t="s">
+        <v>26</v>
+      </c>
+      <c r="O185" t="n">
+        <v>5</v>
+      </c>
+      <c r="P185" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>368</v>
+      </c>
+      <c r="B186" t="b">
+        <v>0</v>
+      </c>
+      <c r="C186" t="s">
+        <v>17</v>
+      </c>
+      <c r="D186" t="s">
+        <v>18</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" t="n">
+        <v>2</v>
+      </c>
+      <c r="G186" t="n">
+        <v>2</v>
+      </c>
+      <c r="H186" t="s">
+        <v>34</v>
+      </c>
+      <c r="I186" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" t="n">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>55</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="s">
+        <v>50</v>
+      </c>
+      <c r="N186" t="s">
+        <v>26</v>
+      </c>
+      <c r="O186" t="n">
+        <v>5</v>
+      </c>
+      <c r="P186" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>369</v>
+      </c>
+      <c r="B187" t="b">
+        <v>0</v>
+      </c>
+      <c r="C187" t="s">
+        <v>17</v>
+      </c>
+      <c r="D187" t="s">
+        <v>18</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2</v>
+      </c>
+      <c r="H187" t="s">
+        <v>34</v>
+      </c>
+      <c r="I187" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" t="n">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>55</v>
+      </c>
+      <c r="L187" t="n">
+        <v>3</v>
+      </c>
+      <c r="M187" t="s">
+        <v>50</v>
+      </c>
+      <c r="N187" t="s">
+        <v>26</v>
+      </c>
+      <c r="O187" t="n">
+        <v>5</v>
+      </c>
+      <c r="P187" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>373</v>
+      </c>
+      <c r="B188" t="b">
+        <v>0</v>
+      </c>
+      <c r="C188" t="s">
+        <v>17</v>
+      </c>
+      <c r="D188" t="s">
+        <v>18</v>
+      </c>
+      <c r="E188" t="n">
+        <v>2</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2</v>
+      </c>
+      <c r="H188" t="s">
+        <v>35</v>
+      </c>
+      <c r="I188" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" t="n">
+        <v>3</v>
+      </c>
+      <c r="K188" t="s">
+        <v>54</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="s">
+        <v>28</v>
+      </c>
+      <c r="N188" t="s">
+        <v>29</v>
+      </c>
+      <c r="O188" t="n">
+        <v>5</v>
+      </c>
+      <c r="P188" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>374</v>
+      </c>
+      <c r="B189" t="b">
+        <v>0</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189" t="s">
+        <v>18</v>
+      </c>
+      <c r="E189" t="n">
+        <v>2</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" t="n">
+        <v>2</v>
+      </c>
+      <c r="H189" t="s">
+        <v>35</v>
+      </c>
+      <c r="I189" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" t="n">
+        <v>3</v>
+      </c>
+      <c r="K189" t="s">
+        <v>54</v>
+      </c>
+      <c r="L189" t="n">
+        <v>2</v>
+      </c>
+      <c r="M189" t="s">
+        <v>28</v>
+      </c>
+      <c r="N189" t="s">
+        <v>29</v>
+      </c>
+      <c r="O189" t="n">
+        <v>5</v>
+      </c>
+      <c r="P189" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>375</v>
+      </c>
+      <c r="B190" t="b">
+        <v>0</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190" t="s">
+        <v>18</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2</v>
+      </c>
+      <c r="H190" t="s">
+        <v>35</v>
+      </c>
+      <c r="I190" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" t="n">
+        <v>3</v>
+      </c>
+      <c r="K190" t="s">
+        <v>54</v>
+      </c>
+      <c r="L190" t="n">
+        <v>3</v>
+      </c>
+      <c r="M190" t="s">
+        <v>28</v>
+      </c>
+      <c r="N190" t="s">
+        <v>29</v>
+      </c>
+      <c r="O190" t="n">
+        <v>5</v>
+      </c>
+      <c r="P190" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>379</v>
+      </c>
+      <c r="B191" t="b">
+        <v>0</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191" t="s">
+        <v>18</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" t="n">
+        <v>2</v>
+      </c>
+      <c r="H191" t="s">
+        <v>36</v>
+      </c>
+      <c r="I191" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" t="n">
+        <v>3</v>
+      </c>
+      <c r="K191" t="s">
+        <v>55</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="s">
+        <v>51</v>
+      </c>
+      <c r="N191" t="s">
+        <v>32</v>
+      </c>
+      <c r="O191" t="n">
+        <v>7</v>
+      </c>
+      <c r="P191" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>380</v>
+      </c>
+      <c r="B192" t="b">
+        <v>0</v>
+      </c>
+      <c r="C192" t="s">
+        <v>17</v>
+      </c>
+      <c r="D192" t="s">
+        <v>18</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" t="n">
+        <v>2</v>
+      </c>
+      <c r="H192" t="s">
+        <v>36</v>
+      </c>
+      <c r="I192" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" t="s">
+        <v>55</v>
+      </c>
+      <c r="L192" t="n">
+        <v>2</v>
+      </c>
+      <c r="M192" t="s">
+        <v>51</v>
+      </c>
+      <c r="N192" t="s">
+        <v>32</v>
+      </c>
+      <c r="O192" t="n">
+        <v>7</v>
+      </c>
+      <c r="P192" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>381</v>
+      </c>
+      <c r="B193" t="b">
+        <v>0</v>
+      </c>
+      <c r="C193" t="s">
+        <v>17</v>
+      </c>
+      <c r="D193" t="s">
+        <v>18</v>
+      </c>
+      <c r="E193" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" t="s">
+        <v>36</v>
+      </c>
+      <c r="I193" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" t="n">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>55</v>
+      </c>
+      <c r="L193" t="n">
+        <v>3</v>
+      </c>
+      <c r="M193" t="s">
+        <v>51</v>
+      </c>
+      <c r="N193" t="s">
+        <v>32</v>
+      </c>
+      <c r="O193" t="n">
+        <v>7</v>
+      </c>
+      <c r="P193" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q193" t="n">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>385</v>
+      </c>
+      <c r="B194" t="b">
+        <v>0</v>
+      </c>
+      <c r="C194" t="s">
+        <v>17</v>
+      </c>
+      <c r="D194" t="s">
+        <v>18</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="s">
+        <v>19</v>
+      </c>
+      <c r="I194" t="n">
         <v>9</v>
       </c>
-      <c r="P145" t="n">
+      <c r="J194" t="n">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>56</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="s">
+        <v>21</v>
+      </c>
+      <c r="N194" t="s">
+        <v>22</v>
+      </c>
+      <c r="O194" t="n">
+        <v>13</v>
+      </c>
+      <c r="P194" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>386</v>
+      </c>
+      <c r="B195" t="b">
+        <v>0</v>
+      </c>
+      <c r="C195" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195" t="s">
+        <v>18</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" t="n">
+        <v>1</v>
+      </c>
+      <c r="H195" t="s">
+        <v>19</v>
+      </c>
+      <c r="I195" t="n">
+        <v>9</v>
+      </c>
+      <c r="J195" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>56</v>
+      </c>
+      <c r="L195" t="n">
+        <v>2</v>
+      </c>
+      <c r="M195" t="s">
+        <v>21</v>
+      </c>
+      <c r="N195" t="s">
+        <v>22</v>
+      </c>
+      <c r="O195" t="n">
+        <v>13</v>
+      </c>
+      <c r="P195" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>387</v>
+      </c>
+      <c r="B196" t="b">
+        <v>0</v>
+      </c>
+      <c r="C196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196" t="s">
+        <v>18</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>19</v>
+      </c>
+      <c r="I196" t="n">
+        <v>9</v>
+      </c>
+      <c r="J196" t="n">
+        <v>3</v>
+      </c>
+      <c r="K196" t="s">
+        <v>56</v>
+      </c>
+      <c r="L196" t="n">
+        <v>3</v>
+      </c>
+      <c r="M196" t="s">
+        <v>21</v>
+      </c>
+      <c r="N196" t="s">
+        <v>22</v>
+      </c>
+      <c r="O196" t="n">
+        <v>13</v>
+      </c>
+      <c r="P196" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q196" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>391</v>
+      </c>
+      <c r="B197" t="b">
+        <v>0</v>
+      </c>
+      <c r="C197" t="s">
+        <v>17</v>
+      </c>
+      <c r="D197" t="s">
+        <v>18</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" t="n">
+        <v>9</v>
+      </c>
+      <c r="J197" t="n">
+        <v>3</v>
+      </c>
+      <c r="K197" t="s">
+        <v>57</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="s">
+        <v>25</v>
+      </c>
+      <c r="N197" t="s">
+        <v>26</v>
+      </c>
+      <c r="O197" t="n">
+        <v>8</v>
+      </c>
+      <c r="P197" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q197" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>392</v>
+      </c>
+      <c r="B198" t="b">
+        <v>0</v>
+      </c>
+      <c r="C198" t="s">
+        <v>17</v>
+      </c>
+      <c r="D198" t="s">
+        <v>18</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" t="n">
+        <v>9</v>
+      </c>
+      <c r="J198" t="n">
+        <v>3</v>
+      </c>
+      <c r="K198" t="s">
+        <v>57</v>
+      </c>
+      <c r="L198" t="n">
+        <v>2</v>
+      </c>
+      <c r="M198" t="s">
+        <v>25</v>
+      </c>
+      <c r="N198" t="s">
+        <v>26</v>
+      </c>
+      <c r="O198" t="n">
+        <v>8</v>
+      </c>
+      <c r="P198" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q198" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>393</v>
+      </c>
+      <c r="B199" t="b">
+        <v>0</v>
+      </c>
+      <c r="C199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199" t="s">
+        <v>18</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+      <c r="H199" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" t="n">
+        <v>9</v>
+      </c>
+      <c r="J199" t="n">
+        <v>3</v>
+      </c>
+      <c r="K199" t="s">
+        <v>57</v>
+      </c>
+      <c r="L199" t="n">
+        <v>3</v>
+      </c>
+      <c r="M199" t="s">
+        <v>25</v>
+      </c>
+      <c r="N199" t="s">
+        <v>26</v>
+      </c>
+      <c r="O199" t="n">
+        <v>8</v>
+      </c>
+      <c r="P199" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q199" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>397</v>
+      </c>
+      <c r="B200" t="b">
+        <v>0</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200" t="s">
+        <v>18</v>
+      </c>
+      <c r="E200" t="n">
+        <v>2</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1</v>
+      </c>
+      <c r="H200" t="s">
+        <v>27</v>
+      </c>
+      <c r="I200" t="n">
+        <v>9</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="s">
+        <v>56</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="s">
+        <v>28</v>
+      </c>
+      <c r="N200" t="s">
+        <v>29</v>
+      </c>
+      <c r="O200" t="n">
+        <v>5</v>
+      </c>
+      <c r="P200" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q200" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>398</v>
+      </c>
+      <c r="B201" t="b">
+        <v>0</v>
+      </c>
+      <c r="C201" t="s">
+        <v>17</v>
+      </c>
+      <c r="D201" t="s">
+        <v>18</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" t="n">
+        <v>1</v>
+      </c>
+      <c r="H201" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" t="n">
+        <v>9</v>
+      </c>
+      <c r="J201" t="n">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>56</v>
+      </c>
+      <c r="L201" t="n">
+        <v>2</v>
+      </c>
+      <c r="M201" t="s">
+        <v>28</v>
+      </c>
+      <c r="N201" t="s">
+        <v>29</v>
+      </c>
+      <c r="O201" t="n">
+        <v>5</v>
+      </c>
+      <c r="P201" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q201" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>399</v>
+      </c>
+      <c r="B202" t="b">
+        <v>0</v>
+      </c>
+      <c r="C202" t="s">
+        <v>17</v>
+      </c>
+      <c r="D202" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202" t="n">
+        <v>2</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>1</v>
+      </c>
+      <c r="H202" t="s">
+        <v>27</v>
+      </c>
+      <c r="I202" t="n">
+        <v>9</v>
+      </c>
+      <c r="J202" t="n">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>56</v>
+      </c>
+      <c r="L202" t="n">
+        <v>3</v>
+      </c>
+      <c r="M202" t="s">
+        <v>28</v>
+      </c>
+      <c r="N202" t="s">
+        <v>29</v>
+      </c>
+      <c r="O202" t="n">
+        <v>5</v>
+      </c>
+      <c r="P202" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q202" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>403</v>
+      </c>
+      <c r="B203" t="b">
+        <v>0</v>
+      </c>
+      <c r="C203" t="s">
+        <v>17</v>
+      </c>
+      <c r="D203" t="s">
+        <v>18</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2</v>
+      </c>
+      <c r="G203" t="n">
+        <v>1</v>
+      </c>
+      <c r="H203" t="s">
+        <v>30</v>
+      </c>
+      <c r="I203" t="n">
+        <v>9</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>57</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="s">
+        <v>31</v>
+      </c>
+      <c r="N203" t="s">
+        <v>32</v>
+      </c>
+      <c r="O203" t="n">
+        <v>15</v>
+      </c>
+      <c r="P203" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q203" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>404</v>
+      </c>
+      <c r="B204" t="b">
+        <v>0</v>
+      </c>
+      <c r="C204" t="s">
+        <v>17</v>
+      </c>
+      <c r="D204" t="s">
+        <v>18</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="s">
+        <v>30</v>
+      </c>
+      <c r="I204" t="n">
+        <v>9</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>57</v>
+      </c>
+      <c r="L204" t="n">
+        <v>2</v>
+      </c>
+      <c r="M204" t="s">
+        <v>31</v>
+      </c>
+      <c r="N204" t="s">
+        <v>32</v>
+      </c>
+      <c r="O204" t="n">
+        <v>15</v>
+      </c>
+      <c r="P204" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q204" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>405</v>
+      </c>
+      <c r="B205" t="b">
+        <v>0</v>
+      </c>
+      <c r="C205" t="s">
+        <v>17</v>
+      </c>
+      <c r="D205" t="s">
+        <v>18</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2</v>
+      </c>
+      <c r="G205" t="n">
+        <v>1</v>
+      </c>
+      <c r="H205" t="s">
+        <v>30</v>
+      </c>
+      <c r="I205" t="n">
+        <v>9</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="s">
+        <v>57</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="s">
+        <v>31</v>
+      </c>
+      <c r="N205" t="s">
+        <v>32</v>
+      </c>
+      <c r="O205" t="n">
+        <v>15</v>
+      </c>
+      <c r="P205" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q205" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>409</v>
+      </c>
+      <c r="B206" t="b">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s">
+        <v>17</v>
+      </c>
+      <c r="D206" t="s">
+        <v>18</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+      <c r="G206" t="n">
+        <v>2</v>
+      </c>
+      <c r="H206" t="s">
+        <v>33</v>
+      </c>
+      <c r="I206" t="n">
+        <v>9</v>
+      </c>
+      <c r="J206" t="n">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>56</v>
+      </c>
+      <c r="L206" t="n">
+        <v>1</v>
+      </c>
+      <c r="M206" t="s">
+        <v>21</v>
+      </c>
+      <c r="N206" t="s">
+        <v>22</v>
+      </c>
+      <c r="O206" t="n">
+        <v>13</v>
+      </c>
+      <c r="P206" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q206" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>410</v>
+      </c>
+      <c r="B207" t="b">
+        <v>0</v>
+      </c>
+      <c r="C207" t="s">
+        <v>17</v>
+      </c>
+      <c r="D207" t="s">
+        <v>18</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2</v>
+      </c>
+      <c r="H207" t="s">
+        <v>33</v>
+      </c>
+      <c r="I207" t="n">
+        <v>9</v>
+      </c>
+      <c r="J207" t="n">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>56</v>
+      </c>
+      <c r="L207" t="n">
+        <v>2</v>
+      </c>
+      <c r="M207" t="s">
+        <v>21</v>
+      </c>
+      <c r="N207" t="s">
+        <v>22</v>
+      </c>
+      <c r="O207" t="n">
+        <v>13</v>
+      </c>
+      <c r="P207" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q207" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>411</v>
+      </c>
+      <c r="B208" t="b">
+        <v>0</v>
+      </c>
+      <c r="C208" t="s">
+        <v>17</v>
+      </c>
+      <c r="D208" t="s">
+        <v>18</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>2</v>
+      </c>
+      <c r="H208" t="s">
+        <v>33</v>
+      </c>
+      <c r="I208" t="n">
+        <v>9</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>56</v>
+      </c>
+      <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="s">
+        <v>21</v>
+      </c>
+      <c r="N208" t="s">
+        <v>22</v>
+      </c>
+      <c r="O208" t="n">
+        <v>13</v>
+      </c>
+      <c r="P208" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q208" t="n">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>415</v>
+      </c>
+      <c r="B209" t="b">
+        <v>0</v>
+      </c>
+      <c r="C209" t="s">
+        <v>17</v>
+      </c>
+      <c r="D209" t="s">
+        <v>18</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" t="n">
+        <v>2</v>
+      </c>
+      <c r="H209" t="s">
+        <v>34</v>
+      </c>
+      <c r="I209" t="n">
+        <v>9</v>
+      </c>
+      <c r="J209" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>57</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="s">
+        <v>25</v>
+      </c>
+      <c r="N209" t="s">
+        <v>26</v>
+      </c>
+      <c r="O209" t="n">
+        <v>8</v>
+      </c>
+      <c r="P209" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q209" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>416</v>
+      </c>
+      <c r="B210" t="b">
+        <v>0</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>18</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" t="n">
+        <v>2</v>
+      </c>
+      <c r="H210" t="s">
+        <v>34</v>
+      </c>
+      <c r="I210" t="n">
+        <v>9</v>
+      </c>
+      <c r="J210" t="n">
+        <v>3</v>
+      </c>
+      <c r="K210" t="s">
+        <v>57</v>
+      </c>
+      <c r="L210" t="n">
+        <v>2</v>
+      </c>
+      <c r="M210" t="s">
+        <v>25</v>
+      </c>
+      <c r="N210" t="s">
+        <v>26</v>
+      </c>
+      <c r="O210" t="n">
+        <v>8</v>
+      </c>
+      <c r="P210" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q210" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>417</v>
+      </c>
+      <c r="B211" t="b">
+        <v>0</v>
+      </c>
+      <c r="C211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211" t="s">
+        <v>18</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2</v>
+      </c>
+      <c r="G211" t="n">
+        <v>2</v>
+      </c>
+      <c r="H211" t="s">
+        <v>34</v>
+      </c>
+      <c r="I211" t="n">
+        <v>9</v>
+      </c>
+      <c r="J211" t="n">
+        <v>3</v>
+      </c>
+      <c r="K211" t="s">
+        <v>57</v>
+      </c>
+      <c r="L211" t="n">
+        <v>3</v>
+      </c>
+      <c r="M211" t="s">
+        <v>25</v>
+      </c>
+      <c r="N211" t="s">
+        <v>26</v>
+      </c>
+      <c r="O211" t="n">
+        <v>8</v>
+      </c>
+      <c r="P211" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q211" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>421</v>
+      </c>
+      <c r="B212" t="b">
+        <v>0</v>
+      </c>
+      <c r="C212" t="s">
+        <v>17</v>
+      </c>
+      <c r="D212" t="s">
+        <v>18</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" t="n">
+        <v>2</v>
+      </c>
+      <c r="H212" t="s">
         <v>35</v>
       </c>
-      <c r="Q145" t="n">
-        <v>633</v>
+      <c r="I212" t="n">
+        <v>9</v>
+      </c>
+      <c r="J212" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" t="s">
+        <v>56</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="s">
+        <v>28</v>
+      </c>
+      <c r="N212" t="s">
+        <v>29</v>
+      </c>
+      <c r="O212" t="n">
+        <v>5</v>
+      </c>
+      <c r="P212" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q212" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>422</v>
+      </c>
+      <c r="B213" t="b">
+        <v>0</v>
+      </c>
+      <c r="C213" t="s">
+        <v>17</v>
+      </c>
+      <c r="D213" t="s">
+        <v>18</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1</v>
+      </c>
+      <c r="G213" t="n">
+        <v>2</v>
+      </c>
+      <c r="H213" t="s">
+        <v>35</v>
+      </c>
+      <c r="I213" t="n">
+        <v>9</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>56</v>
+      </c>
+      <c r="L213" t="n">
+        <v>2</v>
+      </c>
+      <c r="M213" t="s">
+        <v>28</v>
+      </c>
+      <c r="N213" t="s">
+        <v>29</v>
+      </c>
+      <c r="O213" t="n">
+        <v>5</v>
+      </c>
+      <c r="P213" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q213" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>423</v>
+      </c>
+      <c r="B214" t="b">
+        <v>0</v>
+      </c>
+      <c r="C214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" t="s">
+        <v>18</v>
+      </c>
+      <c r="E214" t="n">
+        <v>2</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>2</v>
+      </c>
+      <c r="H214" t="s">
+        <v>35</v>
+      </c>
+      <c r="I214" t="n">
+        <v>9</v>
+      </c>
+      <c r="J214" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>56</v>
+      </c>
+      <c r="L214" t="n">
+        <v>3</v>
+      </c>
+      <c r="M214" t="s">
+        <v>28</v>
+      </c>
+      <c r="N214" t="s">
+        <v>29</v>
+      </c>
+      <c r="O214" t="n">
+        <v>5</v>
+      </c>
+      <c r="P214" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q214" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>427</v>
+      </c>
+      <c r="B215" t="b">
+        <v>0</v>
+      </c>
+      <c r="C215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215" t="s">
+        <v>18</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2</v>
+      </c>
+      <c r="G215" t="n">
+        <v>2</v>
+      </c>
+      <c r="H215" t="s">
+        <v>36</v>
+      </c>
+      <c r="I215" t="n">
+        <v>9</v>
+      </c>
+      <c r="J215" t="n">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>57</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="s">
+        <v>31</v>
+      </c>
+      <c r="N215" t="s">
+        <v>32</v>
+      </c>
+      <c r="O215" t="n">
+        <v>15</v>
+      </c>
+      <c r="P215" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q215" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>428</v>
+      </c>
+      <c r="B216" t="b">
+        <v>0</v>
+      </c>
+      <c r="C216" t="s">
+        <v>17</v>
+      </c>
+      <c r="D216" t="s">
+        <v>18</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>2</v>
+      </c>
+      <c r="H216" t="s">
+        <v>36</v>
+      </c>
+      <c r="I216" t="n">
+        <v>9</v>
+      </c>
+      <c r="J216" t="n">
+        <v>3</v>
+      </c>
+      <c r="K216" t="s">
+        <v>57</v>
+      </c>
+      <c r="L216" t="n">
+        <v>2</v>
+      </c>
+      <c r="M216" t="s">
+        <v>31</v>
+      </c>
+      <c r="N216" t="s">
+        <v>32</v>
+      </c>
+      <c r="O216" t="n">
+        <v>15</v>
+      </c>
+      <c r="P216" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q216" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>429</v>
+      </c>
+      <c r="B217" t="b">
+        <v>0</v>
+      </c>
+      <c r="C217" t="s">
+        <v>17</v>
+      </c>
+      <c r="D217" t="s">
+        <v>18</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2</v>
+      </c>
+      <c r="G217" t="n">
+        <v>2</v>
+      </c>
+      <c r="H217" t="s">
+        <v>36</v>
+      </c>
+      <c r="I217" t="n">
+        <v>9</v>
+      </c>
+      <c r="J217" t="n">
+        <v>3</v>
+      </c>
+      <c r="K217" t="s">
+        <v>57</v>
+      </c>
+      <c r="L217" t="n">
+        <v>3</v>
+      </c>
+      <c r="M217" t="s">
+        <v>31</v>
+      </c>
+      <c r="N217" t="s">
+        <v>32</v>
+      </c>
+      <c r="O217" t="n">
+        <v>15</v>
+      </c>
+      <c r="P217" t="n">
+        <v>56</v>
+      </c>
+      <c r="Q217" t="n">
+        <v>837</v>
       </c>
     </row>
   </sheetData>
